--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="197">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -966,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP96"/>
+  <dimension ref="A1:BP97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2536,10 +2536,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -4805,7 +4805,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -5008,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ20">
         <v>1.44</v>
@@ -6656,7 +6656,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ28">
         <v>1.1</v>
@@ -7895,7 +7895,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR34">
         <v>1.39</v>
@@ -9540,7 +9540,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ42">
         <v>1.33</v>
@@ -9749,7 +9749,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR43">
         <v>1.56</v>
@@ -10982,7 +10982,7 @@
         <v>1.75</v>
       </c>
       <c r="AP49">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ49">
         <v>1.33</v>
@@ -11397,7 +11397,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR51">
         <v>1.18</v>
@@ -13045,7 +13045,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13248,7 +13248,7 @@
         <v>1.8</v>
       </c>
       <c r="AP60">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ60">
         <v>1.89</v>
@@ -14690,7 +14690,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ67">
         <v>0.8</v>
@@ -15517,7 +15517,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ71">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR71">
         <v>0.93</v>
@@ -16135,7 +16135,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -16956,7 +16956,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ78">
         <v>0.9</v>
@@ -17783,7 +17783,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ82">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AR82">
         <v>1.53</v>
@@ -18192,7 +18192,7 @@
         <v>0.88</v>
       </c>
       <c r="AP84">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ84">
         <v>0.9</v>
@@ -20743,6 +20743,212 @@
       </c>
       <c r="BP96">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7451064</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45688.54166666666</v>
+      </c>
+      <c r="F97">
+        <v>20</v>
+      </c>
+      <c r="G97" t="s">
+        <v>76</v>
+      </c>
+      <c r="H97" t="s">
+        <v>71</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
+        <v>81</v>
+      </c>
+      <c r="P97" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q97">
+        <v>2.5</v>
+      </c>
+      <c r="R97">
+        <v>2.1</v>
+      </c>
+      <c r="S97">
+        <v>5</v>
+      </c>
+      <c r="T97">
+        <v>1.44</v>
+      </c>
+      <c r="U97">
+        <v>2.63</v>
+      </c>
+      <c r="V97">
+        <v>3.25</v>
+      </c>
+      <c r="W97">
+        <v>1.33</v>
+      </c>
+      <c r="X97">
+        <v>9</v>
+      </c>
+      <c r="Y97">
+        <v>1.07</v>
+      </c>
+      <c r="Z97">
+        <v>1.75</v>
+      </c>
+      <c r="AA97">
+        <v>3.4</v>
+      </c>
+      <c r="AB97">
+        <v>4.1</v>
+      </c>
+      <c r="AC97">
+        <v>1.06</v>
+      </c>
+      <c r="AD97">
+        <v>8</v>
+      </c>
+      <c r="AE97">
+        <v>1.36</v>
+      </c>
+      <c r="AF97">
+        <v>3</v>
+      </c>
+      <c r="AG97">
+        <v>2.2</v>
+      </c>
+      <c r="AH97">
+        <v>1.65</v>
+      </c>
+      <c r="AI97">
+        <v>2</v>
+      </c>
+      <c r="AJ97">
+        <v>1.73</v>
+      </c>
+      <c r="AK97">
+        <v>1.21</v>
+      </c>
+      <c r="AL97">
+        <v>1.29</v>
+      </c>
+      <c r="AM97">
+        <v>1.9</v>
+      </c>
+      <c r="AN97">
+        <v>1.11</v>
+      </c>
+      <c r="AO97">
+        <v>0</v>
+      </c>
+      <c r="AP97">
+        <v>1.1</v>
+      </c>
+      <c r="AQ97">
+        <v>0.1</v>
+      </c>
+      <c r="AR97">
+        <v>1.22</v>
+      </c>
+      <c r="AS97">
+        <v>0.96</v>
+      </c>
+      <c r="AT97">
+        <v>2.18</v>
+      </c>
+      <c r="AU97">
+        <v>6</v>
+      </c>
+      <c r="AV97">
+        <v>2</v>
+      </c>
+      <c r="AW97">
+        <v>9</v>
+      </c>
+      <c r="AX97">
+        <v>3</v>
+      </c>
+      <c r="AY97">
+        <v>15</v>
+      </c>
+      <c r="AZ97">
+        <v>5</v>
+      </c>
+      <c r="BA97">
+        <v>5</v>
+      </c>
+      <c r="BB97">
+        <v>4</v>
+      </c>
+      <c r="BC97">
+        <v>9</v>
+      </c>
+      <c r="BD97">
+        <v>1.47</v>
+      </c>
+      <c r="BE97">
+        <v>7.3</v>
+      </c>
+      <c r="BF97">
+        <v>3.66</v>
+      </c>
+      <c r="BG97">
+        <v>1.55</v>
+      </c>
+      <c r="BH97">
+        <v>2.23</v>
+      </c>
+      <c r="BI97">
+        <v>1.99</v>
+      </c>
+      <c r="BJ97">
+        <v>1.73</v>
+      </c>
+      <c r="BK97">
+        <v>2.64</v>
+      </c>
+      <c r="BL97">
+        <v>1.4</v>
+      </c>
+      <c r="BM97">
+        <v>3.7</v>
+      </c>
+      <c r="BN97">
+        <v>1.2</v>
+      </c>
+      <c r="BO97">
+        <v>5.25</v>
+      </c>
+      <c r="BP97">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="202">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -457,6 +457,15 @@
     <t>['22', '40', '49', '58']</t>
   </si>
   <si>
+    <t>['31']</t>
+  </si>
+  <si>
+    <t>['24', '25', '72']</t>
+  </si>
+  <si>
+    <t>['2', '60']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -535,9 +544,6 @@
     <t>['27']</t>
   </si>
   <si>
-    <t>['31']</t>
-  </si>
-  <si>
     <t>['22', '40', '55', '89']</t>
   </si>
   <si>
@@ -605,6 +611,15 @@
   </si>
   <si>
     <t>['53']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['14', '53']</t>
+  </si>
+  <si>
+    <t>['57']</t>
   </si>
 </sst>
 </file>
@@ -966,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP97"/>
+  <dimension ref="A1:BP101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1840,7 +1855,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -1918,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ5">
         <v>0.9</v>
@@ -2046,7 +2061,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2127,7 +2142,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ6">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2330,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ7">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2664,7 +2679,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2742,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ9">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2870,7 +2885,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -2948,10 +2963,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR10">
         <v>3.14</v>
@@ -3154,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ11">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3488,7 +3503,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3694,7 +3709,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3900,7 +3915,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4390,7 +4405,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ17">
         <v>0.9</v>
@@ -4596,10 +4611,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ18">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR18">
         <v>0.8100000000000001</v>
@@ -4724,7 +4739,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4930,7 +4945,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5011,7 +5026,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ20">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR20">
         <v>1.92</v>
@@ -5136,7 +5151,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5214,10 +5229,10 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ21">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR21">
         <v>2.05</v>
@@ -5342,7 +5357,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5548,7 +5563,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6038,7 +6053,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ25">
         <v>0.9</v>
@@ -6166,7 +6181,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6247,7 +6262,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR26">
         <v>1.71</v>
@@ -6372,7 +6387,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6453,7 +6468,7 @@
         <v>2</v>
       </c>
       <c r="AQ27">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR27">
         <v>1.84</v>
@@ -6578,7 +6593,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6784,7 +6799,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -6865,7 +6880,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR29">
         <v>1.12</v>
@@ -7068,10 +7083,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ30">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR30">
         <v>1.82</v>
@@ -7274,7 +7289,7 @@
         <v>1.33</v>
       </c>
       <c r="AP31">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ31">
         <v>0.9</v>
@@ -7480,7 +7495,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ32">
         <v>0.9</v>
@@ -7608,7 +7623,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7689,7 +7704,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ33">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -7814,7 +7829,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8020,7 +8035,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8098,7 +8113,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ35">
         <v>1.33</v>
@@ -8510,7 +8525,7 @@
         <v>0.75</v>
       </c>
       <c r="AP37">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ37">
         <v>0.9</v>
@@ -8922,7 +8937,7 @@
         <v>1.25</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ39">
         <v>0.9</v>
@@ -9131,7 +9146,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ40">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR40">
         <v>1.7</v>
@@ -9256,7 +9271,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9337,7 +9352,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ41">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -9462,7 +9477,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9746,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ43">
         <v>0.1</v>
@@ -9955,7 +9970,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ44">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10080,7 +10095,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10158,10 +10173,10 @@
         <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ45">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR45">
         <v>1.19</v>
@@ -10492,7 +10507,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10570,10 +10585,10 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ47">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR47">
         <v>1.56</v>
@@ -10698,7 +10713,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10776,7 +10791,7 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -10904,7 +10919,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -10985,7 +11000,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ49">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11110,7 +11125,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11191,7 +11206,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ50">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR50">
         <v>1.52</v>
@@ -11394,7 +11409,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ51">
         <v>0.1</v>
@@ -11522,7 +11537,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11728,7 +11743,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11934,7 +11949,7 @@
         <v>100</v>
       </c>
       <c r="P54" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -12140,7 +12155,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12552,7 +12567,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12630,10 +12645,10 @@
         <v>1.6</v>
       </c>
       <c r="AP57">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR57">
         <v>1.11</v>
@@ -12758,7 +12773,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12836,10 +12851,10 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ58">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR58">
         <v>1.49</v>
@@ -13042,7 +13057,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ59">
         <v>0.1</v>
@@ -13170,7 +13185,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13251,7 +13266,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ60">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR60">
         <v>1.28</v>
@@ -13454,10 +13469,10 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ61">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR61">
         <v>1.34</v>
@@ -13582,7 +13597,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13660,7 +13675,7 @@
         <v>0.8</v>
       </c>
       <c r="AP62">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ62">
         <v>1.1</v>
@@ -13788,7 +13803,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -13869,7 +13884,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR63">
         <v>1.18</v>
@@ -13994,7 +14009,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14200,7 +14215,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14406,7 +14421,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14612,7 +14627,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14693,7 +14708,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ67">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR67">
         <v>1.18</v>
@@ -14818,7 +14833,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14896,7 +14911,7 @@
         <v>1.17</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ68">
         <v>1.1</v>
@@ -15105,7 +15120,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR69">
         <v>1.96</v>
@@ -15230,7 +15245,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15308,10 +15323,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ70">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR70">
         <v>1.61</v>
@@ -15514,7 +15529,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ71">
         <v>0.1</v>
@@ -15642,7 +15657,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15720,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ72">
         <v>0.9</v>
@@ -15848,7 +15863,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16260,7 +16275,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16338,7 +16353,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ75">
         <v>0.9</v>
@@ -16547,7 +16562,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR76">
         <v>1.66</v>
@@ -16753,7 +16768,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR77">
         <v>1.79</v>
@@ -17165,7 +17180,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ79">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR79">
         <v>1.09</v>
@@ -17290,7 +17305,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17368,10 +17383,10 @@
         <v>1.86</v>
       </c>
       <c r="AP80">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ80">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -17574,7 +17589,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ81">
         <v>1.1</v>
@@ -17702,7 +17717,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17908,7 +17923,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -17986,10 +18001,10 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR83">
         <v>1.51</v>
@@ -18114,7 +18129,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18398,7 +18413,7 @@
         <v>1.38</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ85">
         <v>1.33</v>
@@ -18526,7 +18541,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18607,7 +18622,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ86">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR86">
         <v>1.59</v>
@@ -18732,7 +18747,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18810,7 +18825,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ87">
         <v>0.9</v>
@@ -18938,7 +18953,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19144,7 +19159,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19431,7 +19446,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ90">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR90">
         <v>1.63</v>
@@ -19556,7 +19571,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19634,10 +19649,10 @@
         <v>1.25</v>
       </c>
       <c r="AP91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ91">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR91">
         <v>1.08</v>
@@ -19762,7 +19777,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -19840,7 +19855,7 @@
         <v>0.89</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AQ92">
         <v>0.9</v>
@@ -19968,7 +19983,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20174,7 +20189,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20380,7 +20395,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20667,7 +20682,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ96">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -20949,6 +20964,830 @@
       </c>
       <c r="BP97">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7451061</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F98">
+        <v>20</v>
+      </c>
+      <c r="G98" t="s">
+        <v>75</v>
+      </c>
+      <c r="H98" t="s">
+        <v>79</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>83</v>
+      </c>
+      <c r="P98" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q98">
+        <v>3.75</v>
+      </c>
+      <c r="R98">
+        <v>2.05</v>
+      </c>
+      <c r="S98">
+        <v>3</v>
+      </c>
+      <c r="T98">
+        <v>1.44</v>
+      </c>
+      <c r="U98">
+        <v>2.63</v>
+      </c>
+      <c r="V98">
+        <v>3</v>
+      </c>
+      <c r="W98">
+        <v>1.36</v>
+      </c>
+      <c r="X98">
+        <v>9</v>
+      </c>
+      <c r="Y98">
+        <v>1.07</v>
+      </c>
+      <c r="Z98">
+        <v>3.1</v>
+      </c>
+      <c r="AA98">
+        <v>3.2</v>
+      </c>
+      <c r="AB98">
+        <v>2.2</v>
+      </c>
+      <c r="AC98">
+        <v>1.07</v>
+      </c>
+      <c r="AD98">
+        <v>7.75</v>
+      </c>
+      <c r="AE98">
+        <v>1.35</v>
+      </c>
+      <c r="AF98">
+        <v>2.9</v>
+      </c>
+      <c r="AG98">
+        <v>2.1</v>
+      </c>
+      <c r="AH98">
+        <v>1.7</v>
+      </c>
+      <c r="AI98">
+        <v>1.83</v>
+      </c>
+      <c r="AJ98">
+        <v>1.83</v>
+      </c>
+      <c r="AK98">
+        <v>1.61</v>
+      </c>
+      <c r="AL98">
+        <v>1.33</v>
+      </c>
+      <c r="AM98">
+        <v>1.33</v>
+      </c>
+      <c r="AN98">
+        <v>0.89</v>
+      </c>
+      <c r="AO98">
+        <v>0.8</v>
+      </c>
+      <c r="AP98">
+        <v>0.9</v>
+      </c>
+      <c r="AQ98">
+        <v>0.82</v>
+      </c>
+      <c r="AR98">
+        <v>1.13</v>
+      </c>
+      <c r="AS98">
+        <v>1.37</v>
+      </c>
+      <c r="AT98">
+        <v>2.5</v>
+      </c>
+      <c r="AU98">
+        <v>4</v>
+      </c>
+      <c r="AV98">
+        <v>3</v>
+      </c>
+      <c r="AW98">
+        <v>9</v>
+      </c>
+      <c r="AX98">
+        <v>3</v>
+      </c>
+      <c r="AY98">
+        <v>13</v>
+      </c>
+      <c r="AZ98">
+        <v>6</v>
+      </c>
+      <c r="BA98">
+        <v>2</v>
+      </c>
+      <c r="BB98">
+        <v>4</v>
+      </c>
+      <c r="BC98">
+        <v>6</v>
+      </c>
+      <c r="BD98">
+        <v>2.48</v>
+      </c>
+      <c r="BE98">
+        <v>6.6</v>
+      </c>
+      <c r="BF98">
+        <v>1.75</v>
+      </c>
+      <c r="BG98">
+        <v>1.42</v>
+      </c>
+      <c r="BH98">
+        <v>2.62</v>
+      </c>
+      <c r="BI98">
+        <v>1.78</v>
+      </c>
+      <c r="BJ98">
+        <v>1.9</v>
+      </c>
+      <c r="BK98">
+        <v>2.38</v>
+      </c>
+      <c r="BL98">
+        <v>1.5</v>
+      </c>
+      <c r="BM98">
+        <v>3.4</v>
+      </c>
+      <c r="BN98">
+        <v>1.26</v>
+      </c>
+      <c r="BO98">
+        <v>4.15</v>
+      </c>
+      <c r="BP98">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7451063</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45689.5625</v>
+      </c>
+      <c r="F99">
+        <v>20</v>
+      </c>
+      <c r="G99" t="s">
+        <v>78</v>
+      </c>
+      <c r="H99" t="s">
+        <v>72</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="s">
+        <v>147</v>
+      </c>
+      <c r="P99" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q99">
+        <v>5</v>
+      </c>
+      <c r="R99">
+        <v>1.95</v>
+      </c>
+      <c r="S99">
+        <v>2.75</v>
+      </c>
+      <c r="T99">
+        <v>1.53</v>
+      </c>
+      <c r="U99">
+        <v>2.4</v>
+      </c>
+      <c r="V99">
+        <v>3.62</v>
+      </c>
+      <c r="W99">
+        <v>1.26</v>
+      </c>
+      <c r="X99">
+        <v>11.75</v>
+      </c>
+      <c r="Y99">
+        <v>1.02</v>
+      </c>
+      <c r="Z99">
+        <v>4</v>
+      </c>
+      <c r="AA99">
+        <v>3.1</v>
+      </c>
+      <c r="AB99">
+        <v>1.9</v>
+      </c>
+      <c r="AC99">
+        <v>1.03</v>
+      </c>
+      <c r="AD99">
+        <v>7.3</v>
+      </c>
+      <c r="AE99">
+        <v>1.42</v>
+      </c>
+      <c r="AF99">
+        <v>2.5</v>
+      </c>
+      <c r="AG99">
+        <v>2.4</v>
+      </c>
+      <c r="AH99">
+        <v>1.53</v>
+      </c>
+      <c r="AI99">
+        <v>2.2</v>
+      </c>
+      <c r="AJ99">
+        <v>1.62</v>
+      </c>
+      <c r="AK99">
+        <v>1.81</v>
+      </c>
+      <c r="AL99">
+        <v>1.33</v>
+      </c>
+      <c r="AM99">
+        <v>1.21</v>
+      </c>
+      <c r="AN99">
+        <v>2</v>
+      </c>
+      <c r="AO99">
+        <v>1.89</v>
+      </c>
+      <c r="AP99">
+        <v>2.1</v>
+      </c>
+      <c r="AQ99">
+        <v>1.7</v>
+      </c>
+      <c r="AR99">
+        <v>1.4</v>
+      </c>
+      <c r="AS99">
+        <v>1.29</v>
+      </c>
+      <c r="AT99">
+        <v>2.69</v>
+      </c>
+      <c r="AU99">
+        <v>2</v>
+      </c>
+      <c r="AV99">
+        <v>2</v>
+      </c>
+      <c r="AW99">
+        <v>7</v>
+      </c>
+      <c r="AX99">
+        <v>7</v>
+      </c>
+      <c r="AY99">
+        <v>9</v>
+      </c>
+      <c r="AZ99">
+        <v>9</v>
+      </c>
+      <c r="BA99">
+        <v>1</v>
+      </c>
+      <c r="BB99">
+        <v>3</v>
+      </c>
+      <c r="BC99">
+        <v>4</v>
+      </c>
+      <c r="BD99">
+        <v>2.53</v>
+      </c>
+      <c r="BE99">
+        <v>7.5</v>
+      </c>
+      <c r="BF99">
+        <v>1.75</v>
+      </c>
+      <c r="BG99">
+        <v>1.66</v>
+      </c>
+      <c r="BH99">
+        <v>2.14</v>
+      </c>
+      <c r="BI99">
+        <v>2.11</v>
+      </c>
+      <c r="BJ99">
+        <v>1.68</v>
+      </c>
+      <c r="BK99">
+        <v>2.8</v>
+      </c>
+      <c r="BL99">
+        <v>1.4</v>
+      </c>
+      <c r="BM99">
+        <v>3.95</v>
+      </c>
+      <c r="BN99">
+        <v>1.22</v>
+      </c>
+      <c r="BO99">
+        <v>5.7</v>
+      </c>
+      <c r="BP99">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7451062</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45690.36805555555</v>
+      </c>
+      <c r="F100">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>77</v>
+      </c>
+      <c r="H100" t="s">
+        <v>74</v>
+      </c>
+      <c r="I100">
+        <v>2</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>3</v>
+      </c>
+      <c r="L100">
+        <v>3</v>
+      </c>
+      <c r="M100">
+        <v>2</v>
+      </c>
+      <c r="N100">
+        <v>5</v>
+      </c>
+      <c r="O100" t="s">
+        <v>148</v>
+      </c>
+      <c r="P100" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q100">
+        <v>4.75</v>
+      </c>
+      <c r="R100">
+        <v>2.1</v>
+      </c>
+      <c r="S100">
+        <v>2.5</v>
+      </c>
+      <c r="T100">
+        <v>1.41</v>
+      </c>
+      <c r="U100">
+        <v>2.7</v>
+      </c>
+      <c r="V100">
+        <v>2.85</v>
+      </c>
+      <c r="W100">
+        <v>1.37</v>
+      </c>
+      <c r="X100">
+        <v>7.4</v>
+      </c>
+      <c r="Y100">
+        <v>1.06</v>
+      </c>
+      <c r="Z100">
+        <v>4</v>
+      </c>
+      <c r="AA100">
+        <v>3.4</v>
+      </c>
+      <c r="AB100">
+        <v>1.8</v>
+      </c>
+      <c r="AC100">
+        <v>1.01</v>
+      </c>
+      <c r="AD100">
+        <v>8.5</v>
+      </c>
+      <c r="AE100">
+        <v>1.3</v>
+      </c>
+      <c r="AF100">
+        <v>3.3</v>
+      </c>
+      <c r="AG100">
+        <v>1.95</v>
+      </c>
+      <c r="AH100">
+        <v>1.85</v>
+      </c>
+      <c r="AI100">
+        <v>1.83</v>
+      </c>
+      <c r="AJ100">
+        <v>1.83</v>
+      </c>
+      <c r="AK100">
+        <v>2</v>
+      </c>
+      <c r="AL100">
+        <v>1.22</v>
+      </c>
+      <c r="AM100">
+        <v>1.16</v>
+      </c>
+      <c r="AN100">
+        <v>0.89</v>
+      </c>
+      <c r="AO100">
+        <v>1.44</v>
+      </c>
+      <c r="AP100">
+        <v>1.1</v>
+      </c>
+      <c r="AQ100">
+        <v>1.3</v>
+      </c>
+      <c r="AR100">
+        <v>1.46</v>
+      </c>
+      <c r="AS100">
+        <v>1.45</v>
+      </c>
+      <c r="AT100">
+        <v>2.91</v>
+      </c>
+      <c r="AU100">
+        <v>8</v>
+      </c>
+      <c r="AV100">
+        <v>6</v>
+      </c>
+      <c r="AW100">
+        <v>3</v>
+      </c>
+      <c r="AX100">
+        <v>5</v>
+      </c>
+      <c r="AY100">
+        <v>11</v>
+      </c>
+      <c r="AZ100">
+        <v>11</v>
+      </c>
+      <c r="BA100">
+        <v>4</v>
+      </c>
+      <c r="BB100">
+        <v>5</v>
+      </c>
+      <c r="BC100">
+        <v>9</v>
+      </c>
+      <c r="BD100">
+        <v>2.77</v>
+      </c>
+      <c r="BE100">
+        <v>8</v>
+      </c>
+      <c r="BF100">
+        <v>1.64</v>
+      </c>
+      <c r="BG100">
+        <v>1.15</v>
+      </c>
+      <c r="BH100">
+        <v>4.95</v>
+      </c>
+      <c r="BI100">
+        <v>1.29</v>
+      </c>
+      <c r="BJ100">
+        <v>3.38</v>
+      </c>
+      <c r="BK100">
+        <v>2.25</v>
+      </c>
+      <c r="BL100">
+        <v>2.46</v>
+      </c>
+      <c r="BM100">
+        <v>1.82</v>
+      </c>
+      <c r="BN100">
+        <v>1.93</v>
+      </c>
+      <c r="BO100">
+        <v>2.27</v>
+      </c>
+      <c r="BP100">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7451065</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F101">
+        <v>20</v>
+      </c>
+      <c r="G101" t="s">
+        <v>73</v>
+      </c>
+      <c r="H101" t="s">
+        <v>70</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101">
+        <v>3</v>
+      </c>
+      <c r="O101" t="s">
+        <v>149</v>
+      </c>
+      <c r="P101" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q101">
+        <v>4</v>
+      </c>
+      <c r="R101">
+        <v>2.25</v>
+      </c>
+      <c r="S101">
+        <v>2.63</v>
+      </c>
+      <c r="T101">
+        <v>1.33</v>
+      </c>
+      <c r="U101">
+        <v>3.15</v>
+      </c>
+      <c r="V101">
+        <v>2.57</v>
+      </c>
+      <c r="W101">
+        <v>1.47</v>
+      </c>
+      <c r="X101">
+        <v>6.6</v>
+      </c>
+      <c r="Y101">
+        <v>1.09</v>
+      </c>
+      <c r="Z101">
+        <v>3.4</v>
+      </c>
+      <c r="AA101">
+        <v>3.4</v>
+      </c>
+      <c r="AB101">
+        <v>1.95</v>
+      </c>
+      <c r="AC101">
+        <v>1.01</v>
+      </c>
+      <c r="AD101">
+        <v>11</v>
+      </c>
+      <c r="AE101">
+        <v>1.18</v>
+      </c>
+      <c r="AF101">
+        <v>3.88</v>
+      </c>
+      <c r="AG101">
+        <v>1.73</v>
+      </c>
+      <c r="AH101">
+        <v>2.08</v>
+      </c>
+      <c r="AI101">
+        <v>1.62</v>
+      </c>
+      <c r="AJ101">
+        <v>2.2</v>
+      </c>
+      <c r="AK101">
+        <v>1.8</v>
+      </c>
+      <c r="AL101">
+        <v>1.26</v>
+      </c>
+      <c r="AM101">
+        <v>1.28</v>
+      </c>
+      <c r="AN101">
+        <v>1.5</v>
+      </c>
+      <c r="AO101">
+        <v>1.33</v>
+      </c>
+      <c r="AP101">
+        <v>1.64</v>
+      </c>
+      <c r="AQ101">
+        <v>1.2</v>
+      </c>
+      <c r="AR101">
+        <v>1.55</v>
+      </c>
+      <c r="AS101">
+        <v>1.7</v>
+      </c>
+      <c r="AT101">
+        <v>3.25</v>
+      </c>
+      <c r="AU101">
+        <v>5</v>
+      </c>
+      <c r="AV101">
+        <v>14</v>
+      </c>
+      <c r="AW101">
+        <v>5</v>
+      </c>
+      <c r="AX101">
+        <v>6</v>
+      </c>
+      <c r="AY101">
+        <v>10</v>
+      </c>
+      <c r="AZ101">
+        <v>20</v>
+      </c>
+      <c r="BA101">
+        <v>3</v>
+      </c>
+      <c r="BB101">
+        <v>11</v>
+      </c>
+      <c r="BC101">
+        <v>14</v>
+      </c>
+      <c r="BD101">
+        <v>2.44</v>
+      </c>
+      <c r="BE101">
+        <v>8</v>
+      </c>
+      <c r="BF101">
+        <v>1.75</v>
+      </c>
+      <c r="BG101">
+        <v>1.29</v>
+      </c>
+      <c r="BH101">
+        <v>3.35</v>
+      </c>
+      <c r="BI101">
+        <v>1.53</v>
+      </c>
+      <c r="BJ101">
+        <v>2.41</v>
+      </c>
+      <c r="BK101">
+        <v>1.87</v>
+      </c>
+      <c r="BL101">
+        <v>1.87</v>
+      </c>
+      <c r="BM101">
+        <v>2.38</v>
+      </c>
+      <c r="BN101">
+        <v>1.54</v>
+      </c>
+      <c r="BO101">
+        <v>3.2</v>
+      </c>
+      <c r="BP101">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="203">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -464,6 +464,9 @@
   </si>
   <si>
     <t>['2', '60']</t>
+  </si>
+  <si>
+    <t>['38', '74', '78']</t>
   </si>
   <si>
     <t>['8', '61']</t>
@@ -981,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP101"/>
+  <dimension ref="A1:BP102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1315,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ2">
         <v>0.9</v>
@@ -1855,7 +1858,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -1936,7 +1939,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ5">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2061,7 +2064,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2679,7 +2682,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2885,7 +2888,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3375,10 +3378,10 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ12">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR12">
         <v>2.03</v>
@@ -3503,7 +3506,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3709,7 +3712,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3915,7 +3918,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4408,7 +4411,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ17">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR17">
         <v>1.8</v>
@@ -4739,7 +4742,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4817,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ19">
         <v>0.1</v>
@@ -4945,7 +4948,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5151,7 +5154,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5357,7 +5360,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5438,7 +5441,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ22">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR22">
         <v>1.22</v>
@@ -5563,7 +5566,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6181,7 +6184,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6387,7 +6390,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6465,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ27">
         <v>1.3</v>
@@ -6593,7 +6596,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6799,7 +6802,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7623,7 +7626,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7829,7 +7832,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8035,7 +8038,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8322,7 +8325,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ36">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR36">
         <v>1.6</v>
@@ -8731,7 +8734,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ38">
         <v>1.1</v>
@@ -9271,7 +9274,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9477,7 +9480,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10095,7 +10098,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10382,7 +10385,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ46">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10507,7 +10510,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10713,7 +10716,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10919,7 +10922,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11125,7 +11128,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11537,7 +11540,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11618,7 +11621,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ52">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR52">
         <v>1.48</v>
@@ -11743,7 +11746,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12155,7 +12158,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12233,7 +12236,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ55">
         <v>1.33</v>
@@ -12567,7 +12570,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12773,7 +12776,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13185,7 +13188,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13597,7 +13600,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13803,7 +13806,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14009,7 +14012,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14215,7 +14218,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14421,7 +14424,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14627,7 +14630,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14833,7 +14836,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15117,7 +15120,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ69">
         <v>1.7</v>
@@ -15245,7 +15248,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15657,7 +15660,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15738,7 +15741,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ72">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR72">
         <v>1.34</v>
@@ -15863,7 +15866,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16275,7 +16278,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16765,7 +16768,7 @@
         <v>0.86</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ77">
         <v>0.82</v>
@@ -17305,7 +17308,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17717,7 +17720,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17923,7 +17926,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18129,7 +18132,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18210,7 +18213,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ84">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR84">
         <v>1.2</v>
@@ -18541,7 +18544,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18747,7 +18750,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18953,7 +18956,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19159,7 +19162,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19237,7 +19240,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ89">
         <v>0.9</v>
@@ -19571,7 +19574,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19777,7 +19780,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -19858,7 +19861,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ92">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR92">
         <v>1.57</v>
@@ -19983,7 +19986,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20189,7 +20192,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20267,7 +20270,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ94">
         <v>0.9</v>
@@ -20395,7 +20398,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21013,7 +21016,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21425,7 +21428,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21631,7 +21634,7 @@
         <v>149</v>
       </c>
       <c r="P101" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21788,6 +21791,212 @@
       </c>
       <c r="BP101">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7451066</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45695.58333333334</v>
+      </c>
+      <c r="F102">
+        <v>21</v>
+      </c>
+      <c r="G102" t="s">
+        <v>70</v>
+      </c>
+      <c r="H102" t="s">
+        <v>75</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>3</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>3</v>
+      </c>
+      <c r="O102" t="s">
+        <v>150</v>
+      </c>
+      <c r="P102" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q102">
+        <v>1.51</v>
+      </c>
+      <c r="R102">
+        <v>3.01</v>
+      </c>
+      <c r="S102">
+        <v>10.71</v>
+      </c>
+      <c r="T102">
+        <v>1.24</v>
+      </c>
+      <c r="U102">
+        <v>3.8</v>
+      </c>
+      <c r="V102">
+        <v>2.23</v>
+      </c>
+      <c r="W102">
+        <v>1.61</v>
+      </c>
+      <c r="X102">
+        <v>5.1</v>
+      </c>
+      <c r="Y102">
+        <v>1.15</v>
+      </c>
+      <c r="Z102">
+        <v>1.17</v>
+      </c>
+      <c r="AA102">
+        <v>7.31</v>
+      </c>
+      <c r="AB102">
+        <v>11.95</v>
+      </c>
+      <c r="AC102">
+        <v>1.01</v>
+      </c>
+      <c r="AD102">
+        <v>17</v>
+      </c>
+      <c r="AE102">
+        <v>1.13</v>
+      </c>
+      <c r="AF102">
+        <v>6</v>
+      </c>
+      <c r="AG102">
+        <v>1.47</v>
+      </c>
+      <c r="AH102">
+        <v>2.63</v>
+      </c>
+      <c r="AI102">
+        <v>2.21</v>
+      </c>
+      <c r="AJ102">
+        <v>1.63</v>
+      </c>
+      <c r="AK102">
+        <v>1.01</v>
+      </c>
+      <c r="AL102">
+        <v>1.08</v>
+      </c>
+      <c r="AM102">
+        <v>5</v>
+      </c>
+      <c r="AN102">
+        <v>2</v>
+      </c>
+      <c r="AO102">
+        <v>0.9</v>
+      </c>
+      <c r="AP102">
+        <v>2.09</v>
+      </c>
+      <c r="AQ102">
+        <v>0.82</v>
+      </c>
+      <c r="AR102">
+        <v>1.92</v>
+      </c>
+      <c r="AS102">
+        <v>1.07</v>
+      </c>
+      <c r="AT102">
+        <v>2.99</v>
+      </c>
+      <c r="AU102">
+        <v>5</v>
+      </c>
+      <c r="AV102">
+        <v>2</v>
+      </c>
+      <c r="AW102">
+        <v>5</v>
+      </c>
+      <c r="AX102">
+        <v>3</v>
+      </c>
+      <c r="AY102">
+        <v>10</v>
+      </c>
+      <c r="AZ102">
+        <v>5</v>
+      </c>
+      <c r="BA102">
+        <v>2</v>
+      </c>
+      <c r="BB102">
+        <v>4</v>
+      </c>
+      <c r="BC102">
+        <v>6</v>
+      </c>
+      <c r="BD102">
+        <v>1.12</v>
+      </c>
+      <c r="BE102">
+        <v>12</v>
+      </c>
+      <c r="BF102">
+        <v>7</v>
+      </c>
+      <c r="BG102">
+        <v>1.36</v>
+      </c>
+      <c r="BH102">
+        <v>2.98</v>
+      </c>
+      <c r="BI102">
+        <v>1.62</v>
+      </c>
+      <c r="BJ102">
+        <v>2.22</v>
+      </c>
+      <c r="BK102">
+        <v>2.02</v>
+      </c>
+      <c r="BL102">
+        <v>1.74</v>
+      </c>
+      <c r="BM102">
+        <v>2.6</v>
+      </c>
+      <c r="BN102">
+        <v>1.46</v>
+      </c>
+      <c r="BO102">
+        <v>3.58</v>
+      </c>
+      <c r="BP102">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="205">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -467,6 +467,12 @@
   </si>
   <si>
     <t>['38', '74', '78']</t>
+  </si>
+  <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['9']</t>
   </si>
   <si>
     <t>['8', '61']</t>
@@ -984,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP102"/>
+  <dimension ref="A1:BP104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1524,10 +1530,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ3">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1858,7 +1864,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2064,7 +2070,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2142,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ6">
         <v>0.82</v>
@@ -2682,7 +2688,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2888,7 +2894,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3506,7 +3512,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3712,7 +3718,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3790,10 +3796,10 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ14">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR14">
         <v>1.27</v>
@@ -3918,7 +3924,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -3996,10 +4002,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR15">
         <v>0.6899999999999999</v>
@@ -4742,7 +4748,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4948,7 +4954,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5154,7 +5160,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5360,7 +5366,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5438,7 +5444,7 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ22">
         <v>0.82</v>
@@ -5566,7 +5572,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5850,10 +5856,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR24">
         <v>1.41</v>
@@ -6059,7 +6065,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ25">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR25">
         <v>1.8</v>
@@ -6184,7 +6190,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6390,7 +6396,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6596,7 +6602,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6802,7 +6808,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -6880,7 +6886,7 @@
         <v>2</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29">
         <v>1.7</v>
@@ -7295,7 +7301,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ31">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR31">
         <v>1.34</v>
@@ -7626,7 +7632,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7832,7 +7838,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -7910,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ34">
         <v>0.1</v>
@@ -8038,7 +8044,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8119,7 +8125,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR35">
         <v>1.65</v>
@@ -8943,7 +8949,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ39">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR39">
         <v>1.73</v>
@@ -9274,7 +9280,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9352,7 +9358,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ41">
         <v>0.82</v>
@@ -9480,7 +9486,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9561,7 +9567,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ42">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10098,7 +10104,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10382,7 +10388,7 @@
         <v>1.2</v>
       </c>
       <c r="AP46">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ46">
         <v>0.82</v>
@@ -10510,7 +10516,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10716,7 +10722,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10797,7 +10803,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR48">
         <v>1.2</v>
@@ -10922,7 +10928,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11128,7 +11134,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11540,7 +11546,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11746,7 +11752,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11824,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ53">
         <v>1.1</v>
@@ -12033,7 +12039,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ54">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12158,7 +12164,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12239,7 +12245,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR55">
         <v>1.97</v>
@@ -12442,7 +12448,7 @@
         <v>0.8</v>
       </c>
       <c r="AP56">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ56">
         <v>0.9</v>
@@ -12570,7 +12576,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12776,7 +12782,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13188,7 +13194,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13600,7 +13606,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13806,7 +13812,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -13884,7 +13890,7 @@
         <v>1.83</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ63">
         <v>1.2</v>
@@ -14012,7 +14018,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14090,7 +14096,7 @@
         <v>0.67</v>
       </c>
       <c r="AP64">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ64">
         <v>0.9</v>
@@ -14218,7 +14224,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14299,7 +14305,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ65">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14424,7 +14430,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14505,7 +14511,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ66">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
         <v>1.64</v>
@@ -14630,7 +14636,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14836,7 +14842,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15248,7 +15254,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15660,7 +15666,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15866,7 +15872,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -15947,7 +15953,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16278,7 +16284,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16562,7 +16568,7 @@
         <v>1.71</v>
       </c>
       <c r="AP76">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ76">
         <v>1.2</v>
@@ -16977,7 +16983,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ78">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -17180,7 +17186,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ79">
         <v>1.3</v>
@@ -17308,7 +17314,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17720,7 +17726,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17926,7 +17932,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18132,7 +18138,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18419,7 +18425,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -18544,7 +18550,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18622,7 +18628,7 @@
         <v>2</v>
       </c>
       <c r="AP86">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ86">
         <v>1.7</v>
@@ -18750,7 +18756,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18956,7 +18962,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19034,7 +19040,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ88">
         <v>1.1</v>
@@ -19162,7 +19168,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19243,7 +19249,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ89">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR89">
         <v>1.93</v>
@@ -19574,7 +19580,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19780,7 +19786,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -19986,7 +19992,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20064,10 +20070,10 @@
         <v>0.89</v>
       </c>
       <c r="AP93">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ93">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR93">
         <v>1.14</v>
@@ -20192,7 +20198,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20398,7 +20404,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20682,7 +20688,7 @@
         <v>0.78</v>
       </c>
       <c r="AP96">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ96">
         <v>0.82</v>
@@ -21016,7 +21022,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21428,7 +21434,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21634,7 +21640,7 @@
         <v>149</v>
       </c>
       <c r="P101" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21997,6 +22003,418 @@
       </c>
       <c r="BP102">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7451067</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F103">
+        <v>21</v>
+      </c>
+      <c r="G103" t="s">
+        <v>71</v>
+      </c>
+      <c r="H103" t="s">
+        <v>73</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>151</v>
+      </c>
+      <c r="P103" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q103">
+        <v>3.75</v>
+      </c>
+      <c r="R103">
+        <v>2</v>
+      </c>
+      <c r="S103">
+        <v>2.8</v>
+      </c>
+      <c r="T103">
+        <v>1.4</v>
+      </c>
+      <c r="U103">
+        <v>2.84</v>
+      </c>
+      <c r="V103">
+        <v>3.02</v>
+      </c>
+      <c r="W103">
+        <v>1.36</v>
+      </c>
+      <c r="X103">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y103">
+        <v>1.06</v>
+      </c>
+      <c r="Z103">
+        <v>3.25</v>
+      </c>
+      <c r="AA103">
+        <v>3.42</v>
+      </c>
+      <c r="AB103">
+        <v>2.14</v>
+      </c>
+      <c r="AC103">
+        <v>1.03</v>
+      </c>
+      <c r="AD103">
+        <v>9</v>
+      </c>
+      <c r="AE103">
+        <v>1.29</v>
+      </c>
+      <c r="AF103">
+        <v>3.3</v>
+      </c>
+      <c r="AG103">
+        <v>1.95</v>
+      </c>
+      <c r="AH103">
+        <v>1.75</v>
+      </c>
+      <c r="AI103">
+        <v>1.67</v>
+      </c>
+      <c r="AJ103">
+        <v>2.1</v>
+      </c>
+      <c r="AK103">
+        <v>1.67</v>
+      </c>
+      <c r="AL103">
+        <v>1.3</v>
+      </c>
+      <c r="AM103">
+        <v>1.31</v>
+      </c>
+      <c r="AN103">
+        <v>1.6</v>
+      </c>
+      <c r="AO103">
+        <v>1.33</v>
+      </c>
+      <c r="AP103">
+        <v>1.73</v>
+      </c>
+      <c r="AQ103">
+        <v>1.2</v>
+      </c>
+      <c r="AR103">
+        <v>1.14</v>
+      </c>
+      <c r="AS103">
+        <v>1.37</v>
+      </c>
+      <c r="AT103">
+        <v>2.51</v>
+      </c>
+      <c r="AU103">
+        <v>3</v>
+      </c>
+      <c r="AV103">
+        <v>5</v>
+      </c>
+      <c r="AW103">
+        <v>2</v>
+      </c>
+      <c r="AX103">
+        <v>3</v>
+      </c>
+      <c r="AY103">
+        <v>5</v>
+      </c>
+      <c r="AZ103">
+        <v>8</v>
+      </c>
+      <c r="BA103">
+        <v>2</v>
+      </c>
+      <c r="BB103">
+        <v>2</v>
+      </c>
+      <c r="BC103">
+        <v>4</v>
+      </c>
+      <c r="BD103">
+        <v>2.9</v>
+      </c>
+      <c r="BE103">
+        <v>8</v>
+      </c>
+      <c r="BF103">
+        <v>1.59</v>
+      </c>
+      <c r="BG103">
+        <v>1.32</v>
+      </c>
+      <c r="BH103">
+        <v>3.22</v>
+      </c>
+      <c r="BI103">
+        <v>1.56</v>
+      </c>
+      <c r="BJ103">
+        <v>2.33</v>
+      </c>
+      <c r="BK103">
+        <v>1.93</v>
+      </c>
+      <c r="BL103">
+        <v>1.82</v>
+      </c>
+      <c r="BM103">
+        <v>2.47</v>
+      </c>
+      <c r="BN103">
+        <v>1.51</v>
+      </c>
+      <c r="BO103">
+        <v>3.35</v>
+      </c>
+      <c r="BP103">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7451069</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45696.5625</v>
+      </c>
+      <c r="F104">
+        <v>21</v>
+      </c>
+      <c r="G104" t="s">
+        <v>74</v>
+      </c>
+      <c r="H104" t="s">
+        <v>78</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>1</v>
+      </c>
+      <c r="O104" t="s">
+        <v>152</v>
+      </c>
+      <c r="P104" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q104">
+        <v>2</v>
+      </c>
+      <c r="R104">
+        <v>2.1</v>
+      </c>
+      <c r="S104">
+        <v>6.5</v>
+      </c>
+      <c r="T104">
+        <v>1.42</v>
+      </c>
+      <c r="U104">
+        <v>2.75</v>
+      </c>
+      <c r="V104">
+        <v>3.15</v>
+      </c>
+      <c r="W104">
+        <v>1.33</v>
+      </c>
+      <c r="X104">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y104">
+        <v>1.04</v>
+      </c>
+      <c r="Z104">
+        <v>1.5</v>
+      </c>
+      <c r="AA104">
+        <v>3.92</v>
+      </c>
+      <c r="AB104">
+        <v>6.52</v>
+      </c>
+      <c r="AC104">
+        <v>1.05</v>
+      </c>
+      <c r="AD104">
+        <v>8</v>
+      </c>
+      <c r="AE104">
+        <v>1.3</v>
+      </c>
+      <c r="AF104">
+        <v>3.2</v>
+      </c>
+      <c r="AG104">
+        <v>2.1</v>
+      </c>
+      <c r="AH104">
+        <v>1.65</v>
+      </c>
+      <c r="AI104">
+        <v>2.2</v>
+      </c>
+      <c r="AJ104">
+        <v>1.62</v>
+      </c>
+      <c r="AK104">
+        <v>1.08</v>
+      </c>
+      <c r="AL104">
+        <v>1.22</v>
+      </c>
+      <c r="AM104">
+        <v>2.55</v>
+      </c>
+      <c r="AN104">
+        <v>2.4</v>
+      </c>
+      <c r="AO104">
+        <v>0.9</v>
+      </c>
+      <c r="AP104">
+        <v>2.45</v>
+      </c>
+      <c r="AQ104">
+        <v>0.82</v>
+      </c>
+      <c r="AR104">
+        <v>1.55</v>
+      </c>
+      <c r="AS104">
+        <v>1.4</v>
+      </c>
+      <c r="AT104">
+        <v>2.95</v>
+      </c>
+      <c r="AU104">
+        <v>2</v>
+      </c>
+      <c r="AV104">
+        <v>2</v>
+      </c>
+      <c r="AW104">
+        <v>3</v>
+      </c>
+      <c r="AX104">
+        <v>5</v>
+      </c>
+      <c r="AY104">
+        <v>5</v>
+      </c>
+      <c r="AZ104">
+        <v>7</v>
+      </c>
+      <c r="BA104">
+        <v>2</v>
+      </c>
+      <c r="BB104">
+        <v>3</v>
+      </c>
+      <c r="BC104">
+        <v>5</v>
+      </c>
+      <c r="BD104">
+        <v>1.45</v>
+      </c>
+      <c r="BE104">
+        <v>8.5</v>
+      </c>
+      <c r="BF104">
+        <v>3.29</v>
+      </c>
+      <c r="BG104">
+        <v>1.4</v>
+      </c>
+      <c r="BH104">
+        <v>2.82</v>
+      </c>
+      <c r="BI104">
+        <v>1.68</v>
+      </c>
+      <c r="BJ104">
+        <v>2.11</v>
+      </c>
+      <c r="BK104">
+        <v>2.11</v>
+      </c>
+      <c r="BL104">
+        <v>1.68</v>
+      </c>
+      <c r="BM104">
+        <v>2.75</v>
+      </c>
+      <c r="BN104">
+        <v>1.42</v>
+      </c>
+      <c r="BO104">
+        <v>3.82</v>
+      </c>
+      <c r="BP104">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="208">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,6 +475,9 @@
     <t>['9']</t>
   </si>
   <si>
+    <t>['39', '90+2']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -629,6 +632,12 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['45']</t>
   </si>
 </sst>
 </file>
@@ -990,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP104"/>
+  <dimension ref="A1:BP106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1327,7 +1336,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ2">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1736,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1864,7 +1873,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2070,7 +2079,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2688,7 +2697,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2894,7 +2903,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3512,7 +3521,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3590,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ13">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3718,7 +3727,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3924,7 +3933,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4208,10 +4217,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR16">
         <v>1.93</v>
@@ -4748,7 +4757,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4954,7 +4963,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5160,7 +5169,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5366,7 +5375,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5572,7 +5581,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5650,10 +5659,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ23">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -6190,7 +6199,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6268,7 +6277,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>1.2</v>
@@ -6396,7 +6405,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6602,7 +6611,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6683,7 +6692,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ28">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>1.45</v>
@@ -6808,7 +6817,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7507,7 +7516,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ32">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR32">
         <v>1.2</v>
@@ -7632,7 +7641,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7710,7 +7719,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ33">
         <v>1.2</v>
@@ -7838,7 +7847,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8044,7 +8053,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8328,7 +8337,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>0.82</v>
@@ -8537,7 +8546,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ37">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR37">
         <v>1.04</v>
@@ -8743,7 +8752,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ38">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.94</v>
@@ -9152,7 +9161,7 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>1.3</v>
@@ -9280,7 +9289,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9486,7 +9495,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9976,7 +9985,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ44">
         <v>1.7</v>
@@ -10104,7 +10113,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10516,7 +10525,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10722,7 +10731,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10928,7 +10937,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11134,7 +11143,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11212,7 +11221,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ50">
         <v>1.3</v>
@@ -11546,7 +11555,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11624,7 +11633,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ52">
         <v>0.82</v>
@@ -11752,7 +11761,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11833,7 +11842,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ53">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12036,7 +12045,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
         <v>0.82</v>
@@ -12164,7 +12173,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12451,7 +12460,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ56">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR56">
         <v>1.17</v>
@@ -12576,7 +12585,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12782,7 +12791,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13194,7 +13203,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13606,7 +13615,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13687,7 +13696,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ62">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>0.93</v>
@@ -13812,7 +13821,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14018,7 +14027,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14099,7 +14108,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ64">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14224,7 +14233,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14302,7 +14311,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ65">
         <v>0.82</v>
@@ -14430,7 +14439,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14508,7 +14517,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>1.2</v>
@@ -14636,7 +14645,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14842,7 +14851,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14923,7 +14932,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ68">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.39</v>
@@ -15254,7 +15263,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15666,7 +15675,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15872,7 +15881,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -15950,7 +15959,7 @@
         <v>1.57</v>
       </c>
       <c r="AP73">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ73">
         <v>1.2</v>
@@ -16156,7 +16165,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
         <v>0.1</v>
@@ -16284,7 +16293,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16365,7 +16374,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ75">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR75">
         <v>1.54</v>
@@ -17314,7 +17323,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17601,7 +17610,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ81">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -17726,7 +17735,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17804,7 +17813,7 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ82">
         <v>0.1</v>
@@ -17932,7 +17941,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18138,7 +18147,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18550,7 +18559,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18756,7 +18765,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18837,7 +18846,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ87">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR87">
         <v>1.57</v>
@@ -18962,7 +18971,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19043,7 +19052,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ88">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19168,7 +19177,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19452,7 +19461,7 @@
         <v>0.88</v>
       </c>
       <c r="AP90">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>0.82</v>
@@ -19580,7 +19589,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19786,7 +19795,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -19992,7 +20001,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20198,7 +20207,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20279,7 +20288,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ94">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR94">
         <v>1.89</v>
@@ -20404,7 +20413,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20482,10 +20491,10 @@
         <v>1.22</v>
       </c>
       <c r="AP95">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -21022,7 +21031,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21434,7 +21443,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21640,7 +21649,7 @@
         <v>149</v>
       </c>
       <c r="P101" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22415,6 +22424,418 @@
       </c>
       <c r="BP104">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7451068</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45697.45833333334</v>
+      </c>
+      <c r="F105">
+        <v>21</v>
+      </c>
+      <c r="G105" t="s">
+        <v>72</v>
+      </c>
+      <c r="H105" t="s">
+        <v>76</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="s">
+        <v>81</v>
+      </c>
+      <c r="P105" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q105">
+        <v>1.93</v>
+      </c>
+      <c r="R105">
+        <v>2.25</v>
+      </c>
+      <c r="S105">
+        <v>6</v>
+      </c>
+      <c r="T105">
+        <v>1.35</v>
+      </c>
+      <c r="U105">
+        <v>2.9</v>
+      </c>
+      <c r="V105">
+        <v>2.8</v>
+      </c>
+      <c r="W105">
+        <v>1.37</v>
+      </c>
+      <c r="X105">
+        <v>6.5</v>
+      </c>
+      <c r="Y105">
+        <v>1.08</v>
+      </c>
+      <c r="Z105">
+        <v>1.47</v>
+      </c>
+      <c r="AA105">
+        <v>4.1</v>
+      </c>
+      <c r="AB105">
+        <v>6.2</v>
+      </c>
+      <c r="AC105">
+        <v>1.02</v>
+      </c>
+      <c r="AD105">
+        <v>9.5</v>
+      </c>
+      <c r="AE105">
+        <v>1.27</v>
+      </c>
+      <c r="AF105">
+        <v>3.4</v>
+      </c>
+      <c r="AG105">
+        <v>1.93</v>
+      </c>
+      <c r="AH105">
+        <v>1.77</v>
+      </c>
+      <c r="AI105">
+        <v>1.95</v>
+      </c>
+      <c r="AJ105">
+        <v>1.75</v>
+      </c>
+      <c r="AK105">
+        <v>1.06</v>
+      </c>
+      <c r="AL105">
+        <v>1.22</v>
+      </c>
+      <c r="AM105">
+        <v>2.5</v>
+      </c>
+      <c r="AN105">
+        <v>2.2</v>
+      </c>
+      <c r="AO105">
+        <v>0.9</v>
+      </c>
+      <c r="AP105">
+        <v>2</v>
+      </c>
+      <c r="AQ105">
+        <v>1.09</v>
+      </c>
+      <c r="AR105">
+        <v>1.66</v>
+      </c>
+      <c r="AS105">
+        <v>1.07</v>
+      </c>
+      <c r="AT105">
+        <v>2.73</v>
+      </c>
+      <c r="AU105">
+        <v>5</v>
+      </c>
+      <c r="AV105">
+        <v>2</v>
+      </c>
+      <c r="AW105">
+        <v>9</v>
+      </c>
+      <c r="AX105">
+        <v>3</v>
+      </c>
+      <c r="AY105">
+        <v>14</v>
+      </c>
+      <c r="AZ105">
+        <v>5</v>
+      </c>
+      <c r="BA105">
+        <v>5</v>
+      </c>
+      <c r="BB105">
+        <v>1</v>
+      </c>
+      <c r="BC105">
+        <v>6</v>
+      </c>
+      <c r="BD105">
+        <v>1.37</v>
+      </c>
+      <c r="BE105">
+        <v>9</v>
+      </c>
+      <c r="BF105">
+        <v>3.83</v>
+      </c>
+      <c r="BG105">
+        <v>1.44</v>
+      </c>
+      <c r="BH105">
+        <v>2.67</v>
+      </c>
+      <c r="BI105">
+        <v>1.74</v>
+      </c>
+      <c r="BJ105">
+        <v>2.02</v>
+      </c>
+      <c r="BK105">
+        <v>2.22</v>
+      </c>
+      <c r="BL105">
+        <v>1.62</v>
+      </c>
+      <c r="BM105">
+        <v>2.92</v>
+      </c>
+      <c r="BN105">
+        <v>1.38</v>
+      </c>
+      <c r="BO105">
+        <v>4.1</v>
+      </c>
+      <c r="BP105">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7451070</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45697.57291666666</v>
+      </c>
+      <c r="F106">
+        <v>21</v>
+      </c>
+      <c r="G106" t="s">
+        <v>79</v>
+      </c>
+      <c r="H106" t="s">
+        <v>77</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="K106">
+        <v>2</v>
+      </c>
+      <c r="L106">
+        <v>2</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106">
+        <v>3</v>
+      </c>
+      <c r="O106" t="s">
+        <v>153</v>
+      </c>
+      <c r="P106" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q106">
+        <v>2.88</v>
+      </c>
+      <c r="R106">
+        <v>2.2</v>
+      </c>
+      <c r="S106">
+        <v>3.6</v>
+      </c>
+      <c r="T106">
+        <v>1.36</v>
+      </c>
+      <c r="U106">
+        <v>3</v>
+      </c>
+      <c r="V106">
+        <v>2.75</v>
+      </c>
+      <c r="W106">
+        <v>1.4</v>
+      </c>
+      <c r="X106">
+        <v>7</v>
+      </c>
+      <c r="Y106">
+        <v>1.1</v>
+      </c>
+      <c r="Z106">
+        <v>2.05</v>
+      </c>
+      <c r="AA106">
+        <v>3.5</v>
+      </c>
+      <c r="AB106">
+        <v>3.2</v>
+      </c>
+      <c r="AC106">
+        <v>1.02</v>
+      </c>
+      <c r="AD106">
+        <v>10</v>
+      </c>
+      <c r="AE106">
+        <v>1.2</v>
+      </c>
+      <c r="AF106">
+        <v>4</v>
+      </c>
+      <c r="AG106">
+        <v>1.79</v>
+      </c>
+      <c r="AH106">
+        <v>1.92</v>
+      </c>
+      <c r="AI106">
+        <v>1.67</v>
+      </c>
+      <c r="AJ106">
+        <v>2.1</v>
+      </c>
+      <c r="AK106">
+        <v>1.25</v>
+      </c>
+      <c r="AL106">
+        <v>1.3</v>
+      </c>
+      <c r="AM106">
+        <v>1.67</v>
+      </c>
+      <c r="AN106">
+        <v>1.44</v>
+      </c>
+      <c r="AO106">
+        <v>1.1</v>
+      </c>
+      <c r="AP106">
+        <v>1.6</v>
+      </c>
+      <c r="AQ106">
+        <v>1</v>
+      </c>
+      <c r="AR106">
+        <v>1.58</v>
+      </c>
+      <c r="AS106">
+        <v>1.55</v>
+      </c>
+      <c r="AT106">
+        <v>3.13</v>
+      </c>
+      <c r="AU106">
+        <v>4</v>
+      </c>
+      <c r="AV106">
+        <v>7</v>
+      </c>
+      <c r="AW106">
+        <v>9</v>
+      </c>
+      <c r="AX106">
+        <v>5</v>
+      </c>
+      <c r="AY106">
+        <v>13</v>
+      </c>
+      <c r="AZ106">
+        <v>12</v>
+      </c>
+      <c r="BA106">
+        <v>0</v>
+      </c>
+      <c r="BB106">
+        <v>4</v>
+      </c>
+      <c r="BC106">
+        <v>4</v>
+      </c>
+      <c r="BD106">
+        <v>1.91</v>
+      </c>
+      <c r="BE106">
+        <v>8</v>
+      </c>
+      <c r="BF106">
+        <v>2.1</v>
+      </c>
+      <c r="BG106">
+        <v>1.29</v>
+      </c>
+      <c r="BH106">
+        <v>3.35</v>
+      </c>
+      <c r="BI106">
+        <v>1.53</v>
+      </c>
+      <c r="BJ106">
+        <v>2.41</v>
+      </c>
+      <c r="BK106">
+        <v>1.87</v>
+      </c>
+      <c r="BL106">
+        <v>1.87</v>
+      </c>
+      <c r="BM106">
+        <v>2.38</v>
+      </c>
+      <c r="BN106">
+        <v>1.54</v>
+      </c>
+      <c r="BO106">
+        <v>3.2</v>
+      </c>
+      <c r="BP106">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="210">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -478,6 +478,9 @@
     <t>['39', '90+2']</t>
   </si>
   <si>
+    <t>['59']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -638,6 +641,9 @@
   </si>
   <si>
     <t>['45']</t>
+  </si>
+  <si>
+    <t>['52', '71']</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP106"/>
+  <dimension ref="A1:BP107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1748,7 +1754,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1873,7 +1879,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2079,7 +2085,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2363,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ7">
         <v>0.82</v>
@@ -2697,7 +2703,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2903,7 +2909,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3521,7 +3527,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3602,7 +3608,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3727,7 +3733,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3933,7 +3939,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4757,7 +4763,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4963,7 +4969,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5169,7 +5175,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5375,7 +5381,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5581,7 +5587,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6199,7 +6205,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6405,7 +6411,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6611,7 +6617,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6692,7 +6698,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
         <v>1.45</v>
@@ -6817,7 +6823,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7307,7 +7313,7 @@
         <v>1.33</v>
       </c>
       <c r="AP31">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ31">
         <v>0.82</v>
@@ -7641,7 +7647,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7847,7 +7853,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8053,7 +8059,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8543,7 +8549,7 @@
         <v>0.75</v>
       </c>
       <c r="AP37">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ37">
         <v>1.09</v>
@@ -8752,7 +8758,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ38">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR38">
         <v>1.94</v>
@@ -9289,7 +9295,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9495,7 +9501,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10113,7 +10119,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10525,7 +10531,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10731,7 +10737,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10809,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ48">
         <v>1.2</v>
@@ -10937,7 +10943,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11143,7 +11149,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11555,7 +11561,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11761,7 +11767,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11842,7 +11848,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12173,7 +12179,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12585,7 +12591,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12663,7 +12669,7 @@
         <v>1.6</v>
       </c>
       <c r="AP57">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ57">
         <v>1.2</v>
@@ -12791,7 +12797,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13203,7 +13209,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13615,7 +13621,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13693,10 +13699,10 @@
         <v>0.8</v>
       </c>
       <c r="AP62">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR62">
         <v>0.93</v>
@@ -13821,7 +13827,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14027,7 +14033,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14233,7 +14239,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14439,7 +14445,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14645,7 +14651,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14851,7 +14857,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14932,7 +14938,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR68">
         <v>1.39</v>
@@ -15263,7 +15269,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15547,7 +15553,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ71">
         <v>0.1</v>
@@ -15675,7 +15681,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15881,7 +15887,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16293,7 +16299,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -17323,7 +17329,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17401,7 +17407,7 @@
         <v>1.86</v>
       </c>
       <c r="AP80">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ80">
         <v>1.7</v>
@@ -17610,7 +17616,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -17735,7 +17741,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17941,7 +17947,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18147,7 +18153,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18559,7 +18565,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18765,7 +18771,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18971,7 +18977,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19052,7 +19058,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19177,7 +19183,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19589,7 +19595,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19667,7 +19673,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ91">
         <v>1.3</v>
@@ -19795,7 +19801,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20001,7 +20007,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20207,7 +20213,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20413,7 +20419,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20494,7 +20500,7 @@
         <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -21031,7 +21037,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21109,7 +21115,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AQ98">
         <v>0.82</v>
@@ -21443,7 +21449,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21649,7 +21655,7 @@
         <v>149</v>
       </c>
       <c r="P101" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22473,7 +22479,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22679,7 +22685,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22760,7 +22766,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ106">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR106">
         <v>1.58</v>
@@ -22836,6 +22842,212 @@
       </c>
       <c r="BP106">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7451071</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45702.58333333334</v>
+      </c>
+      <c r="F107">
+        <v>22</v>
+      </c>
+      <c r="G107" t="s">
+        <v>75</v>
+      </c>
+      <c r="H107" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>2</v>
+      </c>
+      <c r="N107">
+        <v>3</v>
+      </c>
+      <c r="O107" t="s">
+        <v>154</v>
+      </c>
+      <c r="P107" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q107">
+        <v>3.5</v>
+      </c>
+      <c r="R107">
+        <v>2</v>
+      </c>
+      <c r="S107">
+        <v>2.95</v>
+      </c>
+      <c r="T107">
+        <v>1.43</v>
+      </c>
+      <c r="U107">
+        <v>2.6</v>
+      </c>
+      <c r="V107">
+        <v>2.95</v>
+      </c>
+      <c r="W107">
+        <v>1.34</v>
+      </c>
+      <c r="X107">
+        <v>8</v>
+      </c>
+      <c r="Y107">
+        <v>1.07</v>
+      </c>
+      <c r="Z107">
+        <v>2.85</v>
+      </c>
+      <c r="AA107">
+        <v>3.05</v>
+      </c>
+      <c r="AB107">
+        <v>2.33</v>
+      </c>
+      <c r="AC107">
+        <v>1.06</v>
+      </c>
+      <c r="AD107">
+        <v>8</v>
+      </c>
+      <c r="AE107">
+        <v>1.35</v>
+      </c>
+      <c r="AF107">
+        <v>2.9</v>
+      </c>
+      <c r="AG107">
+        <v>2.07</v>
+      </c>
+      <c r="AH107">
+        <v>1.7</v>
+      </c>
+      <c r="AI107">
+        <v>1.83</v>
+      </c>
+      <c r="AJ107">
+        <v>1.85</v>
+      </c>
+      <c r="AK107">
+        <v>1.55</v>
+      </c>
+      <c r="AL107">
+        <v>1.32</v>
+      </c>
+      <c r="AM107">
+        <v>1.38</v>
+      </c>
+      <c r="AN107">
+        <v>0.9</v>
+      </c>
+      <c r="AO107">
+        <v>1</v>
+      </c>
+      <c r="AP107">
+        <v>0.82</v>
+      </c>
+      <c r="AQ107">
+        <v>1.17</v>
+      </c>
+      <c r="AR107">
+        <v>1.16</v>
+      </c>
+      <c r="AS107">
+        <v>1.56</v>
+      </c>
+      <c r="AT107">
+        <v>2.72</v>
+      </c>
+      <c r="AU107">
+        <v>4</v>
+      </c>
+      <c r="AV107">
+        <v>7</v>
+      </c>
+      <c r="AW107">
+        <v>3</v>
+      </c>
+      <c r="AX107">
+        <v>10</v>
+      </c>
+      <c r="AY107">
+        <v>7</v>
+      </c>
+      <c r="AZ107">
+        <v>17</v>
+      </c>
+      <c r="BA107">
+        <v>7</v>
+      </c>
+      <c r="BB107">
+        <v>7</v>
+      </c>
+      <c r="BC107">
+        <v>14</v>
+      </c>
+      <c r="BD107">
+        <v>2.39</v>
+      </c>
+      <c r="BE107">
+        <v>8</v>
+      </c>
+      <c r="BF107">
+        <v>1.82</v>
+      </c>
+      <c r="BG107">
+        <v>1.31</v>
+      </c>
+      <c r="BH107">
+        <v>3.15</v>
+      </c>
+      <c r="BI107">
+        <v>1.56</v>
+      </c>
+      <c r="BJ107">
+        <v>2.33</v>
+      </c>
+      <c r="BK107">
+        <v>1.93</v>
+      </c>
+      <c r="BL107">
+        <v>1.82</v>
+      </c>
+      <c r="BM107">
+        <v>2.43</v>
+      </c>
+      <c r="BN107">
+        <v>1.49</v>
+      </c>
+      <c r="BO107">
+        <v>3.22</v>
+      </c>
+      <c r="BP107">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -481,6 +481,12 @@
     <t>['59']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['33', '75', '90+6']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -644,6 +650,9 @@
   </si>
   <si>
     <t>['52', '71']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP107"/>
+  <dimension ref="A1:BP109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1339,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ2">
         <v>1.09</v>
@@ -1879,7 +1888,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2085,7 +2094,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2575,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ8">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2703,7 +2712,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2784,7 +2793,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ9">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2909,7 +2918,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3399,7 +3408,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ12">
         <v>0.82</v>
@@ -3527,7 +3536,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3733,7 +3742,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3939,7 +3948,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4763,7 +4772,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4841,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ19">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -4969,7 +4978,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5047,10 +5056,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR20">
         <v>1.92</v>
@@ -5175,7 +5184,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5381,7 +5390,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5587,7 +5596,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6205,7 +6214,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6411,7 +6420,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6489,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ27">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR27">
         <v>1.84</v>
@@ -6617,7 +6626,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6695,7 +6704,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ28">
         <v>1.17</v>
@@ -6823,7 +6832,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7647,7 +7656,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7853,7 +7862,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -7934,7 +7943,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ34">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR34">
         <v>1.39</v>
@@ -8059,7 +8068,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8755,7 +8764,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ38">
         <v>1.17</v>
@@ -9170,7 +9179,7 @@
         <v>2</v>
       </c>
       <c r="AQ40">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR40">
         <v>1.7</v>
@@ -9295,7 +9304,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9501,7 +9510,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9579,7 +9588,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ42">
         <v>1.2</v>
@@ -9788,7 +9797,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ43">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR43">
         <v>1.56</v>
@@ -10119,7 +10128,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10531,7 +10540,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10737,7 +10746,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10943,7 +10952,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11021,7 +11030,7 @@
         <v>1.75</v>
       </c>
       <c r="AP49">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ49">
         <v>1.2</v>
@@ -11149,7 +11158,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11230,7 +11239,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ50">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR50">
         <v>1.52</v>
@@ -11436,7 +11445,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ51">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR51">
         <v>1.18</v>
@@ -11561,7 +11570,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11767,7 +11776,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12179,7 +12188,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12257,7 +12266,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ55">
         <v>1.2</v>
@@ -12591,7 +12600,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12797,7 +12806,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13084,7 +13093,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ59">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13209,7 +13218,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13287,7 +13296,7 @@
         <v>1.8</v>
       </c>
       <c r="AP60">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ60">
         <v>1.7</v>
@@ -13496,7 +13505,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ61">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR61">
         <v>1.34</v>
@@ -13621,7 +13630,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13827,7 +13836,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14033,7 +14042,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14239,7 +14248,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14445,7 +14454,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14651,7 +14660,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14729,7 +14738,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ67">
         <v>0.82</v>
@@ -14857,7 +14866,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15141,7 +15150,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ69">
         <v>1.7</v>
@@ -15269,7 +15278,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15350,7 +15359,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ70">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR70">
         <v>1.61</v>
@@ -15556,7 +15565,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ71">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR71">
         <v>0.93</v>
@@ -15681,7 +15690,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15887,7 +15896,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16174,7 +16183,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -16299,7 +16308,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16789,7 +16798,7 @@
         <v>0.86</v>
       </c>
       <c r="AP77">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ77">
         <v>0.82</v>
@@ -16995,7 +17004,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ78">
         <v>0.82</v>
@@ -17204,7 +17213,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ79">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR79">
         <v>1.09</v>
@@ -17329,7 +17338,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17741,7 +17750,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17822,7 +17831,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ82">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR82">
         <v>1.53</v>
@@ -17947,7 +17956,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18153,7 +18162,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18231,7 +18240,7 @@
         <v>0.88</v>
       </c>
       <c r="AP84">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ84">
         <v>0.82</v>
@@ -18565,7 +18574,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18771,7 +18780,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18977,7 +18986,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19183,7 +19192,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19261,7 +19270,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ89">
         <v>0.82</v>
@@ -19595,7 +19604,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19676,7 +19685,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ91">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR91">
         <v>1.08</v>
@@ -19801,7 +19810,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20007,7 +20016,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20213,7 +20222,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20291,7 +20300,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ94">
         <v>1.09</v>
@@ -20419,7 +20428,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20909,10 +20918,10 @@
         <v>0</v>
       </c>
       <c r="AP97">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ97">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AR97">
         <v>1.22</v>
@@ -21037,7 +21046,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21449,7 +21458,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21530,7 +21539,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ100">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR100">
         <v>1.46</v>
@@ -21655,7 +21664,7 @@
         <v>149</v>
       </c>
       <c r="P101" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21939,7 +21948,7 @@
         <v>0.9</v>
       </c>
       <c r="AP102">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ102">
         <v>0.82</v>
@@ -22479,7 +22488,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22685,7 +22694,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22891,7 +22900,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23047,6 +23056,418 @@
         <v>3.22</v>
       </c>
       <c r="BP107">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7451073</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F108">
+        <v>22</v>
+      </c>
+      <c r="G108" t="s">
+        <v>76</v>
+      </c>
+      <c r="H108" t="s">
+        <v>74</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>2</v>
+      </c>
+      <c r="O108" t="s">
+        <v>155</v>
+      </c>
+      <c r="P108" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q108">
+        <v>4.7</v>
+      </c>
+      <c r="R108">
+        <v>2.1</v>
+      </c>
+      <c r="S108">
+        <v>2.5</v>
+      </c>
+      <c r="T108">
+        <v>1.46</v>
+      </c>
+      <c r="U108">
+        <v>2.55</v>
+      </c>
+      <c r="V108">
+        <v>3</v>
+      </c>
+      <c r="W108">
+        <v>1.34</v>
+      </c>
+      <c r="X108">
+        <v>8</v>
+      </c>
+      <c r="Y108">
+        <v>1.03</v>
+      </c>
+      <c r="Z108">
+        <v>3.9</v>
+      </c>
+      <c r="AA108">
+        <v>3.15</v>
+      </c>
+      <c r="AB108">
+        <v>1.88</v>
+      </c>
+      <c r="AC108">
+        <v>1.05</v>
+      </c>
+      <c r="AD108">
+        <v>8</v>
+      </c>
+      <c r="AE108">
+        <v>1.36</v>
+      </c>
+      <c r="AF108">
+        <v>2.85</v>
+      </c>
+      <c r="AG108">
+        <v>2.12</v>
+      </c>
+      <c r="AH108">
+        <v>1.67</v>
+      </c>
+      <c r="AI108">
+        <v>1.93</v>
+      </c>
+      <c r="AJ108">
+        <v>1.79</v>
+      </c>
+      <c r="AK108">
+        <v>1.83</v>
+      </c>
+      <c r="AL108">
+        <v>1.29</v>
+      </c>
+      <c r="AM108">
+        <v>1.23</v>
+      </c>
+      <c r="AN108">
+        <v>1.1</v>
+      </c>
+      <c r="AO108">
+        <v>1.3</v>
+      </c>
+      <c r="AP108">
+        <v>1.09</v>
+      </c>
+      <c r="AQ108">
+        <v>1.27</v>
+      </c>
+      <c r="AR108">
+        <v>1.28</v>
+      </c>
+      <c r="AS108">
+        <v>1.47</v>
+      </c>
+      <c r="AT108">
+        <v>2.75</v>
+      </c>
+      <c r="AU108">
+        <v>3</v>
+      </c>
+      <c r="AV108">
+        <v>3</v>
+      </c>
+      <c r="AW108">
+        <v>5</v>
+      </c>
+      <c r="AX108">
+        <v>9</v>
+      </c>
+      <c r="AY108">
+        <v>8</v>
+      </c>
+      <c r="AZ108">
+        <v>12</v>
+      </c>
+      <c r="BA108">
+        <v>2</v>
+      </c>
+      <c r="BB108">
+        <v>7</v>
+      </c>
+      <c r="BC108">
+        <v>9</v>
+      </c>
+      <c r="BD108">
+        <v>2.53</v>
+      </c>
+      <c r="BE108">
+        <v>7.5</v>
+      </c>
+      <c r="BF108">
+        <v>1.75</v>
+      </c>
+      <c r="BG108">
+        <v>1.5</v>
+      </c>
+      <c r="BH108">
+        <v>2.41</v>
+      </c>
+      <c r="BI108">
+        <v>1.87</v>
+      </c>
+      <c r="BJ108">
+        <v>1.87</v>
+      </c>
+      <c r="BK108">
+        <v>2.42</v>
+      </c>
+      <c r="BL108">
+        <v>1.53</v>
+      </c>
+      <c r="BM108">
+        <v>3.25</v>
+      </c>
+      <c r="BN108">
+        <v>1.29</v>
+      </c>
+      <c r="BO108">
+        <v>4.4</v>
+      </c>
+      <c r="BP108">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7451075</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45703.5625</v>
+      </c>
+      <c r="F109">
+        <v>22</v>
+      </c>
+      <c r="G109" t="s">
+        <v>70</v>
+      </c>
+      <c r="H109" t="s">
+        <v>71</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>2</v>
+      </c>
+      <c r="L109">
+        <v>3</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>4</v>
+      </c>
+      <c r="O109" t="s">
+        <v>156</v>
+      </c>
+      <c r="P109" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q109">
+        <v>1.56</v>
+      </c>
+      <c r="R109">
+        <v>2.9</v>
+      </c>
+      <c r="S109">
+        <v>10</v>
+      </c>
+      <c r="T109">
+        <v>1.25</v>
+      </c>
+      <c r="U109">
+        <v>3.6</v>
+      </c>
+      <c r="V109">
+        <v>2.18</v>
+      </c>
+      <c r="W109">
+        <v>1.62</v>
+      </c>
+      <c r="X109">
+        <v>4.75</v>
+      </c>
+      <c r="Y109">
+        <v>1.15</v>
+      </c>
+      <c r="Z109">
+        <v>1.2</v>
+      </c>
+      <c r="AA109">
+        <v>6</v>
+      </c>
+      <c r="AB109">
+        <v>11</v>
+      </c>
+      <c r="AC109">
+        <v>1.01</v>
+      </c>
+      <c r="AD109">
+        <v>13</v>
+      </c>
+      <c r="AE109">
+        <v>1.17</v>
+      </c>
+      <c r="AF109">
+        <v>4.5</v>
+      </c>
+      <c r="AG109">
+        <v>1.55</v>
+      </c>
+      <c r="AH109">
+        <v>2.35</v>
+      </c>
+      <c r="AI109">
+        <v>2.19</v>
+      </c>
+      <c r="AJ109">
+        <v>1.6</v>
+      </c>
+      <c r="AK109">
+        <v>1.04</v>
+      </c>
+      <c r="AL109">
+        <v>1.09</v>
+      </c>
+      <c r="AM109">
+        <v>4</v>
+      </c>
+      <c r="AN109">
+        <v>2.09</v>
+      </c>
+      <c r="AO109">
+        <v>0.1</v>
+      </c>
+      <c r="AP109">
+        <v>2.17</v>
+      </c>
+      <c r="AQ109">
+        <v>0.09</v>
+      </c>
+      <c r="AR109">
+        <v>1.9</v>
+      </c>
+      <c r="AS109">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT109">
+        <v>2.84</v>
+      </c>
+      <c r="AU109">
+        <v>9</v>
+      </c>
+      <c r="AV109">
+        <v>2</v>
+      </c>
+      <c r="AW109">
+        <v>5</v>
+      </c>
+      <c r="AX109">
+        <v>1</v>
+      </c>
+      <c r="AY109">
+        <v>14</v>
+      </c>
+      <c r="AZ109">
+        <v>3</v>
+      </c>
+      <c r="BA109">
+        <v>2</v>
+      </c>
+      <c r="BB109">
+        <v>0</v>
+      </c>
+      <c r="BC109">
+        <v>2</v>
+      </c>
+      <c r="BD109">
+        <v>1.18</v>
+      </c>
+      <c r="BE109">
+        <v>11</v>
+      </c>
+      <c r="BF109">
+        <v>6.16</v>
+      </c>
+      <c r="BG109">
+        <v>1.31</v>
+      </c>
+      <c r="BH109">
+        <v>3.15</v>
+      </c>
+      <c r="BI109">
+        <v>1.56</v>
+      </c>
+      <c r="BJ109">
+        <v>2.33</v>
+      </c>
+      <c r="BK109">
+        <v>1.93</v>
+      </c>
+      <c r="BL109">
+        <v>1.82</v>
+      </c>
+      <c r="BM109">
+        <v>2.43</v>
+      </c>
+      <c r="BN109">
+        <v>1.49</v>
+      </c>
+      <c r="BO109">
+        <v>3.22</v>
+      </c>
+      <c r="BP109">
         <v>1.28</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -654,6 +654,9 @@
   <si>
     <t>['29']</t>
   </si>
+  <si>
+    <t>['15', '37']</t>
+  </si>
 </sst>
 </file>
 
@@ -1014,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1966,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>0.82</v>
@@ -2175,7 +2178,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ6">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2381,7 +2384,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ7">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2996,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>1.2</v>
@@ -3202,10 +3205,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ11">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4644,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ18">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0.8100000000000001</v>
@@ -5262,10 +5265,10 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR21">
         <v>2.05</v>
@@ -6913,7 +6916,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ29">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR29">
         <v>1.12</v>
@@ -7116,10 +7119,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>1.82</v>
@@ -7528,7 +7531,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ32">
         <v>1.09</v>
@@ -8970,7 +8973,7 @@
         <v>1.25</v>
       </c>
       <c r="AP39">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>0.82</v>
@@ -9385,7 +9388,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ41">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -10003,7 +10006,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ44">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10206,7 +10209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ45">
         <v>1.2</v>
@@ -10621,7 +10624,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ47">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR47">
         <v>1.56</v>
@@ -11442,7 +11445,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ51">
         <v>0.09</v>
@@ -12887,7 +12890,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ58">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>1.49</v>
@@ -13090,7 +13093,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ59">
         <v>0.09</v>
@@ -13299,7 +13302,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ60">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR60">
         <v>1.28</v>
@@ -13502,7 +13505,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ61">
         <v>1.27</v>
@@ -14741,7 +14744,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ67">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.18</v>
@@ -14944,7 +14947,7 @@
         <v>1.17</v>
       </c>
       <c r="AP68">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ68">
         <v>1.17</v>
@@ -15153,7 +15156,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ69">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR69">
         <v>1.96</v>
@@ -15356,7 +15359,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ70">
         <v>1.27</v>
@@ -15768,7 +15771,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ72">
         <v>0.82</v>
@@ -16801,7 +16804,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ77">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.79</v>
@@ -17419,7 +17422,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ80">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -17622,7 +17625,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>1.17</v>
@@ -18446,7 +18449,7 @@
         <v>1.38</v>
       </c>
       <c r="AP85">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ85">
         <v>1.2</v>
@@ -18655,7 +18658,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ86">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR86">
         <v>1.59</v>
@@ -18858,7 +18861,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87">
         <v>1.09</v>
@@ -19479,7 +19482,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.63</v>
@@ -19888,7 +19891,7 @@
         <v>0.89</v>
       </c>
       <c r="AP92">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ92">
         <v>0.82</v>
@@ -20715,7 +20718,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ96">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -21127,7 +21130,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ98">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.13</v>
@@ -21330,10 +21333,10 @@
         <v>1.89</v>
       </c>
       <c r="AP99">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ99">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21742,7 +21745,7 @@
         <v>1.33</v>
       </c>
       <c r="AP101">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ101">
         <v>1.2</v>
@@ -23469,6 +23472,418 @@
       </c>
       <c r="BP109">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7451072</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F110">
+        <v>22</v>
+      </c>
+      <c r="G110" t="s">
+        <v>78</v>
+      </c>
+      <c r="H110" t="s">
+        <v>79</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>81</v>
+      </c>
+      <c r="P110" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q110">
+        <v>2.75</v>
+      </c>
+      <c r="R110">
+        <v>2.07</v>
+      </c>
+      <c r="S110">
+        <v>4.1</v>
+      </c>
+      <c r="T110">
+        <v>1.46</v>
+      </c>
+      <c r="U110">
+        <v>2.55</v>
+      </c>
+      <c r="V110">
+        <v>3.05</v>
+      </c>
+      <c r="W110">
+        <v>1.34</v>
+      </c>
+      <c r="X110">
+        <v>9</v>
+      </c>
+      <c r="Y110">
+        <v>1.07</v>
+      </c>
+      <c r="Z110">
+        <v>2.12</v>
+      </c>
+      <c r="AA110">
+        <v>3</v>
+      </c>
+      <c r="AB110">
+        <v>3.35</v>
+      </c>
+      <c r="AC110">
+        <v>1.05</v>
+      </c>
+      <c r="AD110">
+        <v>8</v>
+      </c>
+      <c r="AE110">
+        <v>1.37</v>
+      </c>
+      <c r="AF110">
+        <v>2.8</v>
+      </c>
+      <c r="AG110">
+        <v>2.14</v>
+      </c>
+      <c r="AH110">
+        <v>1.66</v>
+      </c>
+      <c r="AI110">
+        <v>1.88</v>
+      </c>
+      <c r="AJ110">
+        <v>1.84</v>
+      </c>
+      <c r="AK110">
+        <v>1.3</v>
+      </c>
+      <c r="AL110">
+        <v>1.31</v>
+      </c>
+      <c r="AM110">
+        <v>1.66</v>
+      </c>
+      <c r="AN110">
+        <v>2.1</v>
+      </c>
+      <c r="AO110">
+        <v>0.82</v>
+      </c>
+      <c r="AP110">
+        <v>1.91</v>
+      </c>
+      <c r="AQ110">
+        <v>1</v>
+      </c>
+      <c r="AR110">
+        <v>1.34</v>
+      </c>
+      <c r="AS110">
+        <v>1.33</v>
+      </c>
+      <c r="AT110">
+        <v>2.67</v>
+      </c>
+      <c r="AU110">
+        <v>3</v>
+      </c>
+      <c r="AV110">
+        <v>6</v>
+      </c>
+      <c r="AW110">
+        <v>8</v>
+      </c>
+      <c r="AX110">
+        <v>8</v>
+      </c>
+      <c r="AY110">
+        <v>11</v>
+      </c>
+      <c r="AZ110">
+        <v>14</v>
+      </c>
+      <c r="BA110">
+        <v>4</v>
+      </c>
+      <c r="BB110">
+        <v>1</v>
+      </c>
+      <c r="BC110">
+        <v>5</v>
+      </c>
+      <c r="BD110">
+        <v>1.82</v>
+      </c>
+      <c r="BE110">
+        <v>7.5</v>
+      </c>
+      <c r="BF110">
+        <v>2.34</v>
+      </c>
+      <c r="BG110">
+        <v>1.5</v>
+      </c>
+      <c r="BH110">
+        <v>2.41</v>
+      </c>
+      <c r="BI110">
+        <v>1.87</v>
+      </c>
+      <c r="BJ110">
+        <v>1.87</v>
+      </c>
+      <c r="BK110">
+        <v>2.42</v>
+      </c>
+      <c r="BL110">
+        <v>1.53</v>
+      </c>
+      <c r="BM110">
+        <v>3.25</v>
+      </c>
+      <c r="BN110">
+        <v>1.29</v>
+      </c>
+      <c r="BO110">
+        <v>4.4</v>
+      </c>
+      <c r="BP110">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7451074</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45704.57291666666</v>
+      </c>
+      <c r="F111">
+        <v>22</v>
+      </c>
+      <c r="G111" t="s">
+        <v>73</v>
+      </c>
+      <c r="H111" t="s">
+        <v>72</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111">
+        <v>2</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>2</v>
+      </c>
+      <c r="N111">
+        <v>2</v>
+      </c>
+      <c r="O111" t="s">
+        <v>81</v>
+      </c>
+      <c r="P111" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q111">
+        <v>3.55</v>
+      </c>
+      <c r="R111">
+        <v>2.06</v>
+      </c>
+      <c r="S111">
+        <v>3.2</v>
+      </c>
+      <c r="T111">
+        <v>1.46</v>
+      </c>
+      <c r="U111">
+        <v>2.55</v>
+      </c>
+      <c r="V111">
+        <v>3</v>
+      </c>
+      <c r="W111">
+        <v>1.34</v>
+      </c>
+      <c r="X111">
+        <v>8.5</v>
+      </c>
+      <c r="Y111">
+        <v>1.07</v>
+      </c>
+      <c r="Z111">
+        <v>2.75</v>
+      </c>
+      <c r="AA111">
+        <v>2.95</v>
+      </c>
+      <c r="AB111">
+        <v>2.45</v>
+      </c>
+      <c r="AC111">
+        <v>1.05</v>
+      </c>
+      <c r="AD111">
+        <v>8</v>
+      </c>
+      <c r="AE111">
+        <v>1.36</v>
+      </c>
+      <c r="AF111">
+        <v>2.85</v>
+      </c>
+      <c r="AG111">
+        <v>2.12</v>
+      </c>
+      <c r="AH111">
+        <v>1.67</v>
+      </c>
+      <c r="AI111">
+        <v>1.83</v>
+      </c>
+      <c r="AJ111">
+        <v>1.88</v>
+      </c>
+      <c r="AK111">
+        <v>1.5</v>
+      </c>
+      <c r="AL111">
+        <v>1.32</v>
+      </c>
+      <c r="AM111">
+        <v>1.4</v>
+      </c>
+      <c r="AN111">
+        <v>1.64</v>
+      </c>
+      <c r="AO111">
+        <v>1.7</v>
+      </c>
+      <c r="AP111">
+        <v>1.5</v>
+      </c>
+      <c r="AQ111">
+        <v>1.82</v>
+      </c>
+      <c r="AR111">
+        <v>1.53</v>
+      </c>
+      <c r="AS111">
+        <v>1.25</v>
+      </c>
+      <c r="AT111">
+        <v>2.78</v>
+      </c>
+      <c r="AU111">
+        <v>3</v>
+      </c>
+      <c r="AV111">
+        <v>4</v>
+      </c>
+      <c r="AW111">
+        <v>12</v>
+      </c>
+      <c r="AX111">
+        <v>3</v>
+      </c>
+      <c r="AY111">
+        <v>15</v>
+      </c>
+      <c r="AZ111">
+        <v>7</v>
+      </c>
+      <c r="BA111">
+        <v>6</v>
+      </c>
+      <c r="BB111">
+        <v>3</v>
+      </c>
+      <c r="BC111">
+        <v>9</v>
+      </c>
+      <c r="BD111">
+        <v>2.2</v>
+      </c>
+      <c r="BE111">
+        <v>7.5</v>
+      </c>
+      <c r="BF111">
+        <v>1.91</v>
+      </c>
+      <c r="BG111">
+        <v>1.47</v>
+      </c>
+      <c r="BH111">
+        <v>2.5</v>
+      </c>
+      <c r="BI111">
+        <v>1.82</v>
+      </c>
+      <c r="BJ111">
+        <v>1.93</v>
+      </c>
+      <c r="BK111">
+        <v>2.34</v>
+      </c>
+      <c r="BL111">
+        <v>1.56</v>
+      </c>
+      <c r="BM111">
+        <v>3.02</v>
+      </c>
+      <c r="BN111">
+        <v>1.33</v>
+      </c>
+      <c r="BO111">
+        <v>4.2</v>
+      </c>
+      <c r="BP111">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -487,6 +487,9 @@
     <t>['33', '75', '90+6']</t>
   </si>
   <si>
+    <t>['57']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -638,9 +641,6 @@
   </si>
   <si>
     <t>['14', '53']</t>
-  </si>
-  <si>
-    <t>['57']</t>
   </si>
   <si>
     <t>['38']</t>
@@ -1017,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1560,7 +1560,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ3">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1891,7 +1891,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2097,7 +2097,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2715,7 +2715,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ9">
         <v>1.27</v>
@@ -2921,7 +2921,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3539,7 +3539,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3745,7 +3745,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3826,7 +3826,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ14">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR14">
         <v>1.27</v>
@@ -3951,7 +3951,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4441,7 +4441,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ17">
         <v>0.82</v>
@@ -4775,7 +4775,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4981,7 +4981,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5187,7 +5187,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5393,7 +5393,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5599,7 +5599,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6089,10 +6089,10 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ25">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR25">
         <v>1.8</v>
@@ -6217,7 +6217,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6423,7 +6423,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6629,7 +6629,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6835,7 +6835,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7328,7 +7328,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ31">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR31">
         <v>1.34</v>
@@ -7659,7 +7659,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7865,7 +7865,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8071,7 +8071,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8149,7 +8149,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ35">
         <v>1.2</v>
@@ -8976,7 +8976,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR39">
         <v>1.73</v>
@@ -9307,7 +9307,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9513,7 +9513,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9797,7 +9797,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43">
         <v>0.09</v>
@@ -10131,7 +10131,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10543,7 +10543,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10621,7 +10621,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47">
         <v>1.82</v>
@@ -10749,7 +10749,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10955,7 +10955,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11161,7 +11161,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11573,7 +11573,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11779,7 +11779,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12066,7 +12066,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12191,7 +12191,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12603,7 +12603,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12809,7 +12809,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12887,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13221,7 +13221,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13633,7 +13633,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13839,7 +13839,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14045,7 +14045,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14251,7 +14251,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14332,7 +14332,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ65">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14457,7 +14457,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14663,7 +14663,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14869,7 +14869,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15281,7 +15281,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15693,7 +15693,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15899,7 +15899,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16311,7 +16311,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16389,7 +16389,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ75">
         <v>1.09</v>
@@ -17010,7 +17010,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ78">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -17341,7 +17341,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17753,7 +17753,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17959,7 +17959,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18037,7 +18037,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ83">
         <v>1.2</v>
@@ -18165,7 +18165,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18577,7 +18577,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18783,7 +18783,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18989,7 +18989,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19195,7 +19195,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19276,7 +19276,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ89">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR89">
         <v>1.93</v>
@@ -19607,7 +19607,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19813,7 +19813,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20019,7 +20019,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20100,7 +20100,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ93">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR93">
         <v>1.14</v>
@@ -20225,7 +20225,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20431,7 +20431,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21049,7 +21049,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21461,7 +21461,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21539,7 +21539,7 @@
         <v>1.44</v>
       </c>
       <c r="AP100">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ100">
         <v>1.27</v>
@@ -21667,7 +21667,7 @@
         <v>149</v>
       </c>
       <c r="P101" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22366,7 +22366,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ104">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR104">
         <v>1.55</v>
@@ -23315,7 +23315,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23884,6 +23884,212 @@
       </c>
       <c r="BP111">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7451080</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F112">
+        <v>23</v>
+      </c>
+      <c r="G112" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" t="s">
+        <v>78</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="O112" t="s">
+        <v>157</v>
+      </c>
+      <c r="P112" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q112">
+        <v>2.75</v>
+      </c>
+      <c r="R112">
+        <v>2</v>
+      </c>
+      <c r="S112">
+        <v>4</v>
+      </c>
+      <c r="T112">
+        <v>1.41</v>
+      </c>
+      <c r="U112">
+        <v>2.7</v>
+      </c>
+      <c r="V112">
+        <v>3.14</v>
+      </c>
+      <c r="W112">
+        <v>1.32</v>
+      </c>
+      <c r="X112">
+        <v>8.4</v>
+      </c>
+      <c r="Y112">
+        <v>1.02</v>
+      </c>
+      <c r="Z112">
+        <v>2.19</v>
+      </c>
+      <c r="AA112">
+        <v>3.17</v>
+      </c>
+      <c r="AB112">
+        <v>3.39</v>
+      </c>
+      <c r="AC112">
+        <v>1.05</v>
+      </c>
+      <c r="AD112">
+        <v>8</v>
+      </c>
+      <c r="AE112">
+        <v>1.3</v>
+      </c>
+      <c r="AF112">
+        <v>3.2</v>
+      </c>
+      <c r="AG112">
+        <v>2.1</v>
+      </c>
+      <c r="AH112">
+        <v>1.65</v>
+      </c>
+      <c r="AI112">
+        <v>1.8</v>
+      </c>
+      <c r="AJ112">
+        <v>1.91</v>
+      </c>
+      <c r="AK112">
+        <v>1.31</v>
+      </c>
+      <c r="AL112">
+        <v>1.31</v>
+      </c>
+      <c r="AM112">
+        <v>1.67</v>
+      </c>
+      <c r="AN112">
+        <v>1.1</v>
+      </c>
+      <c r="AO112">
+        <v>0.82</v>
+      </c>
+      <c r="AP112">
+        <v>1.27</v>
+      </c>
+      <c r="AQ112">
+        <v>0.75</v>
+      </c>
+      <c r="AR112">
+        <v>1.47</v>
+      </c>
+      <c r="AS112">
+        <v>1.36</v>
+      </c>
+      <c r="AT112">
+        <v>2.83</v>
+      </c>
+      <c r="AU112">
+        <v>6</v>
+      </c>
+      <c r="AV112">
+        <v>3</v>
+      </c>
+      <c r="AW112">
+        <v>7</v>
+      </c>
+      <c r="AX112">
+        <v>3</v>
+      </c>
+      <c r="AY112">
+        <v>13</v>
+      </c>
+      <c r="AZ112">
+        <v>6</v>
+      </c>
+      <c r="BA112">
+        <v>6</v>
+      </c>
+      <c r="BB112">
+        <v>4</v>
+      </c>
+      <c r="BC112">
+        <v>10</v>
+      </c>
+      <c r="BD112">
+        <v>1.75</v>
+      </c>
+      <c r="BE112">
+        <v>8</v>
+      </c>
+      <c r="BF112">
+        <v>2.42</v>
+      </c>
+      <c r="BG112">
+        <v>1.28</v>
+      </c>
+      <c r="BH112">
+        <v>3.25</v>
+      </c>
+      <c r="BI112">
+        <v>1.52</v>
+      </c>
+      <c r="BJ112">
+        <v>2.37</v>
+      </c>
+      <c r="BK112">
+        <v>1.87</v>
+      </c>
+      <c r="BL112">
+        <v>1.87</v>
+      </c>
+      <c r="BM112">
+        <v>2.38</v>
+      </c>
+      <c r="BN112">
+        <v>1.54</v>
+      </c>
+      <c r="BO112">
+        <v>3.12</v>
+      </c>
+      <c r="BP112">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -488,6 +488,12 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['10', '19', '24', '89']</t>
+  </si>
+  <si>
+    <t>['27', '39', '44', '51']</t>
   </si>
   <si>
     <t>['8', '61']</t>
@@ -1017,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1763,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ4">
         <v>1.17</v>
@@ -1891,7 +1897,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2097,7 +2103,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2175,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2715,7 +2721,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2921,7 +2927,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3002,7 +3008,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ10">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR10">
         <v>3.14</v>
@@ -3539,7 +3545,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3745,7 +3751,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3823,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ14">
         <v>0.75</v>
@@ -3951,7 +3957,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4032,7 +4038,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ15">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR15">
         <v>0.6899999999999999</v>
@@ -4235,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ16">
         <v>1.09</v>
@@ -4775,7 +4781,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4981,7 +4987,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5187,7 +5193,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5393,7 +5399,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5599,7 +5605,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5883,10 +5889,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ24">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR24">
         <v>1.41</v>
@@ -6217,7 +6223,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6295,10 +6301,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR26">
         <v>1.71</v>
@@ -6423,7 +6429,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6629,7 +6635,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6835,7 +6841,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7659,7 +7665,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7740,7 +7746,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ33">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -7865,7 +7871,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -7943,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ34">
         <v>0.09</v>
@@ -8071,7 +8077,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8152,7 +8158,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ35">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR35">
         <v>1.65</v>
@@ -8355,7 +8361,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ36">
         <v>0.82</v>
@@ -9179,7 +9185,7 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ40">
         <v>1.27</v>
@@ -9307,7 +9313,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9513,7 +9519,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9594,7 +9600,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ42">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10131,7 +10137,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10212,7 +10218,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ45">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR45">
         <v>1.19</v>
@@ -10415,7 +10421,7 @@
         <v>1.2</v>
       </c>
       <c r="AP46">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ46">
         <v>0.82</v>
@@ -10543,7 +10549,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10749,7 +10755,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10830,7 +10836,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ48">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR48">
         <v>1.2</v>
@@ -10955,7 +10961,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11036,7 +11042,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ49">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11161,7 +11167,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11573,7 +11579,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11779,7 +11785,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11857,7 +11863,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ53">
         <v>1.17</v>
@@ -12063,7 +12069,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ54">
         <v>0.75</v>
@@ -12191,7 +12197,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12272,7 +12278,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ55">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR55">
         <v>1.97</v>
@@ -12603,7 +12609,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12684,7 +12690,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ57">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR57">
         <v>1.11</v>
@@ -12809,7 +12815,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13221,7 +13227,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13633,7 +13639,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13839,7 +13845,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -13920,7 +13926,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ63">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR63">
         <v>1.18</v>
@@ -14045,7 +14051,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14123,7 +14129,7 @@
         <v>0.67</v>
       </c>
       <c r="AP64">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ64">
         <v>1.09</v>
@@ -14251,7 +14257,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14457,7 +14463,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14535,10 +14541,10 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR66">
         <v>1.64</v>
@@ -14663,7 +14669,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14869,7 +14875,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15281,7 +15287,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15693,7 +15699,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15899,7 +15905,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -15980,7 +15986,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ73">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16183,7 +16189,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ74">
         <v>0.09</v>
@@ -16311,7 +16317,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16595,10 +16601,10 @@
         <v>1.71</v>
       </c>
       <c r="AP76">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ76">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR76">
         <v>1.66</v>
@@ -17341,7 +17347,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17753,7 +17759,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17959,7 +17965,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18040,7 +18046,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ83">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR83">
         <v>1.51</v>
@@ -18165,7 +18171,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18452,7 +18458,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ85">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -18577,7 +18583,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18655,7 +18661,7 @@
         <v>2</v>
       </c>
       <c r="AP86">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ86">
         <v>1.82</v>
@@ -18783,7 +18789,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18989,7 +18995,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19195,7 +19201,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19479,7 +19485,7 @@
         <v>0.88</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19607,7 +19613,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19813,7 +19819,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20019,7 +20025,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20225,7 +20231,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20431,7 +20437,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20509,7 +20515,7 @@
         <v>1.22</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ95">
         <v>1.17</v>
@@ -20715,7 +20721,7 @@
         <v>0.78</v>
       </c>
       <c r="AP96">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21049,7 +21055,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21461,7 +21467,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21748,7 +21754,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ101">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR101">
         <v>1.55</v>
@@ -22160,7 +22166,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ103">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR103">
         <v>1.14</v>
@@ -22363,7 +22369,7 @@
         <v>0.9</v>
       </c>
       <c r="AP104">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ104">
         <v>0.75</v>
@@ -22491,7 +22497,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22569,7 +22575,7 @@
         <v>0.9</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ105">
         <v>1.09</v>
@@ -22697,7 +22703,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22903,7 +22909,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23109,7 +23115,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23315,7 +23321,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23727,7 +23733,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -24090,6 +24096,418 @@
       </c>
       <c r="BP112">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7451078</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F113">
+        <v>23</v>
+      </c>
+      <c r="G113" t="s">
+        <v>74</v>
+      </c>
+      <c r="H113" t="s">
+        <v>73</v>
+      </c>
+      <c r="I113">
+        <v>3</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>3</v>
+      </c>
+      <c r="L113">
+        <v>4</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>4</v>
+      </c>
+      <c r="O113" t="s">
+        <v>158</v>
+      </c>
+      <c r="P113" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q113">
+        <v>2.3</v>
+      </c>
+      <c r="R113">
+        <v>2.2</v>
+      </c>
+      <c r="S113">
+        <v>5.2</v>
+      </c>
+      <c r="T113">
+        <v>1.4</v>
+      </c>
+      <c r="U113">
+        <v>2.75</v>
+      </c>
+      <c r="V113">
+        <v>2.8</v>
+      </c>
+      <c r="W113">
+        <v>1.39</v>
+      </c>
+      <c r="X113">
+        <v>6.85</v>
+      </c>
+      <c r="Y113">
+        <v>1.05</v>
+      </c>
+      <c r="Z113">
+        <v>1.74</v>
+      </c>
+      <c r="AA113">
+        <v>3.35</v>
+      </c>
+      <c r="AB113">
+        <v>4.4</v>
+      </c>
+      <c r="AC113">
+        <v>1.03</v>
+      </c>
+      <c r="AD113">
+        <v>9</v>
+      </c>
+      <c r="AE113">
+        <v>1.32</v>
+      </c>
+      <c r="AF113">
+        <v>3.1</v>
+      </c>
+      <c r="AG113">
+        <v>1.98</v>
+      </c>
+      <c r="AH113">
+        <v>1.77</v>
+      </c>
+      <c r="AI113">
+        <v>1.88</v>
+      </c>
+      <c r="AJ113">
+        <v>1.82</v>
+      </c>
+      <c r="AK113">
+        <v>1.19</v>
+      </c>
+      <c r="AL113">
+        <v>1.26</v>
+      </c>
+      <c r="AM113">
+        <v>1.99</v>
+      </c>
+      <c r="AN113">
+        <v>2.45</v>
+      </c>
+      <c r="AO113">
+        <v>1.2</v>
+      </c>
+      <c r="AP113">
+        <v>2.5</v>
+      </c>
+      <c r="AQ113">
+        <v>1.09</v>
+      </c>
+      <c r="AR113">
+        <v>1.48</v>
+      </c>
+      <c r="AS113">
+        <v>1.36</v>
+      </c>
+      <c r="AT113">
+        <v>2.84</v>
+      </c>
+      <c r="AU113">
+        <v>7</v>
+      </c>
+      <c r="AV113">
+        <v>4</v>
+      </c>
+      <c r="AW113">
+        <v>4</v>
+      </c>
+      <c r="AX113">
+        <v>5</v>
+      </c>
+      <c r="AY113">
+        <v>11</v>
+      </c>
+      <c r="AZ113">
+        <v>9</v>
+      </c>
+      <c r="BA113">
+        <v>3</v>
+      </c>
+      <c r="BB113">
+        <v>2</v>
+      </c>
+      <c r="BC113">
+        <v>5</v>
+      </c>
+      <c r="BD113">
+        <v>1.64</v>
+      </c>
+      <c r="BE113">
+        <v>8</v>
+      </c>
+      <c r="BF113">
+        <v>2.77</v>
+      </c>
+      <c r="BG113">
+        <v>1.28</v>
+      </c>
+      <c r="BH113">
+        <v>3.25</v>
+      </c>
+      <c r="BI113">
+        <v>1.52</v>
+      </c>
+      <c r="BJ113">
+        <v>2.37</v>
+      </c>
+      <c r="BK113">
+        <v>1.87</v>
+      </c>
+      <c r="BL113">
+        <v>1.87</v>
+      </c>
+      <c r="BM113">
+        <v>2.38</v>
+      </c>
+      <c r="BN113">
+        <v>1.54</v>
+      </c>
+      <c r="BO113">
+        <v>3.12</v>
+      </c>
+      <c r="BP113">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7451077</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45710.57291666666</v>
+      </c>
+      <c r="F114">
+        <v>23</v>
+      </c>
+      <c r="G114" t="s">
+        <v>72</v>
+      </c>
+      <c r="H114" t="s">
+        <v>70</v>
+      </c>
+      <c r="I114">
+        <v>3</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>3</v>
+      </c>
+      <c r="L114">
+        <v>4</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>4</v>
+      </c>
+      <c r="O114" t="s">
+        <v>159</v>
+      </c>
+      <c r="P114" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q114">
+        <v>3.75</v>
+      </c>
+      <c r="R114">
+        <v>2.03</v>
+      </c>
+      <c r="S114">
+        <v>3.1</v>
+      </c>
+      <c r="T114">
+        <v>1.49</v>
+      </c>
+      <c r="U114">
+        <v>2.45</v>
+      </c>
+      <c r="V114">
+        <v>3.15</v>
+      </c>
+      <c r="W114">
+        <v>1.32</v>
+      </c>
+      <c r="X114">
+        <v>7.8</v>
+      </c>
+      <c r="Y114">
+        <v>1.03</v>
+      </c>
+      <c r="Z114">
+        <v>2.95</v>
+      </c>
+      <c r="AA114">
+        <v>2.95</v>
+      </c>
+      <c r="AB114">
+        <v>2.35</v>
+      </c>
+      <c r="AC114">
+        <v>1.06</v>
+      </c>
+      <c r="AD114">
+        <v>7.5</v>
+      </c>
+      <c r="AE114">
+        <v>1.39</v>
+      </c>
+      <c r="AF114">
+        <v>2.75</v>
+      </c>
+      <c r="AG114">
+        <v>2.2</v>
+      </c>
+      <c r="AH114">
+        <v>1.62</v>
+      </c>
+      <c r="AI114">
+        <v>1.9</v>
+      </c>
+      <c r="AJ114">
+        <v>1.82</v>
+      </c>
+      <c r="AK114">
+        <v>1.54</v>
+      </c>
+      <c r="AL114">
+        <v>1.32</v>
+      </c>
+      <c r="AM114">
+        <v>1.37</v>
+      </c>
+      <c r="AN114">
+        <v>2</v>
+      </c>
+      <c r="AO114">
+        <v>1.2</v>
+      </c>
+      <c r="AP114">
+        <v>2.08</v>
+      </c>
+      <c r="AQ114">
+        <v>1.09</v>
+      </c>
+      <c r="AR114">
+        <v>1.68</v>
+      </c>
+      <c r="AS114">
+        <v>1.85</v>
+      </c>
+      <c r="AT114">
+        <v>3.53</v>
+      </c>
+      <c r="AU114">
+        <v>7</v>
+      </c>
+      <c r="AV114">
+        <v>2</v>
+      </c>
+      <c r="AW114">
+        <v>4</v>
+      </c>
+      <c r="AX114">
+        <v>3</v>
+      </c>
+      <c r="AY114">
+        <v>11</v>
+      </c>
+      <c r="AZ114">
+        <v>5</v>
+      </c>
+      <c r="BA114">
+        <v>4</v>
+      </c>
+      <c r="BB114">
+        <v>2</v>
+      </c>
+      <c r="BC114">
+        <v>6</v>
+      </c>
+      <c r="BD114">
+        <v>1.91</v>
+      </c>
+      <c r="BE114">
+        <v>7.5</v>
+      </c>
+      <c r="BF114">
+        <v>2.2</v>
+      </c>
+      <c r="BG114">
+        <v>1.43</v>
+      </c>
+      <c r="BH114">
+        <v>2.63</v>
+      </c>
+      <c r="BI114">
+        <v>1.74</v>
+      </c>
+      <c r="BJ114">
+        <v>2.02</v>
+      </c>
+      <c r="BK114">
+        <v>2.22</v>
+      </c>
+      <c r="BL114">
+        <v>1.62</v>
+      </c>
+      <c r="BM114">
+        <v>2.85</v>
+      </c>
+      <c r="BN114">
+        <v>1.37</v>
+      </c>
+      <c r="BO114">
+        <v>3.9</v>
+      </c>
+      <c r="BP114">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1023,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP114"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1360,7 +1360,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ3">
         <v>0.75</v>
@@ -1978,7 +1978,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3420,7 +3420,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ12">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR12">
         <v>2.03</v>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ13">
         <v>1.17</v>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ15">
         <v>1.09</v>
@@ -4244,7 +4244,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR16">
         <v>1.93</v>
@@ -4450,7 +4450,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ17">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR17">
         <v>1.8</v>
@@ -5477,10 +5477,10 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ22">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR22">
         <v>1.22</v>
@@ -5683,10 +5683,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -6919,7 +6919,7 @@
         <v>2</v>
       </c>
       <c r="AP29">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ29">
         <v>1.82</v>
@@ -7540,7 +7540,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR32">
         <v>1.2</v>
@@ -7743,7 +7743,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ33">
         <v>1.09</v>
@@ -8364,7 +8364,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ36">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR36">
         <v>1.6</v>
@@ -8570,7 +8570,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ37">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR37">
         <v>1.04</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -10009,7 +10009,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ44">
         <v>1.82</v>
@@ -10424,7 +10424,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ46">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -11245,7 +11245,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ50">
         <v>1.27</v>
@@ -11657,10 +11657,10 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ52">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR52">
         <v>1.48</v>
@@ -12481,10 +12481,10 @@
         <v>0.8</v>
       </c>
       <c r="AP56">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ56">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR56">
         <v>1.17</v>
@@ -13923,7 +13923,7 @@
         <v>1.83</v>
       </c>
       <c r="AP63">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ63">
         <v>1.09</v>
@@ -14132,7 +14132,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ64">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14335,7 +14335,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ65">
         <v>0.75</v>
@@ -15780,7 +15780,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ72">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR72">
         <v>1.34</v>
@@ -15983,7 +15983,7 @@
         <v>1.57</v>
       </c>
       <c r="AP73">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ73">
         <v>1.09</v>
@@ -16398,7 +16398,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ75">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR75">
         <v>1.54</v>
@@ -17219,7 +17219,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ79">
         <v>1.27</v>
@@ -17837,7 +17837,7 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ82">
         <v>0.09</v>
@@ -18252,7 +18252,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ84">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR84">
         <v>1.2</v>
@@ -18870,7 +18870,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ87">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR87">
         <v>1.57</v>
@@ -19073,7 +19073,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ88">
         <v>1.17</v>
@@ -19900,7 +19900,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR92">
         <v>1.57</v>
@@ -20103,7 +20103,7 @@
         <v>0.89</v>
       </c>
       <c r="AP93">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ93">
         <v>0.75</v>
@@ -20312,7 +20312,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ94">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR94">
         <v>1.89</v>
@@ -21960,7 +21960,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ102">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR102">
         <v>1.92</v>
@@ -22163,7 +22163,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ103">
         <v>1.09</v>
@@ -22578,7 +22578,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ105">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR105">
         <v>1.66</v>
@@ -22781,7 +22781,7 @@
         <v>1.1</v>
       </c>
       <c r="AP106">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ106">
         <v>1.17</v>
@@ -24507,6 +24507,418 @@
         <v>3.9</v>
       </c>
       <c r="BP114">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7451076</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F115">
+        <v>23</v>
+      </c>
+      <c r="G115" t="s">
+        <v>71</v>
+      </c>
+      <c r="H115" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115" t="s">
+        <v>133</v>
+      </c>
+      <c r="P115" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q115">
+        <v>2.6</v>
+      </c>
+      <c r="R115">
+        <v>2.05</v>
+      </c>
+      <c r="S115">
+        <v>3.9</v>
+      </c>
+      <c r="T115">
+        <v>1.42</v>
+      </c>
+      <c r="U115">
+        <v>2.65</v>
+      </c>
+      <c r="V115">
+        <v>2.95</v>
+      </c>
+      <c r="W115">
+        <v>1.35</v>
+      </c>
+      <c r="X115">
+        <v>7.75</v>
+      </c>
+      <c r="Y115">
+        <v>1.07</v>
+      </c>
+      <c r="Z115">
+        <v>1.84</v>
+      </c>
+      <c r="AA115">
+        <v>3.18</v>
+      </c>
+      <c r="AB115">
+        <v>3.53</v>
+      </c>
+      <c r="AC115">
+        <v>1.06</v>
+      </c>
+      <c r="AD115">
+        <v>8</v>
+      </c>
+      <c r="AE115">
+        <v>1.33</v>
+      </c>
+      <c r="AF115">
+        <v>3</v>
+      </c>
+      <c r="AG115">
+        <v>2</v>
+      </c>
+      <c r="AH115">
+        <v>1.73</v>
+      </c>
+      <c r="AI115">
+        <v>1.87</v>
+      </c>
+      <c r="AJ115">
+        <v>1.82</v>
+      </c>
+      <c r="AK115">
+        <v>1.24</v>
+      </c>
+      <c r="AL115">
+        <v>1.28</v>
+      </c>
+      <c r="AM115">
+        <v>1.72</v>
+      </c>
+      <c r="AN115">
+        <v>1.73</v>
+      </c>
+      <c r="AO115">
+        <v>0.82</v>
+      </c>
+      <c r="AP115">
+        <v>1.83</v>
+      </c>
+      <c r="AQ115">
+        <v>0.75</v>
+      </c>
+      <c r="AR115">
+        <v>1.11</v>
+      </c>
+      <c r="AS115">
+        <v>1.03</v>
+      </c>
+      <c r="AT115">
+        <v>2.14</v>
+      </c>
+      <c r="AU115">
+        <v>2</v>
+      </c>
+      <c r="AV115">
+        <v>4</v>
+      </c>
+      <c r="AW115">
+        <v>1</v>
+      </c>
+      <c r="AX115">
+        <v>4</v>
+      </c>
+      <c r="AY115">
+        <v>3</v>
+      </c>
+      <c r="AZ115">
+        <v>8</v>
+      </c>
+      <c r="BA115">
+        <v>4</v>
+      </c>
+      <c r="BB115">
+        <v>9</v>
+      </c>
+      <c r="BC115">
+        <v>13</v>
+      </c>
+      <c r="BD115">
+        <v>1.98</v>
+      </c>
+      <c r="BE115">
+        <v>7.6</v>
+      </c>
+      <c r="BF115">
+        <v>2.11</v>
+      </c>
+      <c r="BG115">
+        <v>1.43</v>
+      </c>
+      <c r="BH115">
+        <v>2.63</v>
+      </c>
+      <c r="BI115">
+        <v>1.74</v>
+      </c>
+      <c r="BJ115">
+        <v>2.02</v>
+      </c>
+      <c r="BK115">
+        <v>2.22</v>
+      </c>
+      <c r="BL115">
+        <v>1.62</v>
+      </c>
+      <c r="BM115">
+        <v>2.85</v>
+      </c>
+      <c r="BN115">
+        <v>1.37</v>
+      </c>
+      <c r="BO115">
+        <v>3.9</v>
+      </c>
+      <c r="BP115">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7451079</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45711.5625</v>
+      </c>
+      <c r="F116">
+        <v>23</v>
+      </c>
+      <c r="G116" t="s">
+        <v>79</v>
+      </c>
+      <c r="H116" t="s">
+        <v>76</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116" t="s">
+        <v>81</v>
+      </c>
+      <c r="P116" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q116">
+        <v>2.8</v>
+      </c>
+      <c r="R116">
+        <v>2.08</v>
+      </c>
+      <c r="S116">
+        <v>4</v>
+      </c>
+      <c r="T116">
+        <v>1.46</v>
+      </c>
+      <c r="U116">
+        <v>2.55</v>
+      </c>
+      <c r="V116">
+        <v>3</v>
+      </c>
+      <c r="W116">
+        <v>1.34</v>
+      </c>
+      <c r="X116">
+        <v>8.4</v>
+      </c>
+      <c r="Y116">
+        <v>1.02</v>
+      </c>
+      <c r="Z116">
+        <v>2.15</v>
+      </c>
+      <c r="AA116">
+        <v>3</v>
+      </c>
+      <c r="AB116">
+        <v>3.25</v>
+      </c>
+      <c r="AC116">
+        <v>1.05</v>
+      </c>
+      <c r="AD116">
+        <v>8</v>
+      </c>
+      <c r="AE116">
+        <v>1.36</v>
+      </c>
+      <c r="AF116">
+        <v>2.85</v>
+      </c>
+      <c r="AG116">
+        <v>2.12</v>
+      </c>
+      <c r="AH116">
+        <v>1.67</v>
+      </c>
+      <c r="AI116">
+        <v>1.86</v>
+      </c>
+      <c r="AJ116">
+        <v>1.85</v>
+      </c>
+      <c r="AK116">
+        <v>1.31</v>
+      </c>
+      <c r="AL116">
+        <v>1.31</v>
+      </c>
+      <c r="AM116">
+        <v>1.64</v>
+      </c>
+      <c r="AN116">
+        <v>1.6</v>
+      </c>
+      <c r="AO116">
+        <v>1.09</v>
+      </c>
+      <c r="AP116">
+        <v>1.55</v>
+      </c>
+      <c r="AQ116">
+        <v>1.08</v>
+      </c>
+      <c r="AR116">
+        <v>1.57</v>
+      </c>
+      <c r="AS116">
+        <v>1.05</v>
+      </c>
+      <c r="AT116">
+        <v>2.62</v>
+      </c>
+      <c r="AU116">
+        <v>4</v>
+      </c>
+      <c r="AV116">
+        <v>0</v>
+      </c>
+      <c r="AW116">
+        <v>8</v>
+      </c>
+      <c r="AX116">
+        <v>3</v>
+      </c>
+      <c r="AY116">
+        <v>12</v>
+      </c>
+      <c r="AZ116">
+        <v>3</v>
+      </c>
+      <c r="BA116">
+        <v>5</v>
+      </c>
+      <c r="BB116">
+        <v>2</v>
+      </c>
+      <c r="BC116">
+        <v>7</v>
+      </c>
+      <c r="BD116">
+        <v>1.75</v>
+      </c>
+      <c r="BE116">
+        <v>7.5</v>
+      </c>
+      <c r="BF116">
+        <v>2.53</v>
+      </c>
+      <c r="BG116">
+        <v>1.43</v>
+      </c>
+      <c r="BH116">
+        <v>2.63</v>
+      </c>
+      <c r="BI116">
+        <v>1.74</v>
+      </c>
+      <c r="BJ116">
+        <v>2.02</v>
+      </c>
+      <c r="BK116">
+        <v>2.22</v>
+      </c>
+      <c r="BL116">
+        <v>1.62</v>
+      </c>
+      <c r="BM116">
+        <v>2.85</v>
+      </c>
+      <c r="BN116">
+        <v>1.37</v>
+      </c>
+      <c r="BO116">
+        <v>3.9</v>
+      </c>
+      <c r="BP116">
         <v>1.19</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="218">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,9 @@
     <t>['27', '39', '44', '51']</t>
   </si>
   <si>
+    <t>['17', '26', '42']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -662,6 +665,9 @@
   </si>
   <si>
     <t>['15', '37']</t>
+  </si>
+  <si>
+    <t>['16', '57']</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1772,7 +1778,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ4">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1897,7 +1903,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2103,7 +2109,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2593,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ8">
         <v>0.09</v>
@@ -2721,7 +2727,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2927,7 +2933,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3545,7 +3551,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3626,7 +3632,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ13">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3751,7 +3757,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3957,7 +3963,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4781,7 +4787,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4987,7 +4993,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5065,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20">
         <v>1.27</v>
@@ -5193,7 +5199,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5399,7 +5405,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5605,7 +5611,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6223,7 +6229,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6429,7 +6435,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6635,7 +6641,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6713,10 +6719,10 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR28">
         <v>1.45</v>
@@ -6841,7 +6847,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7665,7 +7671,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7871,7 +7877,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8077,7 +8083,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8776,7 +8782,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ38">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR38">
         <v>1.94</v>
@@ -9313,7 +9319,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9519,7 +9525,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9597,7 +9603,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ42">
         <v>1.09</v>
@@ -10137,7 +10143,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10549,7 +10555,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10755,7 +10761,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10961,7 +10967,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11039,7 +11045,7 @@
         <v>1.75</v>
       </c>
       <c r="AP49">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ49">
         <v>1.09</v>
@@ -11167,7 +11173,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11579,7 +11585,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11785,7 +11791,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11866,7 +11872,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ53">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12197,7 +12203,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12609,7 +12615,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12815,7 +12821,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13227,7 +13233,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13305,7 +13311,7 @@
         <v>1.8</v>
       </c>
       <c r="AP60">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ60">
         <v>1.82</v>
@@ -13639,7 +13645,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13720,7 +13726,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ62">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR62">
         <v>0.93</v>
@@ -13845,7 +13851,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14051,7 +14057,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14257,7 +14263,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14463,7 +14469,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14669,7 +14675,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14747,7 +14753,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -14875,7 +14881,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14956,7 +14962,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ68">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR68">
         <v>1.39</v>
@@ -15287,7 +15293,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15699,7 +15705,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15905,7 +15911,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16317,7 +16323,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -17013,7 +17019,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ78">
         <v>0.75</v>
@@ -17347,7 +17353,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17634,7 +17640,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -17759,7 +17765,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17965,7 +17971,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18171,7 +18177,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18249,7 +18255,7 @@
         <v>0.88</v>
       </c>
       <c r="AP84">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ84">
         <v>0.75</v>
@@ -18583,7 +18589,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18789,7 +18795,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18995,7 +19001,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19076,7 +19082,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ88">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19201,7 +19207,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19613,7 +19619,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19819,7 +19825,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20025,7 +20031,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20231,7 +20237,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20437,7 +20443,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20518,7 +20524,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ95">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -20927,7 +20933,7 @@
         <v>0</v>
       </c>
       <c r="AP97">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ97">
         <v>0.09</v>
@@ -21055,7 +21061,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21467,7 +21473,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -22497,7 +22503,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22703,7 +22709,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22784,7 +22790,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ106">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR106">
         <v>1.58</v>
@@ -22909,7 +22915,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -22990,7 +22996,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ107">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR107">
         <v>1.16</v>
@@ -23115,7 +23121,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23193,7 +23199,7 @@
         <v>1.3</v>
       </c>
       <c r="AP108">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108">
         <v>1.27</v>
@@ -23321,7 +23327,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23733,7 +23739,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -24919,6 +24925,212 @@
         <v>3.9</v>
       </c>
       <c r="BP116">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7451082</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F117">
+        <v>24</v>
+      </c>
+      <c r="G117" t="s">
+        <v>76</v>
+      </c>
+      <c r="H117" t="s">
+        <v>77</v>
+      </c>
+      <c r="I117">
+        <v>3</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>4</v>
+      </c>
+      <c r="L117">
+        <v>3</v>
+      </c>
+      <c r="M117">
+        <v>2</v>
+      </c>
+      <c r="N117">
+        <v>5</v>
+      </c>
+      <c r="O117" t="s">
+        <v>160</v>
+      </c>
+      <c r="P117" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q117">
+        <v>3</v>
+      </c>
+      <c r="R117">
+        <v>2.08</v>
+      </c>
+      <c r="S117">
+        <v>3.8</v>
+      </c>
+      <c r="T117">
+        <v>1.46</v>
+      </c>
+      <c r="U117">
+        <v>2.55</v>
+      </c>
+      <c r="V117">
+        <v>3</v>
+      </c>
+      <c r="W117">
+        <v>1.34</v>
+      </c>
+      <c r="X117">
+        <v>10</v>
+      </c>
+      <c r="Y117">
+        <v>1.06</v>
+      </c>
+      <c r="Z117">
+        <v>2.31</v>
+      </c>
+      <c r="AA117">
+        <v>2.9</v>
+      </c>
+      <c r="AB117">
+        <v>3.05</v>
+      </c>
+      <c r="AC117">
+        <v>1.07</v>
+      </c>
+      <c r="AD117">
+        <v>7.5</v>
+      </c>
+      <c r="AE117">
+        <v>1.36</v>
+      </c>
+      <c r="AF117">
+        <v>2.9</v>
+      </c>
+      <c r="AG117">
+        <v>2.11</v>
+      </c>
+      <c r="AH117">
+        <v>1.67</v>
+      </c>
+      <c r="AI117">
+        <v>1.82</v>
+      </c>
+      <c r="AJ117">
+        <v>1.89</v>
+      </c>
+      <c r="AK117">
+        <v>1.34</v>
+      </c>
+      <c r="AL117">
+        <v>1.33</v>
+      </c>
+      <c r="AM117">
+        <v>1.56</v>
+      </c>
+      <c r="AN117">
+        <v>1.09</v>
+      </c>
+      <c r="AO117">
+        <v>1.17</v>
+      </c>
+      <c r="AP117">
+        <v>1.25</v>
+      </c>
+      <c r="AQ117">
+        <v>1.08</v>
+      </c>
+      <c r="AR117">
+        <v>1.26</v>
+      </c>
+      <c r="AS117">
+        <v>1.61</v>
+      </c>
+      <c r="AT117">
+        <v>2.87</v>
+      </c>
+      <c r="AU117">
+        <v>6</v>
+      </c>
+      <c r="AV117">
+        <v>5</v>
+      </c>
+      <c r="AW117">
+        <v>1</v>
+      </c>
+      <c r="AX117">
+        <v>5</v>
+      </c>
+      <c r="AY117">
+        <v>7</v>
+      </c>
+      <c r="AZ117">
+        <v>10</v>
+      </c>
+      <c r="BA117">
+        <v>3</v>
+      </c>
+      <c r="BB117">
+        <v>6</v>
+      </c>
+      <c r="BC117">
+        <v>9</v>
+      </c>
+      <c r="BD117">
+        <v>2.05</v>
+      </c>
+      <c r="BE117">
+        <v>7.5</v>
+      </c>
+      <c r="BF117">
+        <v>2.05</v>
+      </c>
+      <c r="BG117">
+        <v>1.43</v>
+      </c>
+      <c r="BH117">
+        <v>2.63</v>
+      </c>
+      <c r="BI117">
+        <v>1.74</v>
+      </c>
+      <c r="BJ117">
+        <v>2.02</v>
+      </c>
+      <c r="BK117">
+        <v>2.22</v>
+      </c>
+      <c r="BL117">
+        <v>1.62</v>
+      </c>
+      <c r="BM117">
+        <v>2.85</v>
+      </c>
+      <c r="BN117">
+        <v>1.37</v>
+      </c>
+      <c r="BO117">
+        <v>3.9</v>
+      </c>
+      <c r="BP117">
         <v>1.19</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="220">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -499,6 +499,9 @@
     <t>['17', '26', '42']</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -668,6 +671,9 @@
   </si>
   <si>
     <t>['16', '57']</t>
+  </si>
+  <si>
+    <t>['78', '85']</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP117"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1569,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ3">
         <v>0.75</v>
@@ -1903,7 +1909,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -1981,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ5">
         <v>0.75</v>
@@ -2109,7 +2115,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2190,7 +2196,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2396,7 +2402,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2727,7 +2733,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2933,7 +2939,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3011,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ10">
         <v>1.09</v>
@@ -3220,7 +3226,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ11">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3551,7 +3557,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3757,7 +3763,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3963,7 +3969,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4041,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ15">
         <v>1.09</v>
@@ -4662,7 +4668,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR18">
         <v>0.8100000000000001</v>
@@ -4787,7 +4793,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4993,7 +4999,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5199,7 +5205,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5277,10 +5283,10 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ21">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR21">
         <v>2.05</v>
@@ -5405,7 +5411,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5483,7 +5489,7 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ22">
         <v>0.75</v>
@@ -5611,7 +5617,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6229,7 +6235,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6435,7 +6441,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6641,7 +6647,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6847,7 +6853,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -6925,10 +6931,10 @@
         <v>2</v>
       </c>
       <c r="AP29">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ29">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR29">
         <v>1.12</v>
@@ -7131,10 +7137,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR30">
         <v>1.82</v>
@@ -7671,7 +7677,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7877,7 +7883,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8083,7 +8089,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8985,7 +8991,7 @@
         <v>1.25</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
         <v>0.75</v>
@@ -9319,7 +9325,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9397,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -9525,7 +9531,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10018,7 +10024,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ44">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10143,7 +10149,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10555,7 +10561,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10636,7 +10642,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ47">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR47">
         <v>1.56</v>
@@ -10761,7 +10767,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10967,7 +10973,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11173,7 +11179,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11585,7 +11591,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11791,7 +11797,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12203,7 +12209,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12487,7 +12493,7 @@
         <v>0.8</v>
       </c>
       <c r="AP56">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ56">
         <v>1.08</v>
@@ -12615,7 +12621,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12821,7 +12827,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12902,7 +12908,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR58">
         <v>1.49</v>
@@ -13105,7 +13111,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ59">
         <v>0.09</v>
@@ -13233,7 +13239,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13314,7 +13320,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ60">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR60">
         <v>1.28</v>
@@ -13645,7 +13651,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13851,7 +13857,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -13929,7 +13935,7 @@
         <v>1.83</v>
       </c>
       <c r="AP63">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ63">
         <v>1.09</v>
@@ -14057,7 +14063,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14263,7 +14269,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14469,7 +14475,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14675,7 +14681,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14756,7 +14762,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR67">
         <v>1.18</v>
@@ -14881,7 +14887,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15168,7 +15174,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ69">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR69">
         <v>1.96</v>
@@ -15293,7 +15299,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15371,7 +15377,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ70">
         <v>1.27</v>
@@ -15705,7 +15711,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15911,7 +15917,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16323,7 +16329,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16816,7 +16822,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR77">
         <v>1.79</v>
@@ -17225,7 +17231,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ79">
         <v>1.27</v>
@@ -17353,7 +17359,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17434,7 +17440,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ80">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -17637,7 +17643,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ81">
         <v>1.08</v>
@@ -17765,7 +17771,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17971,7 +17977,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18177,7 +18183,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18589,7 +18595,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18670,7 +18676,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ86">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR86">
         <v>1.59</v>
@@ -18795,7 +18801,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18873,7 +18879,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ87">
         <v>1.08</v>
@@ -19001,7 +19007,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19079,7 +19085,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ88">
         <v>1.08</v>
@@ -19207,7 +19213,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19494,7 +19500,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR90">
         <v>1.63</v>
@@ -19619,7 +19625,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19825,7 +19831,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -19903,7 +19909,7 @@
         <v>0.89</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ92">
         <v>0.75</v>
@@ -20031,7 +20037,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20109,7 +20115,7 @@
         <v>0.89</v>
       </c>
       <c r="AP93">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ93">
         <v>0.75</v>
@@ -20237,7 +20243,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20443,7 +20449,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20730,7 +20736,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -21061,7 +21067,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21142,7 +21148,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR98">
         <v>1.13</v>
@@ -21348,7 +21354,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ99">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21473,7 +21479,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21757,7 +21763,7 @@
         <v>1.33</v>
       </c>
       <c r="AP101">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ101">
         <v>1.09</v>
@@ -22169,7 +22175,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ103">
         <v>1.09</v>
@@ -22503,7 +22509,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22709,7 +22715,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22915,7 +22921,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23121,7 +23127,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23327,7 +23333,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23614,7 +23620,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR110">
         <v>1.34</v>
@@ -23739,7 +23745,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -23817,10 +23823,10 @@
         <v>1.7</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ111">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24641,7 +24647,7 @@
         <v>0.82</v>
       </c>
       <c r="AP115">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ115">
         <v>0.75</v>
@@ -24975,7 +24981,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25132,6 +25138,418 @@
       </c>
       <c r="BP117">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7451085</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F118">
+        <v>24</v>
+      </c>
+      <c r="G118" t="s">
+        <v>71</v>
+      </c>
+      <c r="H118" t="s">
+        <v>72</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118" t="s">
+        <v>81</v>
+      </c>
+      <c r="P118" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q118">
+        <v>5</v>
+      </c>
+      <c r="R118">
+        <v>1.91</v>
+      </c>
+      <c r="S118">
+        <v>2.63</v>
+      </c>
+      <c r="T118">
+        <v>1.54</v>
+      </c>
+      <c r="U118">
+        <v>2.34</v>
+      </c>
+      <c r="V118">
+        <v>3.4</v>
+      </c>
+      <c r="W118">
+        <v>1.28</v>
+      </c>
+      <c r="X118">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y118">
+        <v>1.01</v>
+      </c>
+      <c r="Z118">
+        <v>4.1</v>
+      </c>
+      <c r="AA118">
+        <v>3</v>
+      </c>
+      <c r="AB118">
+        <v>1.9</v>
+      </c>
+      <c r="AC118">
+        <v>1.07</v>
+      </c>
+      <c r="AD118">
+        <v>7</v>
+      </c>
+      <c r="AE118">
+        <v>1.44</v>
+      </c>
+      <c r="AF118">
+        <v>2.6</v>
+      </c>
+      <c r="AG118">
+        <v>2.4</v>
+      </c>
+      <c r="AH118">
+        <v>1.5</v>
+      </c>
+      <c r="AI118">
+        <v>2.1</v>
+      </c>
+      <c r="AJ118">
+        <v>1.67</v>
+      </c>
+      <c r="AK118">
+        <v>1.82</v>
+      </c>
+      <c r="AL118">
+        <v>1.31</v>
+      </c>
+      <c r="AM118">
+        <v>1.21</v>
+      </c>
+      <c r="AN118">
+        <v>1.83</v>
+      </c>
+      <c r="AO118">
+        <v>1.82</v>
+      </c>
+      <c r="AP118">
+        <v>1.77</v>
+      </c>
+      <c r="AQ118">
+        <v>1.75</v>
+      </c>
+      <c r="AR118">
+        <v>1.07</v>
+      </c>
+      <c r="AS118">
+        <v>1.25</v>
+      </c>
+      <c r="AT118">
+        <v>2.32</v>
+      </c>
+      <c r="AU118">
+        <v>3</v>
+      </c>
+      <c r="AV118">
+        <v>0</v>
+      </c>
+      <c r="AW118">
+        <v>4</v>
+      </c>
+      <c r="AX118">
+        <v>8</v>
+      </c>
+      <c r="AY118">
+        <v>7</v>
+      </c>
+      <c r="AZ118">
+        <v>8</v>
+      </c>
+      <c r="BA118">
+        <v>2</v>
+      </c>
+      <c r="BB118">
+        <v>3</v>
+      </c>
+      <c r="BC118">
+        <v>5</v>
+      </c>
+      <c r="BD118">
+        <v>3.04</v>
+      </c>
+      <c r="BE118">
+        <v>8</v>
+      </c>
+      <c r="BF118">
+        <v>1.55</v>
+      </c>
+      <c r="BG118">
+        <v>1.5</v>
+      </c>
+      <c r="BH118">
+        <v>2.41</v>
+      </c>
+      <c r="BI118">
+        <v>1.87</v>
+      </c>
+      <c r="BJ118">
+        <v>1.87</v>
+      </c>
+      <c r="BK118">
+        <v>2.42</v>
+      </c>
+      <c r="BL118">
+        <v>1.53</v>
+      </c>
+      <c r="BM118">
+        <v>3.25</v>
+      </c>
+      <c r="BN118">
+        <v>1.29</v>
+      </c>
+      <c r="BO118">
+        <v>4.4</v>
+      </c>
+      <c r="BP118">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7451083</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45717.5625</v>
+      </c>
+      <c r="F119">
+        <v>24</v>
+      </c>
+      <c r="G119" t="s">
+        <v>73</v>
+      </c>
+      <c r="H119" t="s">
+        <v>79</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>2</v>
+      </c>
+      <c r="N119">
+        <v>3</v>
+      </c>
+      <c r="O119" t="s">
+        <v>161</v>
+      </c>
+      <c r="P119" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q119">
+        <v>2.49</v>
+      </c>
+      <c r="R119">
+        <v>2.25</v>
+      </c>
+      <c r="S119">
+        <v>4.41</v>
+      </c>
+      <c r="T119">
+        <v>1.36</v>
+      </c>
+      <c r="U119">
+        <v>3.02</v>
+      </c>
+      <c r="V119">
+        <v>2.82</v>
+      </c>
+      <c r="W119">
+        <v>1.4</v>
+      </c>
+      <c r="X119">
+        <v>6.8</v>
+      </c>
+      <c r="Y119">
+        <v>1.05</v>
+      </c>
+      <c r="Z119">
+        <v>1.87</v>
+      </c>
+      <c r="AA119">
+        <v>3.3</v>
+      </c>
+      <c r="AB119">
+        <v>4</v>
+      </c>
+      <c r="AC119">
+        <v>1.05</v>
+      </c>
+      <c r="AD119">
+        <v>7.8</v>
+      </c>
+      <c r="AE119">
+        <v>1.25</v>
+      </c>
+      <c r="AF119">
+        <v>3.5</v>
+      </c>
+      <c r="AG119">
+        <v>1.83</v>
+      </c>
+      <c r="AH119">
+        <v>1.85</v>
+      </c>
+      <c r="AI119">
+        <v>1.78</v>
+      </c>
+      <c r="AJ119">
+        <v>1.99</v>
+      </c>
+      <c r="AK119">
+        <v>1.23</v>
+      </c>
+      <c r="AL119">
+        <v>1.27</v>
+      </c>
+      <c r="AM119">
+        <v>1.9</v>
+      </c>
+      <c r="AN119">
+        <v>1.5</v>
+      </c>
+      <c r="AO119">
+        <v>1</v>
+      </c>
+      <c r="AP119">
+        <v>1.38</v>
+      </c>
+      <c r="AQ119">
+        <v>1.15</v>
+      </c>
+      <c r="AR119">
+        <v>1.57</v>
+      </c>
+      <c r="AS119">
+        <v>1.36</v>
+      </c>
+      <c r="AT119">
+        <v>2.93</v>
+      </c>
+      <c r="AU119">
+        <v>6</v>
+      </c>
+      <c r="AV119">
+        <v>6</v>
+      </c>
+      <c r="AW119">
+        <v>3</v>
+      </c>
+      <c r="AX119">
+        <v>4</v>
+      </c>
+      <c r="AY119">
+        <v>9</v>
+      </c>
+      <c r="AZ119">
+        <v>10</v>
+      </c>
+      <c r="BA119">
+        <v>3</v>
+      </c>
+      <c r="BB119">
+        <v>3</v>
+      </c>
+      <c r="BC119">
+        <v>6</v>
+      </c>
+      <c r="BD119">
+        <v>1.68</v>
+      </c>
+      <c r="BE119">
+        <v>7.85</v>
+      </c>
+      <c r="BF119">
+        <v>2.65</v>
+      </c>
+      <c r="BG119">
+        <v>1.39</v>
+      </c>
+      <c r="BH119">
+        <v>2.77</v>
+      </c>
+      <c r="BI119">
+        <v>1.68</v>
+      </c>
+      <c r="BJ119">
+        <v>2.12</v>
+      </c>
+      <c r="BK119">
+        <v>2.11</v>
+      </c>
+      <c r="BL119">
+        <v>1.68</v>
+      </c>
+      <c r="BM119">
+        <v>2.7</v>
+      </c>
+      <c r="BN119">
+        <v>1.41</v>
+      </c>
+      <c r="BO119">
+        <v>3.65</v>
+      </c>
+      <c r="BP119">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="223">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,9 @@
     <t>['25']</t>
   </si>
   <si>
+    <t>['5', '48']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -674,6 +677,12 @@
   </si>
   <si>
     <t>['78', '85']</t>
+  </si>
+  <si>
+    <t>['31', '90+1']</t>
+  </si>
+  <si>
+    <t>['10', '86']</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1369,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ2">
         <v>1.08</v>
@@ -1578,7 +1587,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ3">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1909,7 +1918,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2115,7 +2124,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2399,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ7">
         <v>1.15</v>
@@ -2733,7 +2742,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2814,7 +2823,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ9">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2939,7 +2948,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3429,7 +3438,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ12">
         <v>0.75</v>
@@ -3557,7 +3566,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3763,7 +3772,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3844,7 +3853,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ14">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR14">
         <v>1.27</v>
@@ -3969,7 +3978,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4793,7 +4802,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4871,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ19">
         <v>0.09</v>
@@ -4999,7 +5008,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5080,7 +5089,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR20">
         <v>1.92</v>
@@ -5205,7 +5214,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5411,7 +5420,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5617,7 +5626,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6110,7 +6119,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ25">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR25">
         <v>1.8</v>
@@ -6235,7 +6244,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6441,7 +6450,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6519,10 +6528,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR27">
         <v>1.84</v>
@@ -6647,7 +6656,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6853,7 +6862,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7343,10 +7352,10 @@
         <v>1.33</v>
       </c>
       <c r="AP31">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ31">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR31">
         <v>1.34</v>
@@ -7677,7 +7686,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7883,7 +7892,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8089,7 +8098,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8579,7 +8588,7 @@
         <v>0.75</v>
       </c>
       <c r="AP37">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
         <v>1.08</v>
@@ -8785,7 +8794,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ38">
         <v>1.08</v>
@@ -8994,7 +9003,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ39">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR39">
         <v>1.73</v>
@@ -9200,7 +9209,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ40">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR40">
         <v>1.7</v>
@@ -9325,7 +9334,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9531,7 +9540,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10149,7 +10158,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10561,7 +10570,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10767,7 +10776,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10845,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ48">
         <v>1.09</v>
@@ -10973,7 +10982,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11179,7 +11188,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11260,7 +11269,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ50">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR50">
         <v>1.52</v>
@@ -11591,7 +11600,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11797,7 +11806,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12084,7 +12093,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ54">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12209,7 +12218,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12287,7 +12296,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ55">
         <v>1.09</v>
@@ -12621,7 +12630,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12699,7 +12708,7 @@
         <v>1.6</v>
       </c>
       <c r="AP57">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ57">
         <v>1.09</v>
@@ -12827,7 +12836,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13239,7 +13248,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13526,7 +13535,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ61">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR61">
         <v>1.34</v>
@@ -13651,7 +13660,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13729,7 +13738,7 @@
         <v>0.8</v>
       </c>
       <c r="AP62">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ62">
         <v>1.08</v>
@@ -13857,7 +13866,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14063,7 +14072,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14269,7 +14278,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14350,7 +14359,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ65">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14475,7 +14484,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14681,7 +14690,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14887,7 +14896,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15171,7 +15180,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ69">
         <v>1.75</v>
@@ -15299,7 +15308,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15380,7 +15389,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ70">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR70">
         <v>1.61</v>
@@ -15583,7 +15592,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ71">
         <v>0.09</v>
@@ -15711,7 +15720,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15917,7 +15926,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16329,7 +16338,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16819,7 +16828,7 @@
         <v>0.86</v>
       </c>
       <c r="AP77">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ77">
         <v>1.15</v>
@@ -17028,7 +17037,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ78">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -17234,7 +17243,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR79">
         <v>1.09</v>
@@ -17359,7 +17368,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17437,7 +17446,7 @@
         <v>1.86</v>
       </c>
       <c r="AP80">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ80">
         <v>1.75</v>
@@ -17771,7 +17780,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17977,7 +17986,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18183,7 +18192,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18595,7 +18604,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18801,7 +18810,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19007,7 +19016,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19213,7 +19222,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19291,10 +19300,10 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR89">
         <v>1.93</v>
@@ -19625,7 +19634,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19703,10 +19712,10 @@
         <v>1.25</v>
       </c>
       <c r="AP91">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ91">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR91">
         <v>1.08</v>
@@ -19831,7 +19840,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20037,7 +20046,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20118,7 +20127,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ93">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR93">
         <v>1.14</v>
@@ -20243,7 +20252,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20321,7 +20330,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ94">
         <v>1.08</v>
@@ -20449,7 +20458,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21067,7 +21076,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21145,7 +21154,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ98">
         <v>1.15</v>
@@ -21479,7 +21488,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21560,7 +21569,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ100">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR100">
         <v>1.46</v>
@@ -21969,7 +21978,7 @@
         <v>0.9</v>
       </c>
       <c r="AP102">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ102">
         <v>0.75</v>
@@ -22384,7 +22393,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ104">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR104">
         <v>1.55</v>
@@ -22509,7 +22518,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22715,7 +22724,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22921,7 +22930,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -22999,7 +23008,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AQ107">
         <v>1.08</v>
@@ -23127,7 +23136,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23208,7 +23217,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ108">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR108">
         <v>1.28</v>
@@ -23333,7 +23342,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23411,7 +23420,7 @@
         <v>0.1</v>
       </c>
       <c r="AP109">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AQ109">
         <v>0.09</v>
@@ -23745,7 +23754,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -24032,7 +24041,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ112">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR112">
         <v>1.47</v>
@@ -24981,7 +24990,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25393,7 +25402,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25550,6 +25559,418 @@
       </c>
       <c r="BP119">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7451084</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F120">
+        <v>24</v>
+      </c>
+      <c r="G120" t="s">
+        <v>70</v>
+      </c>
+      <c r="H120" t="s">
+        <v>74</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>2</v>
+      </c>
+      <c r="L120">
+        <v>2</v>
+      </c>
+      <c r="M120">
+        <v>2</v>
+      </c>
+      <c r="N120">
+        <v>4</v>
+      </c>
+      <c r="O120" t="s">
+        <v>162</v>
+      </c>
+      <c r="P120" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q120">
+        <v>2.4</v>
+      </c>
+      <c r="R120">
+        <v>2.22</v>
+      </c>
+      <c r="S120">
+        <v>4.6</v>
+      </c>
+      <c r="T120">
+        <v>1.39</v>
+      </c>
+      <c r="U120">
+        <v>2.8</v>
+      </c>
+      <c r="V120">
+        <v>2.7</v>
+      </c>
+      <c r="W120">
+        <v>1.41</v>
+      </c>
+      <c r="X120">
+        <v>7.7</v>
+      </c>
+      <c r="Y120">
+        <v>1.03</v>
+      </c>
+      <c r="Z120">
+        <v>1.88</v>
+      </c>
+      <c r="AA120">
+        <v>3.1</v>
+      </c>
+      <c r="AB120">
+        <v>4</v>
+      </c>
+      <c r="AC120">
+        <v>1.03</v>
+      </c>
+      <c r="AD120">
+        <v>9</v>
+      </c>
+      <c r="AE120">
+        <v>1.29</v>
+      </c>
+      <c r="AF120">
+        <v>3.3</v>
+      </c>
+      <c r="AG120">
+        <v>1.91</v>
+      </c>
+      <c r="AH120">
+        <v>1.83</v>
+      </c>
+      <c r="AI120">
+        <v>1.76</v>
+      </c>
+      <c r="AJ120">
+        <v>1.96</v>
+      </c>
+      <c r="AK120">
+        <v>1.22</v>
+      </c>
+      <c r="AL120">
+        <v>1.29</v>
+      </c>
+      <c r="AM120">
+        <v>1.84</v>
+      </c>
+      <c r="AN120">
+        <v>2.17</v>
+      </c>
+      <c r="AO120">
+        <v>1.27</v>
+      </c>
+      <c r="AP120">
+        <v>2.08</v>
+      </c>
+      <c r="AQ120">
+        <v>1.25</v>
+      </c>
+      <c r="AR120">
+        <v>1.93</v>
+      </c>
+      <c r="AS120">
+        <v>1.46</v>
+      </c>
+      <c r="AT120">
+        <v>3.39</v>
+      </c>
+      <c r="AU120">
+        <v>5</v>
+      </c>
+      <c r="AV120">
+        <v>4</v>
+      </c>
+      <c r="AW120">
+        <v>2</v>
+      </c>
+      <c r="AX120">
+        <v>7</v>
+      </c>
+      <c r="AY120">
+        <v>7</v>
+      </c>
+      <c r="AZ120">
+        <v>11</v>
+      </c>
+      <c r="BA120">
+        <v>2</v>
+      </c>
+      <c r="BB120">
+        <v>2</v>
+      </c>
+      <c r="BC120">
+        <v>4</v>
+      </c>
+      <c r="BD120">
+        <v>1.59</v>
+      </c>
+      <c r="BE120">
+        <v>7.5</v>
+      </c>
+      <c r="BF120">
+        <v>2.91</v>
+      </c>
+      <c r="BG120">
+        <v>1.6</v>
+      </c>
+      <c r="BH120">
+        <v>2.25</v>
+      </c>
+      <c r="BI120">
+        <v>2.02</v>
+      </c>
+      <c r="BJ120">
+        <v>1.74</v>
+      </c>
+      <c r="BK120">
+        <v>2.6</v>
+      </c>
+      <c r="BL120">
+        <v>1.43</v>
+      </c>
+      <c r="BM120">
+        <v>3.55</v>
+      </c>
+      <c r="BN120">
+        <v>1.23</v>
+      </c>
+      <c r="BO120">
+        <v>4.95</v>
+      </c>
+      <c r="BP120">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7451081</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45718.57291666666</v>
+      </c>
+      <c r="F121">
+        <v>24</v>
+      </c>
+      <c r="G121" t="s">
+        <v>75</v>
+      </c>
+      <c r="H121" t="s">
+        <v>78</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>2</v>
+      </c>
+      <c r="N121">
+        <v>2</v>
+      </c>
+      <c r="O121" t="s">
+        <v>81</v>
+      </c>
+      <c r="P121" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q121">
+        <v>3.6</v>
+      </c>
+      <c r="R121">
+        <v>1.91</v>
+      </c>
+      <c r="S121">
+        <v>3.6</v>
+      </c>
+      <c r="T121">
+        <v>1.57</v>
+      </c>
+      <c r="U121">
+        <v>2.25</v>
+      </c>
+      <c r="V121">
+        <v>3.75</v>
+      </c>
+      <c r="W121">
+        <v>1.25</v>
+      </c>
+      <c r="X121">
+        <v>13</v>
+      </c>
+      <c r="Y121">
+        <v>1.04</v>
+      </c>
+      <c r="Z121">
+        <v>2.69</v>
+      </c>
+      <c r="AA121">
+        <v>3</v>
+      </c>
+      <c r="AB121">
+        <v>2.61</v>
+      </c>
+      <c r="AC121">
+        <v>1.05</v>
+      </c>
+      <c r="AD121">
+        <v>6.55</v>
+      </c>
+      <c r="AE121">
+        <v>1.46</v>
+      </c>
+      <c r="AF121">
+        <v>2.48</v>
+      </c>
+      <c r="AG121">
+        <v>2.6</v>
+      </c>
+      <c r="AH121">
+        <v>1.48</v>
+      </c>
+      <c r="AI121">
+        <v>2.1</v>
+      </c>
+      <c r="AJ121">
+        <v>1.67</v>
+      </c>
+      <c r="AK121">
+        <v>1.47</v>
+      </c>
+      <c r="AL121">
+        <v>1.34</v>
+      </c>
+      <c r="AM121">
+        <v>1.41</v>
+      </c>
+      <c r="AN121">
+        <v>0.82</v>
+      </c>
+      <c r="AO121">
+        <v>0.75</v>
+      </c>
+      <c r="AP121">
+        <v>0.75</v>
+      </c>
+      <c r="AQ121">
+        <v>0.92</v>
+      </c>
+      <c r="AR121">
+        <v>1.15</v>
+      </c>
+      <c r="AS121">
+        <v>1.33</v>
+      </c>
+      <c r="AT121">
+        <v>2.48</v>
+      </c>
+      <c r="AU121">
+        <v>2</v>
+      </c>
+      <c r="AV121">
+        <v>6</v>
+      </c>
+      <c r="AW121">
+        <v>8</v>
+      </c>
+      <c r="AX121">
+        <v>4</v>
+      </c>
+      <c r="AY121">
+        <v>10</v>
+      </c>
+      <c r="AZ121">
+        <v>10</v>
+      </c>
+      <c r="BA121">
+        <v>5</v>
+      </c>
+      <c r="BB121">
+        <v>3</v>
+      </c>
+      <c r="BC121">
+        <v>8</v>
+      </c>
+      <c r="BD121">
+        <v>2.29</v>
+      </c>
+      <c r="BE121">
+        <v>7.5</v>
+      </c>
+      <c r="BF121">
+        <v>1.85</v>
+      </c>
+      <c r="BG121">
+        <v>1.47</v>
+      </c>
+      <c r="BH121">
+        <v>2.5</v>
+      </c>
+      <c r="BI121">
+        <v>1.82</v>
+      </c>
+      <c r="BJ121">
+        <v>1.93</v>
+      </c>
+      <c r="BK121">
+        <v>2.34</v>
+      </c>
+      <c r="BL121">
+        <v>1.56</v>
+      </c>
+      <c r="BM121">
+        <v>3.02</v>
+      </c>
+      <c r="BN121">
+        <v>1.33</v>
+      </c>
+      <c r="BO121">
+        <v>4.2</v>
+      </c>
+      <c r="BP121">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -505,6 +505,9 @@
     <t>['5', '48']</t>
   </si>
   <si>
+    <t>['16']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -683,6 +686,9 @@
   </si>
   <si>
     <t>['10', '86']</t>
+  </si>
+  <si>
+    <t>['39']</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1790,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>1.08</v>
@@ -1918,7 +1924,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -1999,7 +2005,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ5">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2124,7 +2130,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2742,7 +2748,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2948,7 +2954,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3441,7 +3447,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ12">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR12">
         <v>2.03</v>
@@ -3566,7 +3572,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3772,7 +3778,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3978,7 +3984,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4262,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.08</v>
@@ -4471,7 +4477,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ17">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR17">
         <v>1.8</v>
@@ -4802,7 +4808,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -5008,7 +5014,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5214,7 +5220,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5420,7 +5426,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5501,7 +5507,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ22">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR22">
         <v>1.22</v>
@@ -5626,7 +5632,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6244,7 +6250,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6322,7 +6328,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
         <v>1.09</v>
@@ -6450,7 +6456,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6656,7 +6662,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6862,7 +6868,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7686,7 +7692,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7892,7 +7898,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8098,7 +8104,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8382,10 +8388,10 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR36">
         <v>1.6</v>
@@ -9206,7 +9212,7 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>1.25</v>
@@ -9334,7 +9340,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9540,7 +9546,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10158,7 +10164,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10445,7 +10451,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ46">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10570,7 +10576,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10776,7 +10782,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10982,7 +10988,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11188,7 +11194,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11600,7 +11606,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11681,7 +11687,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ52">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR52">
         <v>1.48</v>
@@ -11806,7 +11812,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12090,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
         <v>0.92</v>
@@ -12218,7 +12224,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12630,7 +12636,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12836,7 +12842,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13248,7 +13254,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13660,7 +13666,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13866,7 +13872,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14072,7 +14078,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14278,7 +14284,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14484,7 +14490,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14562,7 +14568,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>1.09</v>
@@ -14690,7 +14696,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14896,7 +14902,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15308,7 +15314,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15720,7 +15726,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15801,7 +15807,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ72">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR72">
         <v>1.34</v>
@@ -15926,7 +15932,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16210,7 +16216,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
         <v>0.09</v>
@@ -16338,7 +16344,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -17368,7 +17374,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17780,7 +17786,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17986,7 +17992,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18192,7 +18198,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18273,7 +18279,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ84">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR84">
         <v>1.2</v>
@@ -18604,7 +18610,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18810,7 +18816,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19016,7 +19022,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19222,7 +19228,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19506,7 +19512,7 @@
         <v>0.88</v>
       </c>
       <c r="AP90">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>1.15</v>
@@ -19634,7 +19640,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19840,7 +19846,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -19921,7 +19927,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ92">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR92">
         <v>1.57</v>
@@ -20046,7 +20052,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20252,7 +20258,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20458,7 +20464,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20536,7 +20542,7 @@
         <v>1.22</v>
       </c>
       <c r="AP95">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
         <v>1.08</v>
@@ -21076,7 +21082,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21488,7 +21494,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21981,7 +21987,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ102">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR102">
         <v>1.92</v>
@@ -22518,7 +22524,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22596,7 +22602,7 @@
         <v>0.9</v>
       </c>
       <c r="AP105">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>1.08</v>
@@ -22724,7 +22730,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22930,7 +22936,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23136,7 +23142,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23342,7 +23348,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23754,7 +23760,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -24450,7 +24456,7 @@
         <v>1.2</v>
       </c>
       <c r="AP114">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
         <v>1.09</v>
@@ -24659,7 +24665,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ115">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AR115">
         <v>1.11</v>
@@ -24990,7 +24996,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25402,7 +25408,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25608,7 +25614,7 @@
         <v>162</v>
       </c>
       <c r="P120" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25814,7 +25820,7 @@
         <v>81</v>
       </c>
       <c r="P121" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q121">
         <v>3.6</v>
@@ -25971,6 +25977,212 @@
       </c>
       <c r="BP121">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7451086</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45723.58333333334</v>
+      </c>
+      <c r="F122">
+        <v>25</v>
+      </c>
+      <c r="G122" t="s">
+        <v>72</v>
+      </c>
+      <c r="H122" t="s">
+        <v>75</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>2</v>
+      </c>
+      <c r="O122" t="s">
+        <v>163</v>
+      </c>
+      <c r="P122" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q122">
+        <v>1.77</v>
+      </c>
+      <c r="R122">
+        <v>2.3</v>
+      </c>
+      <c r="S122">
+        <v>7.5</v>
+      </c>
+      <c r="T122">
+        <v>1.38</v>
+      </c>
+      <c r="U122">
+        <v>2.8</v>
+      </c>
+      <c r="V122">
+        <v>2.85</v>
+      </c>
+      <c r="W122">
+        <v>1.41</v>
+      </c>
+      <c r="X122">
+        <v>6</v>
+      </c>
+      <c r="Y122">
+        <v>1.08</v>
+      </c>
+      <c r="Z122">
+        <v>1.35</v>
+      </c>
+      <c r="AA122">
+        <v>5</v>
+      </c>
+      <c r="AB122">
+        <v>9.4</v>
+      </c>
+      <c r="AC122">
+        <v>1.03</v>
+      </c>
+      <c r="AD122">
+        <v>9</v>
+      </c>
+      <c r="AE122">
+        <v>1.3</v>
+      </c>
+      <c r="AF122">
+        <v>3.3</v>
+      </c>
+      <c r="AG122">
+        <v>1.95</v>
+      </c>
+      <c r="AH122">
+        <v>1.8</v>
+      </c>
+      <c r="AI122">
+        <v>2.4</v>
+      </c>
+      <c r="AJ122">
+        <v>1.5</v>
+      </c>
+      <c r="AK122">
+        <v>1.17</v>
+      </c>
+      <c r="AL122">
+        <v>1.18</v>
+      </c>
+      <c r="AM122">
+        <v>3.3</v>
+      </c>
+      <c r="AN122">
+        <v>2.08</v>
+      </c>
+      <c r="AO122">
+        <v>0.75</v>
+      </c>
+      <c r="AP122">
+        <v>2</v>
+      </c>
+      <c r="AQ122">
+        <v>0.77</v>
+      </c>
+      <c r="AR122">
+        <v>1.67</v>
+      </c>
+      <c r="AS122">
+        <v>1.06</v>
+      </c>
+      <c r="AT122">
+        <v>2.73</v>
+      </c>
+      <c r="AU122">
+        <v>7</v>
+      </c>
+      <c r="AV122">
+        <v>4</v>
+      </c>
+      <c r="AW122">
+        <v>8</v>
+      </c>
+      <c r="AX122">
+        <v>5</v>
+      </c>
+      <c r="AY122">
+        <v>15</v>
+      </c>
+      <c r="AZ122">
+        <v>9</v>
+      </c>
+      <c r="BA122">
+        <v>9</v>
+      </c>
+      <c r="BB122">
+        <v>1</v>
+      </c>
+      <c r="BC122">
+        <v>10</v>
+      </c>
+      <c r="BD122">
+        <v>1.14</v>
+      </c>
+      <c r="BE122">
+        <v>11.75</v>
+      </c>
+      <c r="BF122">
+        <v>6.85</v>
+      </c>
+      <c r="BG122">
+        <v>1.35</v>
+      </c>
+      <c r="BH122">
+        <v>2.84</v>
+      </c>
+      <c r="BI122">
+        <v>1.66</v>
+      </c>
+      <c r="BJ122">
+        <v>2.09</v>
+      </c>
+      <c r="BK122">
+        <v>2.09</v>
+      </c>
+      <c r="BL122">
+        <v>1.63</v>
+      </c>
+      <c r="BM122">
+        <v>2.74</v>
+      </c>
+      <c r="BN122">
+        <v>1.35</v>
+      </c>
+      <c r="BO122">
+        <v>3.6</v>
+      </c>
+      <c r="BP122">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>['16']</t>
+  </si>
+  <si>
+    <t>['22', '82', '90+5']</t>
   </si>
   <si>
     <t>['8', '61']</t>
@@ -1050,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1924,7 +1927,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2130,7 +2133,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2748,7 +2751,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2826,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ9">
         <v>1.25</v>
@@ -2954,7 +2957,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3238,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ11">
         <v>1.75</v>
@@ -3572,7 +3575,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3778,7 +3781,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3984,7 +3987,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4065,7 +4068,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ15">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0.6899999999999999</v>
@@ -4474,7 +4477,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ17">
         <v>0.77</v>
@@ -4680,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ18">
         <v>1.15</v>
@@ -4808,7 +4811,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -5014,7 +5017,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5220,7 +5223,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5426,7 +5429,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5632,7 +5635,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5919,7 +5922,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ24">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.41</v>
@@ -6122,7 +6125,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ25">
         <v>0.92</v>
@@ -6250,7 +6253,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6456,7 +6459,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6662,7 +6665,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6868,7 +6871,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7564,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ32">
         <v>1.08</v>
@@ -7692,7 +7695,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7898,7 +7901,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8104,7 +8107,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8182,10 +8185,10 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ35">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.65</v>
@@ -9340,7 +9343,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9546,7 +9549,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9627,7 +9630,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ42">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -9830,7 +9833,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ43">
         <v>0.09</v>
@@ -10164,7 +10167,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10242,7 +10245,7 @@
         <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ45">
         <v>1.09</v>
@@ -10576,7 +10579,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10654,7 +10657,7 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ47">
         <v>1.75</v>
@@ -10782,7 +10785,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10863,7 +10866,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ48">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.2</v>
@@ -10988,7 +10991,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11194,7 +11197,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11478,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ51">
         <v>0.09</v>
@@ -11606,7 +11609,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11812,7 +11815,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12224,7 +12227,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12305,7 +12308,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ55">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.97</v>
@@ -12636,7 +12639,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12842,7 +12845,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12920,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ58">
         <v>1.15</v>
@@ -13254,7 +13257,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13538,7 +13541,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ61">
         <v>1.25</v>
@@ -13666,7 +13669,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13872,7 +13875,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14078,7 +14081,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14284,7 +14287,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14490,7 +14493,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14571,7 +14574,7 @@
         <v>2</v>
       </c>
       <c r="AQ66">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.64</v>
@@ -14696,7 +14699,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14902,7 +14905,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14980,7 +14983,7 @@
         <v>1.17</v>
       </c>
       <c r="AP68">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ68">
         <v>1.08</v>
@@ -15314,7 +15317,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15726,7 +15729,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15804,7 +15807,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ72">
         <v>0.77</v>
@@ -15932,7 +15935,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16013,7 +16016,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ73">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16344,7 +16347,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16422,7 +16425,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ75">
         <v>1.08</v>
@@ -17374,7 +17377,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17786,7 +17789,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17992,7 +17995,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18070,7 +18073,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ83">
         <v>1.09</v>
@@ -18198,7 +18201,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18482,10 +18485,10 @@
         <v>1.38</v>
       </c>
       <c r="AP85">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ85">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -18610,7 +18613,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18816,7 +18819,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19022,7 +19025,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19228,7 +19231,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19640,7 +19643,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19846,7 +19849,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20052,7 +20055,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20258,7 +20261,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20464,7 +20467,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21082,7 +21085,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21366,7 +21369,7 @@
         <v>1.89</v>
       </c>
       <c r="AP99">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ99">
         <v>1.75</v>
@@ -21494,7 +21497,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21572,7 +21575,7 @@
         <v>1.44</v>
       </c>
       <c r="AP100">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ100">
         <v>1.25</v>
@@ -22193,7 +22196,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ103">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.14</v>
@@ -22524,7 +22527,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22730,7 +22733,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22936,7 +22939,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23142,7 +23145,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23348,7 +23351,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23632,7 +23635,7 @@
         <v>0.82</v>
       </c>
       <c r="AP110">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ110">
         <v>1.15</v>
@@ -23760,7 +23763,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -24044,7 +24047,7 @@
         <v>0.82</v>
       </c>
       <c r="AP112">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ112">
         <v>0.92</v>
@@ -24253,7 +24256,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ113">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.48</v>
@@ -24996,7 +24999,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25408,7 +25411,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25614,7 +25617,7 @@
         <v>162</v>
       </c>
       <c r="P120" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25820,7 +25823,7 @@
         <v>81</v>
       </c>
       <c r="P121" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q121">
         <v>3.6</v>
@@ -26026,7 +26029,7 @@
         <v>163</v>
       </c>
       <c r="P122" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q122">
         <v>1.77</v>
@@ -26183,6 +26186,418 @@
       </c>
       <c r="BP122">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7451090</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F123">
+        <v>25</v>
+      </c>
+      <c r="G123" t="s">
+        <v>78</v>
+      </c>
+      <c r="H123" t="s">
+        <v>76</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123" t="s">
+        <v>81</v>
+      </c>
+      <c r="P123" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q123">
+        <v>3.1</v>
+      </c>
+      <c r="R123">
+        <v>1.83</v>
+      </c>
+      <c r="S123">
+        <v>4</v>
+      </c>
+      <c r="T123">
+        <v>1.57</v>
+      </c>
+      <c r="U123">
+        <v>2.33</v>
+      </c>
+      <c r="V123">
+        <v>3.66</v>
+      </c>
+      <c r="W123">
+        <v>1.22</v>
+      </c>
+      <c r="X123">
+        <v>10</v>
+      </c>
+      <c r="Y123">
+        <v>1.03</v>
+      </c>
+      <c r="Z123">
+        <v>2.4</v>
+      </c>
+      <c r="AA123">
+        <v>2.65</v>
+      </c>
+      <c r="AB123">
+        <v>3.4</v>
+      </c>
+      <c r="AC123">
+        <v>1.08</v>
+      </c>
+      <c r="AD123">
+        <v>6.5</v>
+      </c>
+      <c r="AE123">
+        <v>1.45</v>
+      </c>
+      <c r="AF123">
+        <v>2.55</v>
+      </c>
+      <c r="AG123">
+        <v>2.55</v>
+      </c>
+      <c r="AH123">
+        <v>1.45</v>
+      </c>
+      <c r="AI123">
+        <v>2.1</v>
+      </c>
+      <c r="AJ123">
+        <v>1.67</v>
+      </c>
+      <c r="AK123">
+        <v>1.33</v>
+      </c>
+      <c r="AL123">
+        <v>1.36</v>
+      </c>
+      <c r="AM123">
+        <v>1.56</v>
+      </c>
+      <c r="AN123">
+        <v>1.91</v>
+      </c>
+      <c r="AO123">
+        <v>1.08</v>
+      </c>
+      <c r="AP123">
+        <v>1.83</v>
+      </c>
+      <c r="AQ123">
+        <v>1.08</v>
+      </c>
+      <c r="AR123">
+        <v>1.35</v>
+      </c>
+      <c r="AS123">
+        <v>1</v>
+      </c>
+      <c r="AT123">
+        <v>2.35</v>
+      </c>
+      <c r="AU123">
+        <v>5</v>
+      </c>
+      <c r="AV123">
+        <v>2</v>
+      </c>
+      <c r="AW123">
+        <v>6</v>
+      </c>
+      <c r="AX123">
+        <v>3</v>
+      </c>
+      <c r="AY123">
+        <v>11</v>
+      </c>
+      <c r="AZ123">
+        <v>5</v>
+      </c>
+      <c r="BA123">
+        <v>1</v>
+      </c>
+      <c r="BB123">
+        <v>4</v>
+      </c>
+      <c r="BC123">
+        <v>5</v>
+      </c>
+      <c r="BD123">
+        <v>1.75</v>
+      </c>
+      <c r="BE123">
+        <v>6.2</v>
+      </c>
+      <c r="BF123">
+        <v>2.68</v>
+      </c>
+      <c r="BG123">
+        <v>1.45</v>
+      </c>
+      <c r="BH123">
+        <v>2.48</v>
+      </c>
+      <c r="BI123">
+        <v>1.83</v>
+      </c>
+      <c r="BJ123">
+        <v>1.87</v>
+      </c>
+      <c r="BK123">
+        <v>2.38</v>
+      </c>
+      <c r="BL123">
+        <v>1.49</v>
+      </c>
+      <c r="BM123">
+        <v>3.2</v>
+      </c>
+      <c r="BN123">
+        <v>1.26</v>
+      </c>
+      <c r="BO123">
+        <v>4.4</v>
+      </c>
+      <c r="BP123">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7451089</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45724.5625</v>
+      </c>
+      <c r="F124">
+        <v>25</v>
+      </c>
+      <c r="G124" t="s">
+        <v>77</v>
+      </c>
+      <c r="H124" t="s">
+        <v>73</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>3</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>3</v>
+      </c>
+      <c r="O124" t="s">
+        <v>164</v>
+      </c>
+      <c r="P124" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q124">
+        <v>2.75</v>
+      </c>
+      <c r="R124">
+        <v>2.1</v>
+      </c>
+      <c r="S124">
+        <v>3.75</v>
+      </c>
+      <c r="T124">
+        <v>1.36</v>
+      </c>
+      <c r="U124">
+        <v>2.95</v>
+      </c>
+      <c r="V124">
+        <v>2.84</v>
+      </c>
+      <c r="W124">
+        <v>1.38</v>
+      </c>
+      <c r="X124">
+        <v>6.9</v>
+      </c>
+      <c r="Y124">
+        <v>1.04</v>
+      </c>
+      <c r="Z124">
+        <v>2.1</v>
+      </c>
+      <c r="AA124">
+        <v>3.25</v>
+      </c>
+      <c r="AB124">
+        <v>3.2</v>
+      </c>
+      <c r="AC124">
+        <v>1.03</v>
+      </c>
+      <c r="AD124">
+        <v>9</v>
+      </c>
+      <c r="AE124">
+        <v>1.25</v>
+      </c>
+      <c r="AF124">
+        <v>3.6</v>
+      </c>
+      <c r="AG124">
+        <v>1.85</v>
+      </c>
+      <c r="AH124">
+        <v>1.85</v>
+      </c>
+      <c r="AI124">
+        <v>1.67</v>
+      </c>
+      <c r="AJ124">
+        <v>2.1</v>
+      </c>
+      <c r="AK124">
+        <v>1.3</v>
+      </c>
+      <c r="AL124">
+        <v>1.28</v>
+      </c>
+      <c r="AM124">
+        <v>1.71</v>
+      </c>
+      <c r="AN124">
+        <v>1.27</v>
+      </c>
+      <c r="AO124">
+        <v>1.09</v>
+      </c>
+      <c r="AP124">
+        <v>1.42</v>
+      </c>
+      <c r="AQ124">
+        <v>1</v>
+      </c>
+      <c r="AR124">
+        <v>1.51</v>
+      </c>
+      <c r="AS124">
+        <v>1.34</v>
+      </c>
+      <c r="AT124">
+        <v>2.85</v>
+      </c>
+      <c r="AU124">
+        <v>8</v>
+      </c>
+      <c r="AV124">
+        <v>5</v>
+      </c>
+      <c r="AW124">
+        <v>11</v>
+      </c>
+      <c r="AX124">
+        <v>3</v>
+      </c>
+      <c r="AY124">
+        <v>19</v>
+      </c>
+      <c r="AZ124">
+        <v>8</v>
+      </c>
+      <c r="BA124">
+        <v>6</v>
+      </c>
+      <c r="BB124">
+        <v>2</v>
+      </c>
+      <c r="BC124">
+        <v>8</v>
+      </c>
+      <c r="BD124">
+        <v>1.66</v>
+      </c>
+      <c r="BE124">
+        <v>6.55</v>
+      </c>
+      <c r="BF124">
+        <v>2.85</v>
+      </c>
+      <c r="BG124">
+        <v>1.24</v>
+      </c>
+      <c r="BH124">
+        <v>3.34</v>
+      </c>
+      <c r="BI124">
+        <v>1.48</v>
+      </c>
+      <c r="BJ124">
+        <v>2.4</v>
+      </c>
+      <c r="BK124">
+        <v>1.85</v>
+      </c>
+      <c r="BL124">
+        <v>1.85</v>
+      </c>
+      <c r="BM124">
+        <v>2.38</v>
+      </c>
+      <c r="BN124">
+        <v>1.49</v>
+      </c>
+      <c r="BO124">
+        <v>3.14</v>
+      </c>
+      <c r="BP124">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -511,6 +511,9 @@
     <t>['22', '82', '90+5']</t>
   </si>
   <si>
+    <t>['22', '68']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -692,6 +695,12 @@
   </si>
   <si>
     <t>['39']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['18']</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP124"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1927,7 +1936,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2133,7 +2142,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2211,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ6">
         <v>1.15</v>
@@ -2626,7 +2635,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ8">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2751,7 +2760,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2957,7 +2966,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3038,7 +3047,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ10">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR10">
         <v>3.14</v>
@@ -3575,7 +3584,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3653,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ13">
         <v>1.08</v>
@@ -3781,7 +3790,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3859,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ14">
         <v>0.92</v>
@@ -3987,7 +3996,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4811,7 +4820,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4892,7 +4901,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ19">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -5017,7 +5026,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5223,7 +5232,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5429,7 +5438,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5635,7 +5644,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5713,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ23">
         <v>1.08</v>
@@ -5919,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6253,7 +6262,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6334,7 +6343,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR26">
         <v>1.71</v>
@@ -6459,7 +6468,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6665,7 +6674,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6871,7 +6880,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7695,7 +7704,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7773,10 +7782,10 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ33">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -7901,7 +7910,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -7979,10 +7988,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ34">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR34">
         <v>1.39</v>
@@ -8107,7 +8116,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -9343,7 +9352,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9549,7 +9558,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9836,7 +9845,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ43">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR43">
         <v>1.56</v>
@@ -10039,7 +10048,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ44">
         <v>1.75</v>
@@ -10167,7 +10176,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10248,7 +10257,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ45">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR45">
         <v>1.19</v>
@@ -10451,7 +10460,7 @@
         <v>1.2</v>
       </c>
       <c r="AP46">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ46">
         <v>0.77</v>
@@ -10579,7 +10588,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10785,7 +10794,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10991,7 +11000,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11072,7 +11081,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ49">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11197,7 +11206,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11275,7 +11284,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ50">
         <v>1.25</v>
@@ -11484,7 +11493,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ51">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR51">
         <v>1.18</v>
@@ -11609,7 +11618,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11687,7 +11696,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ52">
         <v>0.77</v>
@@ -11815,7 +11824,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11893,7 +11902,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ53">
         <v>1.08</v>
@@ -12227,7 +12236,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12639,7 +12648,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12720,7 +12729,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ57">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR57">
         <v>1.11</v>
@@ -12845,7 +12854,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13132,7 +13141,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ59">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13257,7 +13266,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13669,7 +13678,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13875,7 +13884,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -13956,7 +13965,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ63">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
         <v>1.18</v>
@@ -14081,7 +14090,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14159,7 +14168,7 @@
         <v>0.67</v>
       </c>
       <c r="AP64">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ64">
         <v>1.08</v>
@@ -14287,7 +14296,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14365,7 +14374,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ65">
         <v>0.92</v>
@@ -14493,7 +14502,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14699,7 +14708,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14905,7 +14914,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15317,7 +15326,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15604,7 +15613,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ71">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR71">
         <v>0.93</v>
@@ -15729,7 +15738,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15935,7 +15944,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16013,7 +16022,7 @@
         <v>1.57</v>
       </c>
       <c r="AP73">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16222,7 +16231,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -16347,7 +16356,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16631,10 +16640,10 @@
         <v>1.71</v>
       </c>
       <c r="AP76">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ76">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR76">
         <v>1.66</v>
@@ -17377,7 +17386,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17789,7 +17798,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17867,10 +17876,10 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ82">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR82">
         <v>1.53</v>
@@ -17995,7 +18004,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18076,7 +18085,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ83">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR83">
         <v>1.51</v>
@@ -18201,7 +18210,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18613,7 +18622,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18691,7 +18700,7 @@
         <v>2</v>
       </c>
       <c r="AP86">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ86">
         <v>1.75</v>
@@ -18819,7 +18828,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19025,7 +19034,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19231,7 +19240,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19643,7 +19652,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19849,7 +19858,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20055,7 +20064,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20261,7 +20270,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20467,7 +20476,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20751,7 +20760,7 @@
         <v>0.78</v>
       </c>
       <c r="AP96">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ96">
         <v>1.15</v>
@@ -20960,7 +20969,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ97">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR97">
         <v>1.22</v>
@@ -21085,7 +21094,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21497,7 +21506,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21784,7 +21793,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ101">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR101">
         <v>1.55</v>
@@ -22399,7 +22408,7 @@
         <v>0.9</v>
       </c>
       <c r="AP104">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ104">
         <v>0.92</v>
@@ -22527,7 +22536,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22733,7 +22742,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22811,7 +22820,7 @@
         <v>1.1</v>
       </c>
       <c r="AP106">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ106">
         <v>1.08</v>
@@ -22939,7 +22948,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23145,7 +23154,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23351,7 +23360,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23432,7 +23441,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ109">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR109">
         <v>1.9</v>
@@ -23763,7 +23772,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -24253,7 +24262,7 @@
         <v>1.2</v>
       </c>
       <c r="AP113">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -24462,7 +24471,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR114">
         <v>1.68</v>
@@ -24871,7 +24880,7 @@
         <v>1.09</v>
       </c>
       <c r="AP116">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ116">
         <v>1.08</v>
@@ -24999,7 +25008,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25411,7 +25420,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25617,7 +25626,7 @@
         <v>162</v>
       </c>
       <c r="P120" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25823,7 +25832,7 @@
         <v>81</v>
       </c>
       <c r="P121" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q121">
         <v>3.6</v>
@@ -26029,7 +26038,7 @@
         <v>163</v>
       </c>
       <c r="P122" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q122">
         <v>1.77</v>
@@ -26598,6 +26607,418 @@
       </c>
       <c r="BP124">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7451087</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F125">
+        <v>25</v>
+      </c>
+      <c r="G125" t="s">
+        <v>74</v>
+      </c>
+      <c r="H125" t="s">
+        <v>71</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>2</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>3</v>
+      </c>
+      <c r="O125" t="s">
+        <v>165</v>
+      </c>
+      <c r="P125" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q125">
+        <v>1.91</v>
+      </c>
+      <c r="R125">
+        <v>2.2</v>
+      </c>
+      <c r="S125">
+        <v>7</v>
+      </c>
+      <c r="T125">
+        <v>1.39</v>
+      </c>
+      <c r="U125">
+        <v>2.88</v>
+      </c>
+      <c r="V125">
+        <v>2.99</v>
+      </c>
+      <c r="W125">
+        <v>1.36</v>
+      </c>
+      <c r="X125">
+        <v>7.5</v>
+      </c>
+      <c r="Y125">
+        <v>1.03</v>
+      </c>
+      <c r="Z125">
+        <v>1.42</v>
+      </c>
+      <c r="AA125">
+        <v>4.27</v>
+      </c>
+      <c r="AB125">
+        <v>7.22</v>
+      </c>
+      <c r="AC125">
+        <v>1.03</v>
+      </c>
+      <c r="AD125">
+        <v>9</v>
+      </c>
+      <c r="AE125">
+        <v>1.29</v>
+      </c>
+      <c r="AF125">
+        <v>3.3</v>
+      </c>
+      <c r="AG125">
+        <v>1.99</v>
+      </c>
+      <c r="AH125">
+        <v>1.81</v>
+      </c>
+      <c r="AI125">
+        <v>2.1</v>
+      </c>
+      <c r="AJ125">
+        <v>1.67</v>
+      </c>
+      <c r="AK125">
+        <v>1.07</v>
+      </c>
+      <c r="AL125">
+        <v>1.2</v>
+      </c>
+      <c r="AM125">
+        <v>2.74</v>
+      </c>
+      <c r="AN125">
+        <v>2.5</v>
+      </c>
+      <c r="AO125">
+        <v>0.09</v>
+      </c>
+      <c r="AP125">
+        <v>2.54</v>
+      </c>
+      <c r="AQ125">
+        <v>0.08</v>
+      </c>
+      <c r="AR125">
+        <v>1.5</v>
+      </c>
+      <c r="AS125">
+        <v>0.91</v>
+      </c>
+      <c r="AT125">
+        <v>2.41</v>
+      </c>
+      <c r="AU125">
+        <v>5</v>
+      </c>
+      <c r="AV125">
+        <v>4</v>
+      </c>
+      <c r="AW125">
+        <v>1</v>
+      </c>
+      <c r="AX125">
+        <v>4</v>
+      </c>
+      <c r="AY125">
+        <v>6</v>
+      </c>
+      <c r="AZ125">
+        <v>8</v>
+      </c>
+      <c r="BA125">
+        <v>5</v>
+      </c>
+      <c r="BB125">
+        <v>4</v>
+      </c>
+      <c r="BC125">
+        <v>9</v>
+      </c>
+      <c r="BD125">
+        <v>1.27</v>
+      </c>
+      <c r="BE125">
+        <v>9.5</v>
+      </c>
+      <c r="BF125">
+        <v>4.7</v>
+      </c>
+      <c r="BG125">
+        <v>1.39</v>
+      </c>
+      <c r="BH125">
+        <v>2.67</v>
+      </c>
+      <c r="BI125">
+        <v>1.72</v>
+      </c>
+      <c r="BJ125">
+        <v>2</v>
+      </c>
+      <c r="BK125">
+        <v>2.19</v>
+      </c>
+      <c r="BL125">
+        <v>1.57</v>
+      </c>
+      <c r="BM125">
+        <v>2.92</v>
+      </c>
+      <c r="BN125">
+        <v>1.31</v>
+      </c>
+      <c r="BO125">
+        <v>3.9</v>
+      </c>
+      <c r="BP125">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7451088</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45725.5625</v>
+      </c>
+      <c r="F126">
+        <v>25</v>
+      </c>
+      <c r="G126" t="s">
+        <v>79</v>
+      </c>
+      <c r="H126" t="s">
+        <v>70</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>81</v>
+      </c>
+      <c r="P126" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q126">
+        <v>4.33</v>
+      </c>
+      <c r="R126">
+        <v>2.3</v>
+      </c>
+      <c r="S126">
+        <v>2.25</v>
+      </c>
+      <c r="T126">
+        <v>1.32</v>
+      </c>
+      <c r="U126">
+        <v>3.23</v>
+      </c>
+      <c r="V126">
+        <v>2.41</v>
+      </c>
+      <c r="W126">
+        <v>1.53</v>
+      </c>
+      <c r="X126">
+        <v>5.7</v>
+      </c>
+      <c r="Y126">
+        <v>1.08</v>
+      </c>
+      <c r="Z126">
+        <v>4.92</v>
+      </c>
+      <c r="AA126">
+        <v>3.64</v>
+      </c>
+      <c r="AB126">
+        <v>1.68</v>
+      </c>
+      <c r="AC126">
+        <v>1.01</v>
+      </c>
+      <c r="AD126">
+        <v>13</v>
+      </c>
+      <c r="AE126">
+        <v>1.14</v>
+      </c>
+      <c r="AF126">
+        <v>4.8</v>
+      </c>
+      <c r="AG126">
+        <v>1.57</v>
+      </c>
+      <c r="AH126">
+        <v>2.25</v>
+      </c>
+      <c r="AI126">
+        <v>1.57</v>
+      </c>
+      <c r="AJ126">
+        <v>2.25</v>
+      </c>
+      <c r="AK126">
+        <v>2.11</v>
+      </c>
+      <c r="AL126">
+        <v>1.22</v>
+      </c>
+      <c r="AM126">
+        <v>1.19</v>
+      </c>
+      <c r="AN126">
+        <v>1.55</v>
+      </c>
+      <c r="AO126">
+        <v>1.09</v>
+      </c>
+      <c r="AP126">
+        <v>1.42</v>
+      </c>
+      <c r="AQ126">
+        <v>1.25</v>
+      </c>
+      <c r="AR126">
+        <v>1.57</v>
+      </c>
+      <c r="AS126">
+        <v>1.75</v>
+      </c>
+      <c r="AT126">
+        <v>3.32</v>
+      </c>
+      <c r="AU126">
+        <v>0</v>
+      </c>
+      <c r="AV126">
+        <v>7</v>
+      </c>
+      <c r="AW126">
+        <v>3</v>
+      </c>
+      <c r="AX126">
+        <v>11</v>
+      </c>
+      <c r="AY126">
+        <v>3</v>
+      </c>
+      <c r="AZ126">
+        <v>18</v>
+      </c>
+      <c r="BA126">
+        <v>1</v>
+      </c>
+      <c r="BB126">
+        <v>11</v>
+      </c>
+      <c r="BC126">
+        <v>12</v>
+      </c>
+      <c r="BD126">
+        <v>3.1</v>
+      </c>
+      <c r="BE126">
+        <v>8.6</v>
+      </c>
+      <c r="BF126">
+        <v>1.5</v>
+      </c>
+      <c r="BG126">
+        <v>1.28</v>
+      </c>
+      <c r="BH126">
+        <v>3.08</v>
+      </c>
+      <c r="BI126">
+        <v>1.54</v>
+      </c>
+      <c r="BJ126">
+        <v>2.25</v>
+      </c>
+      <c r="BK126">
+        <v>1.95</v>
+      </c>
+      <c r="BL126">
+        <v>1.76</v>
+      </c>
+      <c r="BM126">
+        <v>2.54</v>
+      </c>
+      <c r="BN126">
+        <v>1.43</v>
+      </c>
+      <c r="BO126">
+        <v>3.42</v>
+      </c>
+      <c r="BP126">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="230">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -702,6 +702,9 @@
   <si>
     <t>['18']</t>
   </si>
+  <si>
+    <t>['45+3', '45+6', '81']</t>
+  </si>
 </sst>
 </file>
 
@@ -1062,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1602,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ3">
         <v>0.92</v>
@@ -2223,7 +2226,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ6">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2429,7 +2432,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ7">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -4074,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4695,7 +4698,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ18">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR18">
         <v>0.8100000000000001</v>
@@ -5516,7 +5519,7 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ22">
         <v>0.77</v>
@@ -6958,7 +6961,7 @@
         <v>2</v>
       </c>
       <c r="AP29">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ29">
         <v>1.75</v>
@@ -7167,7 +7170,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ30">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR30">
         <v>1.82</v>
@@ -9430,10 +9433,10 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ41">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR41">
         <v>1.08</v>
@@ -12520,7 +12523,7 @@
         <v>0.8</v>
       </c>
       <c r="AP56">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ56">
         <v>1.08</v>
@@ -12935,7 +12938,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ58">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR58">
         <v>1.49</v>
@@ -13962,7 +13965,7 @@
         <v>1.83</v>
       </c>
       <c r="AP63">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ63">
         <v>1.25</v>
@@ -14789,7 +14792,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ67">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR67">
         <v>1.18</v>
@@ -16849,7 +16852,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ77">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR77">
         <v>1.79</v>
@@ -17258,7 +17261,7 @@
         <v>1.43</v>
       </c>
       <c r="AP79">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ79">
         <v>1.25</v>
@@ -19112,7 +19115,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ88">
         <v>1.08</v>
@@ -19527,7 +19530,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR90">
         <v>1.63</v>
@@ -20142,7 +20145,7 @@
         <v>0.89</v>
       </c>
       <c r="AP93">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ93">
         <v>0.92</v>
@@ -20763,7 +20766,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ96">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR96">
         <v>1.54</v>
@@ -21175,7 +21178,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ98">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR98">
         <v>1.13</v>
@@ -22202,7 +22205,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ103">
         <v>1</v>
@@ -23647,7 +23650,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ110">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR110">
         <v>1.34</v>
@@ -24674,7 +24677,7 @@
         <v>0.82</v>
       </c>
       <c r="AP115">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ115">
         <v>0.77</v>
@@ -25292,7 +25295,7 @@
         <v>1.82</v>
       </c>
       <c r="AP118">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ118">
         <v>1.75</v>
@@ -25501,7 +25504,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ119">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR119">
         <v>1.57</v>
@@ -27019,6 +27022,212 @@
       </c>
       <c r="BP126">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7451094</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45730.58333333334</v>
+      </c>
+      <c r="F127">
+        <v>26</v>
+      </c>
+      <c r="G127" t="s">
+        <v>71</v>
+      </c>
+      <c r="H127" t="s">
+        <v>79</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>2</v>
+      </c>
+      <c r="K127">
+        <v>2</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>3</v>
+      </c>
+      <c r="N127">
+        <v>3</v>
+      </c>
+      <c r="O127" t="s">
+        <v>81</v>
+      </c>
+      <c r="P127" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q127">
+        <v>3.3</v>
+      </c>
+      <c r="R127">
+        <v>1.98</v>
+      </c>
+      <c r="S127">
+        <v>3.2</v>
+      </c>
+      <c r="T127">
+        <v>1.44</v>
+      </c>
+      <c r="U127">
+        <v>2.55</v>
+      </c>
+      <c r="V127">
+        <v>3</v>
+      </c>
+      <c r="W127">
+        <v>1.34</v>
+      </c>
+      <c r="X127">
+        <v>8</v>
+      </c>
+      <c r="Y127">
+        <v>1.07</v>
+      </c>
+      <c r="Z127">
+        <v>2.98</v>
+      </c>
+      <c r="AA127">
+        <v>2.83</v>
+      </c>
+      <c r="AB127">
+        <v>2.51</v>
+      </c>
+      <c r="AC127">
+        <v>1.07</v>
+      </c>
+      <c r="AD127">
+        <v>7.5</v>
+      </c>
+      <c r="AE127">
+        <v>1.36</v>
+      </c>
+      <c r="AF127">
+        <v>2.95</v>
+      </c>
+      <c r="AG127">
+        <v>2.1</v>
+      </c>
+      <c r="AH127">
+        <v>1.67</v>
+      </c>
+      <c r="AI127">
+        <v>1.85</v>
+      </c>
+      <c r="AJ127">
+        <v>1.83</v>
+      </c>
+      <c r="AK127">
+        <v>1.47</v>
+      </c>
+      <c r="AL127">
+        <v>1.33</v>
+      </c>
+      <c r="AM127">
+        <v>1.43</v>
+      </c>
+      <c r="AN127">
+        <v>1.77</v>
+      </c>
+      <c r="AO127">
+        <v>1.15</v>
+      </c>
+      <c r="AP127">
+        <v>1.64</v>
+      </c>
+      <c r="AQ127">
+        <v>1.29</v>
+      </c>
+      <c r="AR127">
+        <v>1.05</v>
+      </c>
+      <c r="AS127">
+        <v>1.38</v>
+      </c>
+      <c r="AT127">
+        <v>2.43</v>
+      </c>
+      <c r="AU127">
+        <v>0</v>
+      </c>
+      <c r="AV127">
+        <v>7</v>
+      </c>
+      <c r="AW127">
+        <v>5</v>
+      </c>
+      <c r="AX127">
+        <v>3</v>
+      </c>
+      <c r="AY127">
+        <v>5</v>
+      </c>
+      <c r="AZ127">
+        <v>10</v>
+      </c>
+      <c r="BA127">
+        <v>4</v>
+      </c>
+      <c r="BB127">
+        <v>3</v>
+      </c>
+      <c r="BC127">
+        <v>7</v>
+      </c>
+      <c r="BD127">
+        <v>2.53</v>
+      </c>
+      <c r="BE127">
+        <v>7.5</v>
+      </c>
+      <c r="BF127">
+        <v>1.75</v>
+      </c>
+      <c r="BG127">
+        <v>1.43</v>
+      </c>
+      <c r="BH127">
+        <v>2.63</v>
+      </c>
+      <c r="BI127">
+        <v>1.74</v>
+      </c>
+      <c r="BJ127">
+        <v>2.02</v>
+      </c>
+      <c r="BK127">
+        <v>2.22</v>
+      </c>
+      <c r="BL127">
+        <v>1.62</v>
+      </c>
+      <c r="BM127">
+        <v>2.85</v>
+      </c>
+      <c r="BN127">
+        <v>1.37</v>
+      </c>
+      <c r="BO127">
+        <v>3.9</v>
+      </c>
+      <c r="BP127">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -512,6 +512,12 @@
   </si>
   <si>
     <t>['22', '68']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['14', '33', '61']</t>
   </si>
   <si>
     <t>['8', '61']</t>
@@ -1065,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP127"/>
+  <dimension ref="A1:BP129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1399,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ2">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1814,7 +1820,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1939,7 +1945,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2145,7 +2151,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2429,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ7">
         <v>1.29</v>
@@ -2763,7 +2769,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2969,7 +2975,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3459,7 +3465,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ12">
         <v>0.77</v>
@@ -3587,7 +3593,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3668,7 +3674,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ13">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3793,7 +3799,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3999,7 +4005,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4286,7 +4292,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>1.93</v>
@@ -4823,7 +4829,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4901,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ19">
         <v>0.08</v>
@@ -5029,7 +5035,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5235,7 +5241,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5441,7 +5447,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5647,7 +5653,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5728,7 +5734,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ23">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -6265,7 +6271,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6471,7 +6477,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6549,7 +6555,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ27">
         <v>1.25</v>
@@ -6677,7 +6683,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6758,7 +6764,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>1.45</v>
@@ -6883,7 +6889,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7373,7 +7379,7 @@
         <v>1.33</v>
       </c>
       <c r="AP31">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ31">
         <v>0.92</v>
@@ -7582,7 +7588,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ32">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.2</v>
@@ -7707,7 +7713,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7913,7 +7919,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8119,7 +8125,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8609,10 +8615,10 @@
         <v>0.75</v>
       </c>
       <c r="AP37">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ37">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>1.04</v>
@@ -8815,10 +8821,10 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ38">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.94</v>
@@ -9355,7 +9361,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9561,7 +9567,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10179,7 +10185,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10591,7 +10597,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10797,7 +10803,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10875,7 +10881,7 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11003,7 +11009,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11209,7 +11215,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11621,7 +11627,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11827,7 +11833,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11908,7 +11914,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ53">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR53">
         <v>1.65</v>
@@ -12239,7 +12245,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12317,7 +12323,7 @@
         <v>1.4</v>
       </c>
       <c r="AP55">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -12526,7 +12532,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ56">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.17</v>
@@ -12651,7 +12657,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12729,7 +12735,7 @@
         <v>1.6</v>
       </c>
       <c r="AP57">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ57">
         <v>1.25</v>
@@ -12857,7 +12863,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13269,7 +13275,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13681,7 +13687,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13759,10 +13765,10 @@
         <v>0.8</v>
       </c>
       <c r="AP62">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ62">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>0.93</v>
@@ -13887,7 +13893,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14093,7 +14099,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14174,7 +14180,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ64">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR64">
         <v>1.63</v>
@@ -14299,7 +14305,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14505,7 +14511,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14711,7 +14717,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14917,7 +14923,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -14998,7 +15004,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ68">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.39</v>
@@ -15201,7 +15207,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ69">
         <v>1.75</v>
@@ -15329,7 +15335,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15613,7 +15619,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ71">
         <v>0.08</v>
@@ -15741,7 +15747,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15947,7 +15953,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16359,7 +16365,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16440,7 +16446,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ75">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.54</v>
@@ -16849,7 +16855,7 @@
         <v>0.86</v>
       </c>
       <c r="AP77">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ77">
         <v>1.29</v>
@@ -17389,7 +17395,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17467,7 +17473,7 @@
         <v>1.86</v>
       </c>
       <c r="AP80">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ80">
         <v>1.75</v>
@@ -17676,7 +17682,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ81">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR81">
         <v>1.59</v>
@@ -17801,7 +17807,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -18007,7 +18013,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18213,7 +18219,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18625,7 +18631,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18831,7 +18837,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18912,7 +18918,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ87">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR87">
         <v>1.57</v>
@@ -19037,7 +19043,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19118,7 +19124,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ88">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.12</v>
@@ -19243,7 +19249,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19321,7 +19327,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ89">
         <v>0.92</v>
@@ -19655,7 +19661,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19733,7 +19739,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ91">
         <v>1.25</v>
@@ -19861,7 +19867,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20067,7 +20073,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20273,7 +20279,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20351,10 +20357,10 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ94">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.89</v>
@@ -20479,7 +20485,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20560,7 +20566,7 @@
         <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -21097,7 +21103,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21175,7 +21181,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ98">
         <v>1.29</v>
@@ -21509,7 +21515,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21999,7 +22005,7 @@
         <v>0.9</v>
       </c>
       <c r="AP102">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ102">
         <v>0.77</v>
@@ -22539,7 +22545,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22620,7 +22626,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR105">
         <v>1.66</v>
@@ -22745,7 +22751,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22826,7 +22832,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ106">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.58</v>
@@ -22951,7 +22957,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23029,10 +23035,10 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ107">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR107">
         <v>1.16</v>
@@ -23157,7 +23163,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23363,7 +23369,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23441,7 +23447,7 @@
         <v>0.1</v>
       </c>
       <c r="AP109">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ109">
         <v>0.08</v>
@@ -23775,7 +23781,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -24886,7 +24892,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ116">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR116">
         <v>1.57</v>
@@ -25011,7 +25017,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25092,7 +25098,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ117">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR117">
         <v>1.26</v>
@@ -25423,7 +25429,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25629,7 +25635,7 @@
         <v>162</v>
       </c>
       <c r="P120" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25707,7 +25713,7 @@
         <v>1.27</v>
       </c>
       <c r="AP120">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ120">
         <v>1.25</v>
@@ -25835,7 +25841,7 @@
         <v>81</v>
       </c>
       <c r="P121" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q121">
         <v>3.6</v>
@@ -25913,7 +25919,7 @@
         <v>0.75</v>
       </c>
       <c r="AP121">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AQ121">
         <v>0.92</v>
@@ -26041,7 +26047,7 @@
         <v>163</v>
       </c>
       <c r="P122" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q122">
         <v>1.77</v>
@@ -26328,7 +26334,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ123">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR123">
         <v>1.35</v>
@@ -26659,7 +26665,7 @@
         <v>165</v>
       </c>
       <c r="P125" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q125">
         <v>1.91</v>
@@ -26865,7 +26871,7 @@
         <v>81</v>
       </c>
       <c r="P126" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27071,7 +27077,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q127">
         <v>3.3</v>
@@ -27228,6 +27234,418 @@
       </c>
       <c r="BP127">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7451091</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F128">
+        <v>26</v>
+      </c>
+      <c r="G128" t="s">
+        <v>75</v>
+      </c>
+      <c r="H128" t="s">
+        <v>76</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>166</v>
+      </c>
+      <c r="P128" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q128">
+        <v>3.75</v>
+      </c>
+      <c r="R128">
+        <v>1.95</v>
+      </c>
+      <c r="S128">
+        <v>3.4</v>
+      </c>
+      <c r="T128">
+        <v>1.57</v>
+      </c>
+      <c r="U128">
+        <v>2.25</v>
+      </c>
+      <c r="V128">
+        <v>3.75</v>
+      </c>
+      <c r="W128">
+        <v>1.25</v>
+      </c>
+      <c r="X128">
+        <v>11</v>
+      </c>
+      <c r="Y128">
+        <v>1.05</v>
+      </c>
+      <c r="Z128">
+        <v>2.8</v>
+      </c>
+      <c r="AA128">
+        <v>2.87</v>
+      </c>
+      <c r="AB128">
+        <v>2.4</v>
+      </c>
+      <c r="AC128">
+        <v>1.1</v>
+      </c>
+      <c r="AD128">
+        <v>6.25</v>
+      </c>
+      <c r="AE128">
+        <v>1.5</v>
+      </c>
+      <c r="AF128">
+        <v>2.5</v>
+      </c>
+      <c r="AG128">
+        <v>2.4</v>
+      </c>
+      <c r="AH128">
+        <v>1.5</v>
+      </c>
+      <c r="AI128">
+        <v>2.1</v>
+      </c>
+      <c r="AJ128">
+        <v>1.67</v>
+      </c>
+      <c r="AK128">
+        <v>1.5</v>
+      </c>
+      <c r="AL128">
+        <v>1.37</v>
+      </c>
+      <c r="AM128">
+        <v>1.38</v>
+      </c>
+      <c r="AN128">
+        <v>0.75</v>
+      </c>
+      <c r="AO128">
+        <v>1.08</v>
+      </c>
+      <c r="AP128">
+        <v>0.92</v>
+      </c>
+      <c r="AQ128">
+        <v>1</v>
+      </c>
+      <c r="AR128">
+        <v>1.18</v>
+      </c>
+      <c r="AS128">
+        <v>0.99</v>
+      </c>
+      <c r="AT128">
+        <v>2.17</v>
+      </c>
+      <c r="AU128">
+        <v>3</v>
+      </c>
+      <c r="AV128">
+        <v>3</v>
+      </c>
+      <c r="AW128">
+        <v>5</v>
+      </c>
+      <c r="AX128">
+        <v>7</v>
+      </c>
+      <c r="AY128">
+        <v>8</v>
+      </c>
+      <c r="AZ128">
+        <v>10</v>
+      </c>
+      <c r="BA128">
+        <v>4</v>
+      </c>
+      <c r="BB128">
+        <v>3</v>
+      </c>
+      <c r="BC128">
+        <v>7</v>
+      </c>
+      <c r="BD128">
+        <v>2.07</v>
+      </c>
+      <c r="BE128">
+        <v>6.1</v>
+      </c>
+      <c r="BF128">
+        <v>2.18</v>
+      </c>
+      <c r="BG128">
+        <v>1.42</v>
+      </c>
+      <c r="BH128">
+        <v>2.57</v>
+      </c>
+      <c r="BI128">
+        <v>1.78</v>
+      </c>
+      <c r="BJ128">
+        <v>1.93</v>
+      </c>
+      <c r="BK128">
+        <v>2.3</v>
+      </c>
+      <c r="BL128">
+        <v>1.52</v>
+      </c>
+      <c r="BM128">
+        <v>3.08</v>
+      </c>
+      <c r="BN128">
+        <v>1.28</v>
+      </c>
+      <c r="BO128">
+        <v>4.15</v>
+      </c>
+      <c r="BP128">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7451093</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45731.5625</v>
+      </c>
+      <c r="F129">
+        <v>26</v>
+      </c>
+      <c r="G129" t="s">
+        <v>70</v>
+      </c>
+      <c r="H129" t="s">
+        <v>77</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>3</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>3</v>
+      </c>
+      <c r="O129" t="s">
+        <v>167</v>
+      </c>
+      <c r="P129" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q129">
+        <v>1.95</v>
+      </c>
+      <c r="R129">
+        <v>2.4</v>
+      </c>
+      <c r="S129">
+        <v>6</v>
+      </c>
+      <c r="T129">
+        <v>1.3</v>
+      </c>
+      <c r="U129">
+        <v>3.4</v>
+      </c>
+      <c r="V129">
+        <v>2.5</v>
+      </c>
+      <c r="W129">
+        <v>1.5</v>
+      </c>
+      <c r="X129">
+        <v>6</v>
+      </c>
+      <c r="Y129">
+        <v>1.13</v>
+      </c>
+      <c r="Z129">
+        <v>1.44</v>
+      </c>
+      <c r="AA129">
+        <v>4.33</v>
+      </c>
+      <c r="AB129">
+        <v>5.5</v>
+      </c>
+      <c r="AC129">
+        <v>1.03</v>
+      </c>
+      <c r="AD129">
+        <v>10</v>
+      </c>
+      <c r="AE129">
+        <v>1.18</v>
+      </c>
+      <c r="AF129">
+        <v>4.5</v>
+      </c>
+      <c r="AG129">
+        <v>1.61</v>
+      </c>
+      <c r="AH129">
+        <v>2.15</v>
+      </c>
+      <c r="AI129">
+        <v>1.8</v>
+      </c>
+      <c r="AJ129">
+        <v>1.91</v>
+      </c>
+      <c r="AK129">
+        <v>1.13</v>
+      </c>
+      <c r="AL129">
+        <v>1.19</v>
+      </c>
+      <c r="AM129">
+        <v>2.6</v>
+      </c>
+      <c r="AN129">
+        <v>2.08</v>
+      </c>
+      <c r="AO129">
+        <v>1.08</v>
+      </c>
+      <c r="AP129">
+        <v>2.14</v>
+      </c>
+      <c r="AQ129">
+        <v>1</v>
+      </c>
+      <c r="AR129">
+        <v>1.87</v>
+      </c>
+      <c r="AS129">
+        <v>1.6</v>
+      </c>
+      <c r="AT129">
+        <v>3.47</v>
+      </c>
+      <c r="AU129">
+        <v>9</v>
+      </c>
+      <c r="AV129">
+        <v>2</v>
+      </c>
+      <c r="AW129">
+        <v>15</v>
+      </c>
+      <c r="AX129">
+        <v>4</v>
+      </c>
+      <c r="AY129">
+        <v>24</v>
+      </c>
+      <c r="AZ129">
+        <v>6</v>
+      </c>
+      <c r="BA129">
+        <v>11</v>
+      </c>
+      <c r="BB129">
+        <v>2</v>
+      </c>
+      <c r="BC129">
+        <v>13</v>
+      </c>
+      <c r="BD129">
+        <v>1.32</v>
+      </c>
+      <c r="BE129">
+        <v>9.6</v>
+      </c>
+      <c r="BF129">
+        <v>4.1</v>
+      </c>
+      <c r="BG129">
+        <v>1.22</v>
+      </c>
+      <c r="BH129">
+        <v>3.5</v>
+      </c>
+      <c r="BI129">
+        <v>1.44</v>
+      </c>
+      <c r="BJ129">
+        <v>2.51</v>
+      </c>
+      <c r="BK129">
+        <v>1.79</v>
+      </c>
+      <c r="BL129">
+        <v>1.92</v>
+      </c>
+      <c r="BM129">
+        <v>2.28</v>
+      </c>
+      <c r="BN129">
+        <v>1.53</v>
+      </c>
+      <c r="BO129">
+        <v>2.97</v>
+      </c>
+      <c r="BP129">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -518,6 +518,9 @@
   </si>
   <si>
     <t>['14', '33', '61']</t>
+  </si>
+  <si>
+    <t>['25', '35', '88']</t>
   </si>
   <si>
     <t>['8', '61']</t>
@@ -1071,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP129"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1614,7 +1617,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ3">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1817,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ4">
         <v>1</v>
@@ -1945,7 +1948,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2023,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ5">
         <v>0.77</v>
@@ -2151,7 +2154,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2769,7 +2772,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2850,7 +2853,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ9">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2975,7 +2978,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3053,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ10">
         <v>1.25</v>
@@ -3593,7 +3596,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3799,7 +3802,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3880,7 +3883,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ14">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR14">
         <v>1.27</v>
@@ -4005,7 +4008,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4289,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4829,7 +4832,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -5035,7 +5038,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5116,7 +5119,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ20">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR20">
         <v>1.92</v>
@@ -5241,7 +5244,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5319,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ21">
         <v>1.75</v>
@@ -5447,7 +5450,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5653,7 +5656,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -6146,7 +6149,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ25">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR25">
         <v>1.8</v>
@@ -6271,7 +6274,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6349,7 +6352,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ26">
         <v>1.25</v>
@@ -6477,7 +6480,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6558,7 +6561,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ27">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR27">
         <v>1.84</v>
@@ -6683,7 +6686,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6889,7 +6892,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7173,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ30">
         <v>1.29</v>
@@ -7382,7 +7385,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ31">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR31">
         <v>1.34</v>
@@ -7713,7 +7716,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7919,7 +7922,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8125,7 +8128,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8409,7 +8412,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ36">
         <v>0.77</v>
@@ -9027,10 +9030,10 @@
         <v>1.25</v>
       </c>
       <c r="AP39">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ39">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR39">
         <v>1.73</v>
@@ -9233,10 +9236,10 @@
         <v>1.67</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ40">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR40">
         <v>1.7</v>
@@ -9361,7 +9364,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9567,7 +9570,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10185,7 +10188,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10597,7 +10600,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10803,7 +10806,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -11009,7 +11012,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11215,7 +11218,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11296,7 +11299,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ50">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR50">
         <v>1.52</v>
@@ -11627,7 +11630,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11833,7 +11836,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12117,10 +12120,10 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ54">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12245,7 +12248,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12657,7 +12660,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12863,7 +12866,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13147,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>0.08</v>
@@ -13275,7 +13278,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13562,7 +13565,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ61">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR61">
         <v>1.34</v>
@@ -13687,7 +13690,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13893,7 +13896,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14099,7 +14102,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14305,7 +14308,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14386,7 +14389,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ65">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR65">
         <v>1.5</v>
@@ -14511,7 +14514,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14589,7 +14592,7 @@
         <v>1.67</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ66">
         <v>1</v>
@@ -14717,7 +14720,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14923,7 +14926,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15335,7 +15338,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15413,10 +15416,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ70">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR70">
         <v>1.61</v>
@@ -15747,7 +15750,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15953,7 +15956,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16237,7 +16240,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ74">
         <v>0.08</v>
@@ -16365,7 +16368,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -17064,7 +17067,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ78">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -17270,7 +17273,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ79">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR79">
         <v>1.09</v>
@@ -17395,7 +17398,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17679,7 +17682,7 @@
         <v>1.14</v>
       </c>
       <c r="AP81">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ81">
         <v>1</v>
@@ -17807,7 +17810,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -18013,7 +18016,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18219,7 +18222,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18631,7 +18634,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18837,7 +18840,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -18915,7 +18918,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ87">
         <v>1</v>
@@ -19043,7 +19046,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19249,7 +19252,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19330,7 +19333,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ89">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR89">
         <v>1.93</v>
@@ -19533,7 +19536,7 @@
         <v>0.88</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ90">
         <v>1.29</v>
@@ -19661,7 +19664,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19742,7 +19745,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ91">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR91">
         <v>1.08</v>
@@ -19867,7 +19870,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -19945,7 +19948,7 @@
         <v>0.89</v>
       </c>
       <c r="AP92">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ92">
         <v>0.77</v>
@@ -20073,7 +20076,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20154,7 +20157,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ93">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR93">
         <v>1.14</v>
@@ -20279,7 +20282,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20485,7 +20488,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20563,7 +20566,7 @@
         <v>1.22</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ95">
         <v>1</v>
@@ -21103,7 +21106,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21515,7 +21518,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21596,7 +21599,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ100">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR100">
         <v>1.46</v>
@@ -21799,7 +21802,7 @@
         <v>1.33</v>
       </c>
       <c r="AP101">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ101">
         <v>1.25</v>
@@ -22420,7 +22423,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ104">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR104">
         <v>1.55</v>
@@ -22545,7 +22548,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22623,7 +22626,7 @@
         <v>0.9</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ105">
         <v>1</v>
@@ -22751,7 +22754,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22957,7 +22960,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23163,7 +23166,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23244,7 +23247,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ108">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR108">
         <v>1.28</v>
@@ -23369,7 +23372,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23781,7 +23784,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -23859,7 +23862,7 @@
         <v>1.7</v>
       </c>
       <c r="AP111">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ111">
         <v>1.75</v>
@@ -24068,7 +24071,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ112">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR112">
         <v>1.47</v>
@@ -24477,7 +24480,7 @@
         <v>1.2</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ114">
         <v>1.25</v>
@@ -25017,7 +25020,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25429,7 +25432,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25507,7 +25510,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ119">
         <v>1.29</v>
@@ -25635,7 +25638,7 @@
         <v>162</v>
       </c>
       <c r="P120" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25716,7 +25719,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ120">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR120">
         <v>1.93</v>
@@ -25841,7 +25844,7 @@
         <v>81</v>
       </c>
       <c r="P121" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q121">
         <v>3.6</v>
@@ -25922,7 +25925,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ121">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR121">
         <v>1.15</v>
@@ -26047,7 +26050,7 @@
         <v>163</v>
       </c>
       <c r="P122" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q122">
         <v>1.77</v>
@@ -26125,7 +26128,7 @@
         <v>0.75</v>
       </c>
       <c r="AP122">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ122">
         <v>0.77</v>
@@ -26665,7 +26668,7 @@
         <v>165</v>
       </c>
       <c r="P125" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q125">
         <v>1.91</v>
@@ -26871,7 +26874,7 @@
         <v>81</v>
       </c>
       <c r="P126" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27077,7 +27080,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q127">
         <v>3.3</v>
@@ -27646,6 +27649,418 @@
       </c>
       <c r="BP129">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7451092</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45732.45833333334</v>
+      </c>
+      <c r="F130">
+        <v>26</v>
+      </c>
+      <c r="G130" t="s">
+        <v>73</v>
+      </c>
+      <c r="H130" t="s">
+        <v>78</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130" t="s">
+        <v>81</v>
+      </c>
+      <c r="P130" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q130">
+        <v>2.6</v>
+      </c>
+      <c r="R130">
+        <v>2.05</v>
+      </c>
+      <c r="S130">
+        <v>4.75</v>
+      </c>
+      <c r="T130">
+        <v>1.5</v>
+      </c>
+      <c r="U130">
+        <v>2.5</v>
+      </c>
+      <c r="V130">
+        <v>3.4</v>
+      </c>
+      <c r="W130">
+        <v>1.3</v>
+      </c>
+      <c r="X130">
+        <v>10</v>
+      </c>
+      <c r="Y130">
+        <v>1.06</v>
+      </c>
+      <c r="Z130">
+        <v>1.88</v>
+      </c>
+      <c r="AA130">
+        <v>2.94</v>
+      </c>
+      <c r="AB130">
+        <v>5.03</v>
+      </c>
+      <c r="AC130">
+        <v>1.07</v>
+      </c>
+      <c r="AD130">
+        <v>7.5</v>
+      </c>
+      <c r="AE130">
+        <v>1.4</v>
+      </c>
+      <c r="AF130">
+        <v>2.8</v>
+      </c>
+      <c r="AG130">
+        <v>2.2</v>
+      </c>
+      <c r="AH130">
+        <v>1.63</v>
+      </c>
+      <c r="AI130">
+        <v>2</v>
+      </c>
+      <c r="AJ130">
+        <v>1.73</v>
+      </c>
+      <c r="AK130">
+        <v>1.22</v>
+      </c>
+      <c r="AL130">
+        <v>1.3</v>
+      </c>
+      <c r="AM130">
+        <v>1.87</v>
+      </c>
+      <c r="AN130">
+        <v>1.38</v>
+      </c>
+      <c r="AO130">
+        <v>0.92</v>
+      </c>
+      <c r="AP130">
+        <v>1.36</v>
+      </c>
+      <c r="AQ130">
+        <v>0.93</v>
+      </c>
+      <c r="AR130">
+        <v>1.57</v>
+      </c>
+      <c r="AS130">
+        <v>1.33</v>
+      </c>
+      <c r="AT130">
+        <v>2.9</v>
+      </c>
+      <c r="AU130">
+        <v>3</v>
+      </c>
+      <c r="AV130">
+        <v>3</v>
+      </c>
+      <c r="AW130">
+        <v>9</v>
+      </c>
+      <c r="AX130">
+        <v>5</v>
+      </c>
+      <c r="AY130">
+        <v>12</v>
+      </c>
+      <c r="AZ130">
+        <v>8</v>
+      </c>
+      <c r="BA130">
+        <v>7</v>
+      </c>
+      <c r="BB130">
+        <v>4</v>
+      </c>
+      <c r="BC130">
+        <v>11</v>
+      </c>
+      <c r="BD130">
+        <v>1.68</v>
+      </c>
+      <c r="BE130">
+        <v>6.25</v>
+      </c>
+      <c r="BF130">
+        <v>2.85</v>
+      </c>
+      <c r="BG130">
+        <v>1.43</v>
+      </c>
+      <c r="BH130">
+        <v>2.54</v>
+      </c>
+      <c r="BI130">
+        <v>1.79</v>
+      </c>
+      <c r="BJ130">
+        <v>1.92</v>
+      </c>
+      <c r="BK130">
+        <v>2.3</v>
+      </c>
+      <c r="BL130">
+        <v>1.52</v>
+      </c>
+      <c r="BM130">
+        <v>3.08</v>
+      </c>
+      <c r="BN130">
+        <v>1.28</v>
+      </c>
+      <c r="BO130">
+        <v>4.1</v>
+      </c>
+      <c r="BP130">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7451095</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45732.57291666666</v>
+      </c>
+      <c r="F131">
+        <v>26</v>
+      </c>
+      <c r="G131" t="s">
+        <v>72</v>
+      </c>
+      <c r="H131" t="s">
+        <v>74</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131">
+        <v>3</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>3</v>
+      </c>
+      <c r="O131" t="s">
+        <v>168</v>
+      </c>
+      <c r="P131" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q131">
+        <v>3.1</v>
+      </c>
+      <c r="R131">
+        <v>1.91</v>
+      </c>
+      <c r="S131">
+        <v>4.33</v>
+      </c>
+      <c r="T131">
+        <v>1.62</v>
+      </c>
+      <c r="U131">
+        <v>2.2</v>
+      </c>
+      <c r="V131">
+        <v>4</v>
+      </c>
+      <c r="W131">
+        <v>1.22</v>
+      </c>
+      <c r="X131">
+        <v>13</v>
+      </c>
+      <c r="Y131">
+        <v>1.04</v>
+      </c>
+      <c r="Z131">
+        <v>2.42</v>
+      </c>
+      <c r="AA131">
+        <v>2.58</v>
+      </c>
+      <c r="AB131">
+        <v>3.79</v>
+      </c>
+      <c r="AC131">
+        <v>1.11</v>
+      </c>
+      <c r="AD131">
+        <v>6</v>
+      </c>
+      <c r="AE131">
+        <v>1.5</v>
+      </c>
+      <c r="AF131">
+        <v>2.5</v>
+      </c>
+      <c r="AG131">
+        <v>2.6</v>
+      </c>
+      <c r="AH131">
+        <v>1.48</v>
+      </c>
+      <c r="AI131">
+        <v>2.25</v>
+      </c>
+      <c r="AJ131">
+        <v>1.57</v>
+      </c>
+      <c r="AK131">
+        <v>1.27</v>
+      </c>
+      <c r="AL131">
+        <v>1.35</v>
+      </c>
+      <c r="AM131">
+        <v>1.66</v>
+      </c>
+      <c r="AN131">
+        <v>2</v>
+      </c>
+      <c r="AO131">
+        <v>1.25</v>
+      </c>
+      <c r="AP131">
+        <v>2.07</v>
+      </c>
+      <c r="AQ131">
+        <v>1.15</v>
+      </c>
+      <c r="AR131">
+        <v>1.7</v>
+      </c>
+      <c r="AS131">
+        <v>1.46</v>
+      </c>
+      <c r="AT131">
+        <v>3.16</v>
+      </c>
+      <c r="AU131">
+        <v>7</v>
+      </c>
+      <c r="AV131">
+        <v>3</v>
+      </c>
+      <c r="AW131">
+        <v>5</v>
+      </c>
+      <c r="AX131">
+        <v>7</v>
+      </c>
+      <c r="AY131">
+        <v>12</v>
+      </c>
+      <c r="AZ131">
+        <v>10</v>
+      </c>
+      <c r="BA131">
+        <v>4</v>
+      </c>
+      <c r="BB131">
+        <v>2</v>
+      </c>
+      <c r="BC131">
+        <v>6</v>
+      </c>
+      <c r="BD131">
+        <v>1.5</v>
+      </c>
+      <c r="BE131">
+        <v>6.55</v>
+      </c>
+      <c r="BF131">
+        <v>3.5</v>
+      </c>
+      <c r="BG131">
+        <v>1.52</v>
+      </c>
+      <c r="BH131">
+        <v>2.3</v>
+      </c>
+      <c r="BI131">
+        <v>1.94</v>
+      </c>
+      <c r="BJ131">
+        <v>1.77</v>
+      </c>
+      <c r="BK131">
+        <v>2.57</v>
+      </c>
+      <c r="BL131">
+        <v>1.42</v>
+      </c>
+      <c r="BM131">
+        <v>3.5</v>
+      </c>
+      <c r="BN131">
+        <v>1.22</v>
+      </c>
+      <c r="BO131">
+        <v>4.7</v>
+      </c>
+      <c r="BP131">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="237">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -523,6 +523,15 @@
     <t>['25', '35', '88']</t>
   </si>
   <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['45', '90+3']</t>
+  </si>
+  <si>
+    <t>['64', '76']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -713,6 +722,9 @@
   </si>
   <si>
     <t>['45+3', '45+6', '81']</t>
+  </si>
+  <si>
+    <t>['68']</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1948,7 +1960,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2154,7 +2166,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2644,10 +2656,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ8">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2772,7 +2784,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2850,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
         <v>1.15</v>
@@ -2978,7 +2990,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3265,7 +3277,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ11">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3596,7 +3608,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3674,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -3802,7 +3814,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -4008,7 +4020,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4089,7 +4101,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR15">
         <v>0.6899999999999999</v>
@@ -4498,7 +4510,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ17">
         <v>0.77</v>
@@ -4832,7 +4844,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -4913,7 +4925,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ19">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -5038,7 +5050,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5116,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ20">
         <v>1.15</v>
@@ -5244,7 +5256,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5325,7 +5337,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ21">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR21">
         <v>2.05</v>
@@ -5450,7 +5462,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5656,7 +5668,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5734,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -5943,7 +5955,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR24">
         <v>1.41</v>
@@ -6146,7 +6158,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25">
         <v>0.93</v>
@@ -6274,7 +6286,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6480,7 +6492,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6686,7 +6698,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6764,7 +6776,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -6892,7 +6904,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -6973,7 +6985,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR29">
         <v>1.12</v>
@@ -7716,7 +7728,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7794,7 +7806,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ33">
         <v>1.25</v>
@@ -7922,7 +7934,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8003,7 +8015,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ34">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR34">
         <v>1.39</v>
@@ -8128,7 +8140,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8206,10 +8218,10 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR35">
         <v>1.65</v>
@@ -9364,7 +9376,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9570,7 +9582,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9648,10 +9660,10 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -9854,10 +9866,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR43">
         <v>1.56</v>
@@ -10060,10 +10072,10 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ44">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10188,7 +10200,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10600,7 +10612,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10678,10 +10690,10 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ47">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR47">
         <v>1.56</v>
@@ -10806,7 +10818,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10887,7 +10899,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR48">
         <v>1.2</v>
@@ -11012,7 +11024,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11090,7 +11102,7 @@
         <v>1.75</v>
       </c>
       <c r="AP49">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ49">
         <v>1.25</v>
@@ -11218,7 +11230,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11296,7 +11308,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ50">
         <v>1.15</v>
@@ -11505,7 +11517,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ51">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR51">
         <v>1.18</v>
@@ -11630,7 +11642,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11708,7 +11720,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ52">
         <v>0.77</v>
@@ -11836,7 +11848,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12248,7 +12260,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12329,7 +12341,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR55">
         <v>1.97</v>
@@ -12660,7 +12672,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12866,7 +12878,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12944,7 +12956,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ58">
         <v>1.29</v>
@@ -13153,7 +13165,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ59">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13278,7 +13290,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13356,10 +13368,10 @@
         <v>1.8</v>
       </c>
       <c r="AP60">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ60">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR60">
         <v>1.28</v>
@@ -13690,7 +13702,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13896,7 +13908,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14102,7 +14114,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14308,7 +14320,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14386,7 +14398,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ65">
         <v>0.93</v>
@@ -14514,7 +14526,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14595,7 +14607,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR66">
         <v>1.64</v>
@@ -14720,7 +14732,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14798,7 +14810,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ67">
         <v>1.29</v>
@@ -14926,7 +14938,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15213,7 +15225,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ69">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR69">
         <v>1.96</v>
@@ -15338,7 +15350,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15625,7 +15637,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ71">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR71">
         <v>0.93</v>
@@ -15750,7 +15762,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15956,7 +15968,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16034,10 +16046,10 @@
         <v>1.57</v>
       </c>
       <c r="AP73">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16243,7 +16255,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ74">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -16368,7 +16380,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16446,7 +16458,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -17064,7 +17076,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ78">
         <v>0.93</v>
@@ -17398,7 +17410,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17479,7 +17491,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ80">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -17810,7 +17822,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17888,10 +17900,10 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ82">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR82">
         <v>1.53</v>
@@ -18016,7 +18028,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18094,7 +18106,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ83">
         <v>1.25</v>
@@ -18222,7 +18234,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18300,7 +18312,7 @@
         <v>0.88</v>
       </c>
       <c r="AP84">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ84">
         <v>0.77</v>
@@ -18509,7 +18521,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ85">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -18634,7 +18646,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18715,7 +18727,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ86">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR86">
         <v>1.59</v>
@@ -18840,7 +18852,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19046,7 +19058,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19252,7 +19264,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19664,7 +19676,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19870,7 +19882,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20076,7 +20088,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20282,7 +20294,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20488,7 +20500,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20978,10 +20990,10 @@
         <v>0</v>
       </c>
       <c r="AP97">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ97">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR97">
         <v>1.22</v>
@@ -21106,7 +21118,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21393,7 +21405,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ99">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21518,7 +21530,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21596,7 +21608,7 @@
         <v>1.44</v>
       </c>
       <c r="AP100">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ100">
         <v>1.15</v>
@@ -22217,7 +22229,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR103">
         <v>1.14</v>
@@ -22548,7 +22560,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22754,7 +22766,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22832,7 +22844,7 @@
         <v>1.1</v>
       </c>
       <c r="AP106">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -22960,7 +22972,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23166,7 +23178,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23244,7 +23256,7 @@
         <v>1.3</v>
       </c>
       <c r="AP108">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ108">
         <v>1.15</v>
@@ -23372,7 +23384,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23453,7 +23465,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ109">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR109">
         <v>1.9</v>
@@ -23784,7 +23796,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -23865,7 +23877,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ111">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24068,7 +24080,7 @@
         <v>0.82</v>
       </c>
       <c r="AP112">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ112">
         <v>0.93</v>
@@ -24277,7 +24289,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR113">
         <v>1.48</v>
@@ -24892,7 +24904,7 @@
         <v>1.09</v>
       </c>
       <c r="AP116">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25020,7 +25032,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25098,7 +25110,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ117">
         <v>1</v>
@@ -25307,7 +25319,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ118">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR118">
         <v>1.07</v>
@@ -25432,7 +25444,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25638,7 +25650,7 @@
         <v>162</v>
       </c>
       <c r="P120" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25844,7 +25856,7 @@
         <v>81</v>
       </c>
       <c r="P121" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q121">
         <v>3.6</v>
@@ -26050,7 +26062,7 @@
         <v>163</v>
       </c>
       <c r="P122" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q122">
         <v>1.77</v>
@@ -26540,10 +26552,10 @@
         <v>1.09</v>
       </c>
       <c r="AP124">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR124">
         <v>1.51</v>
@@ -26668,7 +26680,7 @@
         <v>165</v>
       </c>
       <c r="P125" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q125">
         <v>1.91</v>
@@ -26749,7 +26761,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ125">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AR125">
         <v>1.5</v>
@@ -26874,7 +26886,7 @@
         <v>81</v>
       </c>
       <c r="P126" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -26952,7 +26964,7 @@
         <v>1.09</v>
       </c>
       <c r="AP126">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ126">
         <v>1.25</v>
@@ -27080,7 +27092,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q127">
         <v>3.3</v>
@@ -28061,6 +28073,624 @@
       </c>
       <c r="BP131">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7451098</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F132">
+        <v>27</v>
+      </c>
+      <c r="G132" t="s">
+        <v>77</v>
+      </c>
+      <c r="H132" t="s">
+        <v>71</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>2</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>2</v>
+      </c>
+      <c r="O132" t="s">
+        <v>169</v>
+      </c>
+      <c r="P132" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q132">
+        <v>2.5</v>
+      </c>
+      <c r="R132">
+        <v>2.1</v>
+      </c>
+      <c r="S132">
+        <v>4.75</v>
+      </c>
+      <c r="T132">
+        <v>1.44</v>
+      </c>
+      <c r="U132">
+        <v>2.63</v>
+      </c>
+      <c r="V132">
+        <v>3.25</v>
+      </c>
+      <c r="W132">
+        <v>1.33</v>
+      </c>
+      <c r="X132">
+        <v>9</v>
+      </c>
+      <c r="Y132">
+        <v>1.07</v>
+      </c>
+      <c r="Z132">
+        <v>1.73</v>
+      </c>
+      <c r="AA132">
+        <v>3.4</v>
+      </c>
+      <c r="AB132">
+        <v>4.2</v>
+      </c>
+      <c r="AC132">
+        <v>1.06</v>
+      </c>
+      <c r="AD132">
+        <v>8</v>
+      </c>
+      <c r="AE132">
+        <v>1.33</v>
+      </c>
+      <c r="AF132">
+        <v>3.1</v>
+      </c>
+      <c r="AG132">
+        <v>1.95</v>
+      </c>
+      <c r="AH132">
+        <v>1.75</v>
+      </c>
+      <c r="AI132">
+        <v>1.91</v>
+      </c>
+      <c r="AJ132">
+        <v>1.8</v>
+      </c>
+      <c r="AK132">
+        <v>1.2</v>
+      </c>
+      <c r="AL132">
+        <v>1.28</v>
+      </c>
+      <c r="AM132">
+        <v>1.98</v>
+      </c>
+      <c r="AN132">
+        <v>1.42</v>
+      </c>
+      <c r="AO132">
+        <v>0.08</v>
+      </c>
+      <c r="AP132">
+        <v>1.38</v>
+      </c>
+      <c r="AQ132">
+        <v>0.15</v>
+      </c>
+      <c r="AR132">
+        <v>1.57</v>
+      </c>
+      <c r="AS132">
+        <v>0.92</v>
+      </c>
+      <c r="AT132">
+        <v>2.49</v>
+      </c>
+      <c r="AU132">
+        <v>7</v>
+      </c>
+      <c r="AV132">
+        <v>5</v>
+      </c>
+      <c r="AW132">
+        <v>3</v>
+      </c>
+      <c r="AX132">
+        <v>1</v>
+      </c>
+      <c r="AY132">
+        <v>10</v>
+      </c>
+      <c r="AZ132">
+        <v>6</v>
+      </c>
+      <c r="BA132">
+        <v>4</v>
+      </c>
+      <c r="BB132">
+        <v>0</v>
+      </c>
+      <c r="BC132">
+        <v>4</v>
+      </c>
+      <c r="BD132">
+        <v>1.41</v>
+      </c>
+      <c r="BE132">
+        <v>9</v>
+      </c>
+      <c r="BF132">
+        <v>3.66</v>
+      </c>
+      <c r="BG132">
+        <v>1.36</v>
+      </c>
+      <c r="BH132">
+        <v>2.92</v>
+      </c>
+      <c r="BI132">
+        <v>1.62</v>
+      </c>
+      <c r="BJ132">
+        <v>2.22</v>
+      </c>
+      <c r="BK132">
+        <v>2.02</v>
+      </c>
+      <c r="BL132">
+        <v>1.74</v>
+      </c>
+      <c r="BM132">
+        <v>2.57</v>
+      </c>
+      <c r="BN132">
+        <v>1.45</v>
+      </c>
+      <c r="BO132">
+        <v>3.42</v>
+      </c>
+      <c r="BP132">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7451100</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F133">
+        <v>27</v>
+      </c>
+      <c r="G133" t="s">
+        <v>76</v>
+      </c>
+      <c r="H133" t="s">
+        <v>73</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>2</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>3</v>
+      </c>
+      <c r="O133" t="s">
+        <v>170</v>
+      </c>
+      <c r="P133" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q133">
+        <v>3.2</v>
+      </c>
+      <c r="R133">
+        <v>2</v>
+      </c>
+      <c r="S133">
+        <v>3.75</v>
+      </c>
+      <c r="T133">
+        <v>1.5</v>
+      </c>
+      <c r="U133">
+        <v>2.5</v>
+      </c>
+      <c r="V133">
+        <v>3.5</v>
+      </c>
+      <c r="W133">
+        <v>1.29</v>
+      </c>
+      <c r="X133">
+        <v>10</v>
+      </c>
+      <c r="Y133">
+        <v>1.06</v>
+      </c>
+      <c r="Z133">
+        <v>2.71</v>
+      </c>
+      <c r="AA133">
+        <v>2.7</v>
+      </c>
+      <c r="AB133">
+        <v>3.07</v>
+      </c>
+      <c r="AC133">
+        <v>1.06</v>
+      </c>
+      <c r="AD133">
+        <v>6.3</v>
+      </c>
+      <c r="AE133">
+        <v>1.4</v>
+      </c>
+      <c r="AF133">
+        <v>2.88</v>
+      </c>
+      <c r="AG133">
+        <v>2.25</v>
+      </c>
+      <c r="AH133">
+        <v>1.62</v>
+      </c>
+      <c r="AI133">
+        <v>1.83</v>
+      </c>
+      <c r="AJ133">
+        <v>1.83</v>
+      </c>
+      <c r="AK133">
+        <v>1.36</v>
+      </c>
+      <c r="AL133">
+        <v>1.4</v>
+      </c>
+      <c r="AM133">
+        <v>1.53</v>
+      </c>
+      <c r="AN133">
+        <v>1.25</v>
+      </c>
+      <c r="AO133">
+        <v>1</v>
+      </c>
+      <c r="AP133">
+        <v>1.38</v>
+      </c>
+      <c r="AQ133">
+        <v>0.92</v>
+      </c>
+      <c r="AR133">
+        <v>1.26</v>
+      </c>
+      <c r="AS133">
+        <v>1.32</v>
+      </c>
+      <c r="AT133">
+        <v>2.58</v>
+      </c>
+      <c r="AU133">
+        <v>6</v>
+      </c>
+      <c r="AV133">
+        <v>2</v>
+      </c>
+      <c r="AW133">
+        <v>9</v>
+      </c>
+      <c r="AX133">
+        <v>5</v>
+      </c>
+      <c r="AY133">
+        <v>15</v>
+      </c>
+      <c r="AZ133">
+        <v>7</v>
+      </c>
+      <c r="BA133">
+        <v>7</v>
+      </c>
+      <c r="BB133">
+        <v>2</v>
+      </c>
+      <c r="BC133">
+        <v>9</v>
+      </c>
+      <c r="BD133">
+        <v>2</v>
+      </c>
+      <c r="BE133">
+        <v>7.5</v>
+      </c>
+      <c r="BF133">
+        <v>2.05</v>
+      </c>
+      <c r="BG133">
+        <v>1.47</v>
+      </c>
+      <c r="BH133">
+        <v>2.5</v>
+      </c>
+      <c r="BI133">
+        <v>1.82</v>
+      </c>
+      <c r="BJ133">
+        <v>1.93</v>
+      </c>
+      <c r="BK133">
+        <v>2.34</v>
+      </c>
+      <c r="BL133">
+        <v>1.56</v>
+      </c>
+      <c r="BM133">
+        <v>3.02</v>
+      </c>
+      <c r="BN133">
+        <v>1.33</v>
+      </c>
+      <c r="BO133">
+        <v>4.2</v>
+      </c>
+      <c r="BP133">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7451097</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45745.61458333334</v>
+      </c>
+      <c r="F134">
+        <v>27</v>
+      </c>
+      <c r="G134" t="s">
+        <v>79</v>
+      </c>
+      <c r="H134" t="s">
+        <v>72</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>2</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>3</v>
+      </c>
+      <c r="O134" t="s">
+        <v>171</v>
+      </c>
+      <c r="P134" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q134">
+        <v>5</v>
+      </c>
+      <c r="R134">
+        <v>2</v>
+      </c>
+      <c r="S134">
+        <v>2.63</v>
+      </c>
+      <c r="T134">
+        <v>1.5</v>
+      </c>
+      <c r="U134">
+        <v>2.5</v>
+      </c>
+      <c r="V134">
+        <v>3.5</v>
+      </c>
+      <c r="W134">
+        <v>1.29</v>
+      </c>
+      <c r="X134">
+        <v>11</v>
+      </c>
+      <c r="Y134">
+        <v>1.05</v>
+      </c>
+      <c r="Z134">
+        <v>4.2</v>
+      </c>
+      <c r="AA134">
+        <v>3.1</v>
+      </c>
+      <c r="AB134">
+        <v>1.85</v>
+      </c>
+      <c r="AC134">
+        <v>1.04</v>
+      </c>
+      <c r="AD134">
+        <v>6.75</v>
+      </c>
+      <c r="AE134">
+        <v>1.38</v>
+      </c>
+      <c r="AF134">
+        <v>2.63</v>
+      </c>
+      <c r="AG134">
+        <v>2.3</v>
+      </c>
+      <c r="AH134">
+        <v>1.6</v>
+      </c>
+      <c r="AI134">
+        <v>2</v>
+      </c>
+      <c r="AJ134">
+        <v>1.73</v>
+      </c>
+      <c r="AK134">
+        <v>1.83</v>
+      </c>
+      <c r="AL134">
+        <v>1.35</v>
+      </c>
+      <c r="AM134">
+        <v>1.22</v>
+      </c>
+      <c r="AN134">
+        <v>1.42</v>
+      </c>
+      <c r="AO134">
+        <v>1.75</v>
+      </c>
+      <c r="AP134">
+        <v>1.54</v>
+      </c>
+      <c r="AQ134">
+        <v>1.62</v>
+      </c>
+      <c r="AR134">
+        <v>1.47</v>
+      </c>
+      <c r="AS134">
+        <v>1.21</v>
+      </c>
+      <c r="AT134">
+        <v>2.68</v>
+      </c>
+      <c r="AU134">
+        <v>5</v>
+      </c>
+      <c r="AV134">
+        <v>6</v>
+      </c>
+      <c r="AW134">
+        <v>4</v>
+      </c>
+      <c r="AX134">
+        <v>7</v>
+      </c>
+      <c r="AY134">
+        <v>9</v>
+      </c>
+      <c r="AZ134">
+        <v>13</v>
+      </c>
+      <c r="BA134">
+        <v>6</v>
+      </c>
+      <c r="BB134">
+        <v>8</v>
+      </c>
+      <c r="BC134">
+        <v>14</v>
+      </c>
+      <c r="BD134">
+        <v>2.66</v>
+      </c>
+      <c r="BE134">
+        <v>7.5</v>
+      </c>
+      <c r="BF134">
+        <v>1.69</v>
+      </c>
+      <c r="BG134">
+        <v>1.47</v>
+      </c>
+      <c r="BH134">
+        <v>2.5</v>
+      </c>
+      <c r="BI134">
+        <v>1.82</v>
+      </c>
+      <c r="BJ134">
+        <v>1.93</v>
+      </c>
+      <c r="BK134">
+        <v>2.34</v>
+      </c>
+      <c r="BL134">
+        <v>1.56</v>
+      </c>
+      <c r="BM134">
+        <v>3.02</v>
+      </c>
+      <c r="BN134">
+        <v>1.33</v>
+      </c>
+      <c r="BO134">
+        <v>4.2</v>
+      </c>
+      <c r="BP134">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="237">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -532,6 +532,9 @@
     <t>['64', '76']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -614,9 +617,6 @@
   </si>
   <si>
     <t>['11', '45+2', '50', '86']</t>
-  </si>
-  <si>
-    <t>['76']</t>
   </si>
   <si>
     <t>['50', '79', '84']</t>
@@ -1086,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1960,7 +1960,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2041,7 +2041,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ5">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2166,7 +2166,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ6">
         <v>1.29</v>
@@ -2784,7 +2784,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2990,7 +2990,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3071,7 +3071,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ10">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
         <v>3.14</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ11">
         <v>1.62</v>
@@ -3483,7 +3483,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ12">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR12">
         <v>2.03</v>
@@ -3608,7 +3608,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3814,7 +3814,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -3892,7 +3892,7 @@
         <v>1</v>
       </c>
       <c r="AP14">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ14">
         <v>0.93</v>
@@ -4020,7 +4020,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4513,7 +4513,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ17">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR17">
         <v>1.8</v>
@@ -4716,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ18">
         <v>1.29</v>
@@ -4844,7 +4844,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -5050,7 +5050,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5256,7 +5256,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5462,7 +5462,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5543,7 +5543,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ22">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR22">
         <v>1.22</v>
@@ -5668,7 +5668,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5952,7 +5952,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ24">
         <v>0.92</v>
@@ -6286,7 +6286,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6367,7 +6367,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ26">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR26">
         <v>1.71</v>
@@ -6492,7 +6492,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6698,7 +6698,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6904,7 +6904,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7600,7 +7600,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7728,7 +7728,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7809,7 +7809,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ33">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -7934,7 +7934,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8012,7 +8012,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ34">
         <v>0.15</v>
@@ -8140,7 +8140,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8427,7 +8427,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ36">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR36">
         <v>1.6</v>
@@ -9376,7 +9376,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9582,7 +9582,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -10200,7 +10200,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10278,10 +10278,10 @@
         <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ45">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR45">
         <v>1.19</v>
@@ -10484,10 +10484,10 @@
         <v>1.2</v>
       </c>
       <c r="AP46">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ46">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR46">
         <v>1.57</v>
@@ -10612,7 +10612,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10818,7 +10818,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -11024,7 +11024,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11105,7 +11105,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ49">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11230,7 +11230,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11514,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ51">
         <v>0.15</v>
@@ -11642,7 +11642,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11723,7 +11723,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ52">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR52">
         <v>1.48</v>
@@ -11848,7 +11848,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -11926,7 +11926,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12260,7 +12260,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12672,7 +12672,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12753,7 +12753,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ57">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR57">
         <v>1.11</v>
@@ -12878,7 +12878,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13290,7 +13290,7 @@
         <v>81</v>
       </c>
       <c r="P60" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="Q60">
         <v>5</v>
@@ -13574,7 +13574,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ61">
         <v>1.15</v>
@@ -13989,7 +13989,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ63">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR63">
         <v>1.18</v>
@@ -14192,7 +14192,7 @@
         <v>0.67</v>
       </c>
       <c r="AP64">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14320,7 +14320,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14526,7 +14526,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -15016,7 +15016,7 @@
         <v>1.17</v>
       </c>
       <c r="AP68">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15840,10 +15840,10 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ72">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR72">
         <v>1.34</v>
@@ -16664,10 +16664,10 @@
         <v>1.71</v>
       </c>
       <c r="AP76">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ76">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR76">
         <v>1.66</v>
@@ -17822,7 +17822,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -18028,7 +18028,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18109,7 +18109,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ83">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR83">
         <v>1.51</v>
@@ -18315,7 +18315,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ84">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR84">
         <v>1.2</v>
@@ -18518,7 +18518,7 @@
         <v>1.38</v>
       </c>
       <c r="AP85">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ85">
         <v>0.92</v>
@@ -18724,7 +18724,7 @@
         <v>2</v>
       </c>
       <c r="AP86">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ86">
         <v>1.62</v>
@@ -19963,7 +19963,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ92">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR92">
         <v>1.57</v>
@@ -20784,7 +20784,7 @@
         <v>0.78</v>
       </c>
       <c r="AP96">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ96">
         <v>1.29</v>
@@ -21402,7 +21402,7 @@
         <v>1.89</v>
       </c>
       <c r="AP99">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ99">
         <v>1.62</v>
@@ -21817,7 +21817,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ101">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR101">
         <v>1.55</v>
@@ -22023,7 +22023,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ102">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR102">
         <v>1.92</v>
@@ -22432,7 +22432,7 @@
         <v>0.9</v>
       </c>
       <c r="AP104">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ104">
         <v>0.93</v>
@@ -23384,7 +23384,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23668,7 +23668,7 @@
         <v>0.82</v>
       </c>
       <c r="AP110">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ110">
         <v>1.29</v>
@@ -24286,7 +24286,7 @@
         <v>1.2</v>
       </c>
       <c r="AP113">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ113">
         <v>0.92</v>
@@ -24495,7 +24495,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ114">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR114">
         <v>1.68</v>
@@ -24701,7 +24701,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ115">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR115">
         <v>1.11</v>
@@ -26143,7 +26143,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ122">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR122">
         <v>1.67</v>
@@ -26346,7 +26346,7 @@
         <v>1.08</v>
       </c>
       <c r="AP123">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -26758,7 +26758,7 @@
         <v>0.09</v>
       </c>
       <c r="AP125">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ125">
         <v>0.15</v>
@@ -26967,7 +26967,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ126">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR126">
         <v>1.57</v>
@@ -28122,7 +28122,7 @@
         <v>169</v>
       </c>
       <c r="P132" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28691,6 +28691,418 @@
       </c>
       <c r="BP134">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7451096</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45746.45833333334</v>
+      </c>
+      <c r="F135">
+        <v>27</v>
+      </c>
+      <c r="G135" t="s">
+        <v>74</v>
+      </c>
+      <c r="H135" t="s">
+        <v>75</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>154</v>
+      </c>
+      <c r="P135" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q135">
+        <v>1.8</v>
+      </c>
+      <c r="R135">
+        <v>2.4</v>
+      </c>
+      <c r="S135">
+        <v>10</v>
+      </c>
+      <c r="T135">
+        <v>1.36</v>
+      </c>
+      <c r="U135">
+        <v>3</v>
+      </c>
+      <c r="V135">
+        <v>2.75</v>
+      </c>
+      <c r="W135">
+        <v>1.4</v>
+      </c>
+      <c r="X135">
+        <v>7</v>
+      </c>
+      <c r="Y135">
+        <v>1.1</v>
+      </c>
+      <c r="Z135">
+        <v>1.27</v>
+      </c>
+      <c r="AA135">
+        <v>5.29</v>
+      </c>
+      <c r="AB135">
+        <v>10.32</v>
+      </c>
+      <c r="AC135">
+        <v>1</v>
+      </c>
+      <c r="AD135">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE135">
+        <v>1.22</v>
+      </c>
+      <c r="AF135">
+        <v>3.52</v>
+      </c>
+      <c r="AG135">
+        <v>1.8</v>
+      </c>
+      <c r="AH135">
+        <v>2</v>
+      </c>
+      <c r="AI135">
+        <v>2.5</v>
+      </c>
+      <c r="AJ135">
+        <v>1.5</v>
+      </c>
+      <c r="AK135">
+        <v>1.05</v>
+      </c>
+      <c r="AL135">
+        <v>1.18</v>
+      </c>
+      <c r="AM135">
+        <v>3.4</v>
+      </c>
+      <c r="AN135">
+        <v>2.54</v>
+      </c>
+      <c r="AO135">
+        <v>0.77</v>
+      </c>
+      <c r="AP135">
+        <v>2.57</v>
+      </c>
+      <c r="AQ135">
+        <v>0.71</v>
+      </c>
+      <c r="AR135">
+        <v>1.47</v>
+      </c>
+      <c r="AS135">
+        <v>1.07</v>
+      </c>
+      <c r="AT135">
+        <v>2.54</v>
+      </c>
+      <c r="AU135">
+        <v>7</v>
+      </c>
+      <c r="AV135">
+        <v>0</v>
+      </c>
+      <c r="AW135">
+        <v>10</v>
+      </c>
+      <c r="AX135">
+        <v>4</v>
+      </c>
+      <c r="AY135">
+        <v>17</v>
+      </c>
+      <c r="AZ135">
+        <v>4</v>
+      </c>
+      <c r="BA135">
+        <v>11</v>
+      </c>
+      <c r="BB135">
+        <v>0</v>
+      </c>
+      <c r="BC135">
+        <v>11</v>
+      </c>
+      <c r="BD135">
+        <v>1.26</v>
+      </c>
+      <c r="BE135">
+        <v>9.5</v>
+      </c>
+      <c r="BF135">
+        <v>4.66</v>
+      </c>
+      <c r="BG135">
+        <v>1.43</v>
+      </c>
+      <c r="BH135">
+        <v>2.63</v>
+      </c>
+      <c r="BI135">
+        <v>1.74</v>
+      </c>
+      <c r="BJ135">
+        <v>2.02</v>
+      </c>
+      <c r="BK135">
+        <v>2.22</v>
+      </c>
+      <c r="BL135">
+        <v>1.62</v>
+      </c>
+      <c r="BM135">
+        <v>2.85</v>
+      </c>
+      <c r="BN135">
+        <v>1.37</v>
+      </c>
+      <c r="BO135">
+        <v>3.9</v>
+      </c>
+      <c r="BP135">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7451099</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45746.57291666666</v>
+      </c>
+      <c r="F136">
+        <v>27</v>
+      </c>
+      <c r="G136" t="s">
+        <v>78</v>
+      </c>
+      <c r="H136" t="s">
+        <v>70</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>1</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>2</v>
+      </c>
+      <c r="O136" t="s">
+        <v>172</v>
+      </c>
+      <c r="P136" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q136">
+        <v>5.5</v>
+      </c>
+      <c r="R136">
+        <v>2.1</v>
+      </c>
+      <c r="S136">
+        <v>2.3</v>
+      </c>
+      <c r="T136">
+        <v>1.44</v>
+      </c>
+      <c r="U136">
+        <v>2.63</v>
+      </c>
+      <c r="V136">
+        <v>3.25</v>
+      </c>
+      <c r="W136">
+        <v>1.33</v>
+      </c>
+      <c r="X136">
+        <v>9</v>
+      </c>
+      <c r="Y136">
+        <v>1.07</v>
+      </c>
+      <c r="Z136">
+        <v>5</v>
+      </c>
+      <c r="AA136">
+        <v>3.4</v>
+      </c>
+      <c r="AB136">
+        <v>1.62</v>
+      </c>
+      <c r="AC136">
+        <v>1.02</v>
+      </c>
+      <c r="AD136">
+        <v>8</v>
+      </c>
+      <c r="AE136">
+        <v>1.3</v>
+      </c>
+      <c r="AF136">
+        <v>2.98</v>
+      </c>
+      <c r="AG136">
+        <v>2.1</v>
+      </c>
+      <c r="AH136">
+        <v>1.7</v>
+      </c>
+      <c r="AI136">
+        <v>2</v>
+      </c>
+      <c r="AJ136">
+        <v>1.73</v>
+      </c>
+      <c r="AK136">
+        <v>2.1</v>
+      </c>
+      <c r="AL136">
+        <v>1.3</v>
+      </c>
+      <c r="AM136">
+        <v>1.17</v>
+      </c>
+      <c r="AN136">
+        <v>1.83</v>
+      </c>
+      <c r="AO136">
+        <v>1.25</v>
+      </c>
+      <c r="AP136">
+        <v>1.77</v>
+      </c>
+      <c r="AQ136">
+        <v>1.23</v>
+      </c>
+      <c r="AR136">
+        <v>1.36</v>
+      </c>
+      <c r="AS136">
+        <v>1.79</v>
+      </c>
+      <c r="AT136">
+        <v>3.15</v>
+      </c>
+      <c r="AU136">
+        <v>5</v>
+      </c>
+      <c r="AV136">
+        <v>4</v>
+      </c>
+      <c r="AW136">
+        <v>4</v>
+      </c>
+      <c r="AX136">
+        <v>14</v>
+      </c>
+      <c r="AY136">
+        <v>9</v>
+      </c>
+      <c r="AZ136">
+        <v>18</v>
+      </c>
+      <c r="BA136">
+        <v>2</v>
+      </c>
+      <c r="BB136">
+        <v>2</v>
+      </c>
+      <c r="BC136">
+        <v>4</v>
+      </c>
+      <c r="BD136">
+        <v>2.8</v>
+      </c>
+      <c r="BE136">
+        <v>8</v>
+      </c>
+      <c r="BF136">
+        <v>1.59</v>
+      </c>
+      <c r="BG136">
+        <v>1.43</v>
+      </c>
+      <c r="BH136">
+        <v>2.63</v>
+      </c>
+      <c r="BI136">
+        <v>1.74</v>
+      </c>
+      <c r="BJ136">
+        <v>2.02</v>
+      </c>
+      <c r="BK136">
+        <v>2.22</v>
+      </c>
+      <c r="BL136">
+        <v>1.62</v>
+      </c>
+      <c r="BM136">
+        <v>2.85</v>
+      </c>
+      <c r="BN136">
+        <v>1.37</v>
+      </c>
+      <c r="BO136">
+        <v>3.9</v>
+      </c>
+      <c r="BP136">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="237">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1086,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2659,7 +2659,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ8">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ11">
         <v>1.62</v>
@@ -4716,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18">
         <v>1.29</v>
@@ -4925,7 +4925,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ19">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR19">
         <v>1.9</v>
@@ -7600,7 +7600,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8015,7 +8015,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ34">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR34">
         <v>1.39</v>
@@ -9869,7 +9869,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ43">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR43">
         <v>1.56</v>
@@ -10278,7 +10278,7 @@
         <v>1.33</v>
       </c>
       <c r="AP45">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ45">
         <v>1.23</v>
@@ -11514,10 +11514,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ51">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR51">
         <v>1.18</v>
@@ -13165,7 +13165,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ59">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13574,7 +13574,7 @@
         <v>1.8</v>
       </c>
       <c r="AP61">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ61">
         <v>1.15</v>
@@ -15016,7 +15016,7 @@
         <v>1.17</v>
       </c>
       <c r="AP68">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15637,7 +15637,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ71">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR71">
         <v>0.93</v>
@@ -15840,7 +15840,7 @@
         <v>1</v>
       </c>
       <c r="AP72">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ72">
         <v>0.71</v>
@@ -16255,7 +16255,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ74">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR74">
         <v>1.72</v>
@@ -17903,7 +17903,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ82">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR82">
         <v>1.53</v>
@@ -18518,7 +18518,7 @@
         <v>1.38</v>
       </c>
       <c r="AP85">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ85">
         <v>0.92</v>
@@ -20993,7 +20993,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ97">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR97">
         <v>1.22</v>
@@ -21402,7 +21402,7 @@
         <v>1.89</v>
       </c>
       <c r="AP99">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99">
         <v>1.62</v>
@@ -23465,7 +23465,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ109">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR109">
         <v>1.9</v>
@@ -23668,7 +23668,7 @@
         <v>0.82</v>
       </c>
       <c r="AP110">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ110">
         <v>1.29</v>
@@ -26346,7 +26346,7 @@
         <v>1.08</v>
       </c>
       <c r="AP123">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -26761,7 +26761,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ125">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR125">
         <v>1.5</v>
@@ -28203,7 +28203,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ132">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR132">
         <v>1.57</v>
@@ -29024,7 +29024,7 @@
         <v>1.25</v>
       </c>
       <c r="AP136">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AQ136">
         <v>1.23</v>
@@ -29103,6 +29103,212 @@
       </c>
       <c r="BP136">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7451103</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45751.54166666666</v>
+      </c>
+      <c r="F137">
+        <v>28</v>
+      </c>
+      <c r="G137" t="s">
+        <v>78</v>
+      </c>
+      <c r="H137" t="s">
+        <v>71</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137" t="s">
+        <v>81</v>
+      </c>
+      <c r="P137" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q137">
+        <v>2.65</v>
+      </c>
+      <c r="R137">
+        <v>1.9</v>
+      </c>
+      <c r="S137">
+        <v>4.6</v>
+      </c>
+      <c r="T137">
+        <v>1.53</v>
+      </c>
+      <c r="U137">
+        <v>2.3</v>
+      </c>
+      <c r="V137">
+        <v>3.4</v>
+      </c>
+      <c r="W137">
+        <v>1.27</v>
+      </c>
+      <c r="X137">
+        <v>9.75</v>
+      </c>
+      <c r="Y137">
+        <v>1.04</v>
+      </c>
+      <c r="Z137">
+        <v>2.26</v>
+      </c>
+      <c r="AA137">
+        <v>2.9</v>
+      </c>
+      <c r="AB137">
+        <v>3.6</v>
+      </c>
+      <c r="AC137">
+        <v>1.1</v>
+      </c>
+      <c r="AD137">
+        <v>6.25</v>
+      </c>
+      <c r="AE137">
+        <v>1.49</v>
+      </c>
+      <c r="AF137">
+        <v>2.4</v>
+      </c>
+      <c r="AG137">
+        <v>2.55</v>
+      </c>
+      <c r="AH137">
+        <v>1.48</v>
+      </c>
+      <c r="AI137">
+        <v>2.15</v>
+      </c>
+      <c r="AJ137">
+        <v>1.6</v>
+      </c>
+      <c r="AK137">
+        <v>1.22</v>
+      </c>
+      <c r="AL137">
+        <v>1.35</v>
+      </c>
+      <c r="AM137">
+        <v>1.78</v>
+      </c>
+      <c r="AN137">
+        <v>1.77</v>
+      </c>
+      <c r="AO137">
+        <v>0.15</v>
+      </c>
+      <c r="AP137">
+        <v>1.71</v>
+      </c>
+      <c r="AQ137">
+        <v>0.21</v>
+      </c>
+      <c r="AR137">
+        <v>1.35</v>
+      </c>
+      <c r="AS137">
+        <v>0.93</v>
+      </c>
+      <c r="AT137">
+        <v>2.28</v>
+      </c>
+      <c r="AU137">
+        <v>6</v>
+      </c>
+      <c r="AV137">
+        <v>3</v>
+      </c>
+      <c r="AW137">
+        <v>9</v>
+      </c>
+      <c r="AX137">
+        <v>2</v>
+      </c>
+      <c r="AY137">
+        <v>15</v>
+      </c>
+      <c r="AZ137">
+        <v>5</v>
+      </c>
+      <c r="BA137">
+        <v>6</v>
+      </c>
+      <c r="BB137">
+        <v>1</v>
+      </c>
+      <c r="BC137">
+        <v>7</v>
+      </c>
+      <c r="BD137">
+        <v>1.64</v>
+      </c>
+      <c r="BE137">
+        <v>7.5</v>
+      </c>
+      <c r="BF137">
+        <v>2.78</v>
+      </c>
+      <c r="BG137">
+        <v>1.5</v>
+      </c>
+      <c r="BH137">
+        <v>2.4</v>
+      </c>
+      <c r="BI137">
+        <v>1.87</v>
+      </c>
+      <c r="BJ137">
+        <v>1.87</v>
+      </c>
+      <c r="BK137">
+        <v>2.42</v>
+      </c>
+      <c r="BL137">
+        <v>1.52</v>
+      </c>
+      <c r="BM137">
+        <v>3.25</v>
+      </c>
+      <c r="BN137">
+        <v>1.29</v>
+      </c>
+      <c r="BO137">
+        <v>4.4</v>
+      </c>
+      <c r="BP137">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -535,6 +535,9 @@
     <t>['76']</t>
   </si>
   <si>
+    <t>['21', '53', '67']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -725,6 +728,9 @@
   </si>
   <si>
     <t>['68']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1960,7 +1966,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2166,7 +2172,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2656,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
         <v>0.21</v>
@@ -2784,7 +2790,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2865,7 +2871,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2990,7 +2996,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3071,7 +3077,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR10">
         <v>3.14</v>
@@ -3608,7 +3614,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3686,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -3814,7 +3820,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -4020,7 +4026,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4844,7 +4850,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -5050,7 +5056,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5128,10 +5134,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ20">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR20">
         <v>1.92</v>
@@ -5256,7 +5262,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5462,7 +5468,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5668,7 +5674,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5746,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -6286,7 +6292,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6367,7 +6373,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ26">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR26">
         <v>1.71</v>
@@ -6492,7 +6498,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6573,7 +6579,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ27">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR27">
         <v>1.84</v>
@@ -6698,7 +6704,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6776,7 +6782,7 @@
         <v>0.5</v>
       </c>
       <c r="AP28">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -6904,7 +6910,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -7728,7 +7734,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7806,10 +7812,10 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ33">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR33">
         <v>1.4</v>
@@ -7934,7 +7940,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8140,7 +8146,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -9251,7 +9257,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ40">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR40">
         <v>1.7</v>
@@ -9376,7 +9382,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9582,7 +9588,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9660,7 +9666,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42">
         <v>0.92</v>
@@ -10072,7 +10078,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ44">
         <v>1.62</v>
@@ -10200,7 +10206,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10281,7 +10287,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ45">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR45">
         <v>1.19</v>
@@ -10612,7 +10618,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10818,7 +10824,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -11024,7 +11030,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11102,10 +11108,10 @@
         <v>1.75</v>
       </c>
       <c r="AP49">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR49">
         <v>1.37</v>
@@ -11230,7 +11236,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11308,10 +11314,10 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ50">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR50">
         <v>1.52</v>
@@ -11642,7 +11648,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11720,7 +11726,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ52">
         <v>0.71</v>
@@ -11848,7 +11854,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12260,7 +12266,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12672,7 +12678,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12753,7 +12759,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ57">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR57">
         <v>1.11</v>
@@ -12878,7 +12884,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13368,7 +13374,7 @@
         <v>1.8</v>
       </c>
       <c r="AP60">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60">
         <v>1.62</v>
@@ -13577,7 +13583,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ61">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR61">
         <v>1.34</v>
@@ -13702,7 +13708,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13908,7 +13914,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -13989,7 +13995,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ63">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR63">
         <v>1.18</v>
@@ -14114,7 +14120,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14320,7 +14326,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14398,7 +14404,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ65">
         <v>0.93</v>
@@ -14526,7 +14532,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14732,7 +14738,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14810,7 +14816,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ67">
         <v>1.29</v>
@@ -14938,7 +14944,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15350,7 +15356,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15431,7 +15437,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ70">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR70">
         <v>1.61</v>
@@ -15762,7 +15768,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15968,7 +15974,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16046,7 +16052,7 @@
         <v>1.57</v>
       </c>
       <c r="AP73">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ73">
         <v>0.92</v>
@@ -16380,7 +16386,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16667,7 +16673,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ76">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR76">
         <v>1.66</v>
@@ -17076,7 +17082,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78">
         <v>0.93</v>
@@ -17285,7 +17291,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ79">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR79">
         <v>1.09</v>
@@ -17410,7 +17416,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17822,7 +17828,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -17900,7 +17906,7 @@
         <v>0</v>
       </c>
       <c r="AP82">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ82">
         <v>0.21</v>
@@ -18028,7 +18034,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18109,7 +18115,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ83">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR83">
         <v>1.51</v>
@@ -18234,7 +18240,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18312,7 +18318,7 @@
         <v>0.88</v>
       </c>
       <c r="AP84">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>0.71</v>
@@ -18646,7 +18652,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18852,7 +18858,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19058,7 +19064,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19264,7 +19270,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19676,7 +19682,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19757,7 +19763,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ91">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR91">
         <v>1.08</v>
@@ -19882,7 +19888,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20088,7 +20094,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20294,7 +20300,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20500,7 +20506,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -20990,7 +20996,7 @@
         <v>0</v>
       </c>
       <c r="AP97">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ97">
         <v>0.21</v>
@@ -21118,7 +21124,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21530,7 +21536,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21611,7 +21617,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ100">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR100">
         <v>1.46</v>
@@ -21817,7 +21823,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ101">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR101">
         <v>1.55</v>
@@ -22560,7 +22566,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22766,7 +22772,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22844,7 +22850,7 @@
         <v>1.1</v>
       </c>
       <c r="AP106">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -22972,7 +22978,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23178,7 +23184,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23256,10 +23262,10 @@
         <v>1.3</v>
       </c>
       <c r="AP108">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ108">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR108">
         <v>1.28</v>
@@ -23384,7 +23390,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23796,7 +23802,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -24495,7 +24501,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ114">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR114">
         <v>1.68</v>
@@ -24904,7 +24910,7 @@
         <v>1.09</v>
       </c>
       <c r="AP116">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25032,7 +25038,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25110,7 +25116,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ117">
         <v>1</v>
@@ -25444,7 +25450,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25650,7 +25656,7 @@
         <v>162</v>
       </c>
       <c r="P120" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25731,7 +25737,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ120">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR120">
         <v>1.93</v>
@@ -25856,7 +25862,7 @@
         <v>81</v>
       </c>
       <c r="P121" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q121">
         <v>3.6</v>
@@ -26062,7 +26068,7 @@
         <v>163</v>
       </c>
       <c r="P122" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q122">
         <v>1.77</v>
@@ -26680,7 +26686,7 @@
         <v>165</v>
       </c>
       <c r="P125" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q125">
         <v>1.91</v>
@@ -26886,7 +26892,7 @@
         <v>81</v>
       </c>
       <c r="P126" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -26964,10 +26970,10 @@
         <v>1.09</v>
       </c>
       <c r="AP126">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ126">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR126">
         <v>1.57</v>
@@ -27092,7 +27098,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q127">
         <v>3.3</v>
@@ -27997,7 +28003,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ131">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR131">
         <v>1.7</v>
@@ -28122,7 +28128,7 @@
         <v>169</v>
       </c>
       <c r="P132" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28328,7 +28334,7 @@
         <v>170</v>
       </c>
       <c r="P133" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q133">
         <v>3.2</v>
@@ -28406,7 +28412,7 @@
         <v>1</v>
       </c>
       <c r="AP133">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
         <v>0.92</v>
@@ -28612,7 +28618,7 @@
         <v>1.75</v>
       </c>
       <c r="AP134">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ134">
         <v>1.62</v>
@@ -28946,7 +28952,7 @@
         <v>172</v>
       </c>
       <c r="P136" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q136">
         <v>5.5</v>
@@ -29027,7 +29033,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ136">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR136">
         <v>1.36</v>
@@ -29309,6 +29315,418 @@
       </c>
       <c r="BP137">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7451105</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F138">
+        <v>28</v>
+      </c>
+      <c r="G138" t="s">
+        <v>79</v>
+      </c>
+      <c r="H138" t="s">
+        <v>74</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138" t="s">
+        <v>81</v>
+      </c>
+      <c r="P138" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q138">
+        <v>4.33</v>
+      </c>
+      <c r="R138">
+        <v>2.05</v>
+      </c>
+      <c r="S138">
+        <v>2.75</v>
+      </c>
+      <c r="T138">
+        <v>1.5</v>
+      </c>
+      <c r="U138">
+        <v>2.5</v>
+      </c>
+      <c r="V138">
+        <v>3.4</v>
+      </c>
+      <c r="W138">
+        <v>1.3</v>
+      </c>
+      <c r="X138">
+        <v>10</v>
+      </c>
+      <c r="Y138">
+        <v>1.06</v>
+      </c>
+      <c r="Z138">
+        <v>3.98</v>
+      </c>
+      <c r="AA138">
+        <v>3.16</v>
+      </c>
+      <c r="AB138">
+        <v>2</v>
+      </c>
+      <c r="AC138">
+        <v>1.08</v>
+      </c>
+      <c r="AD138">
+        <v>7</v>
+      </c>
+      <c r="AE138">
+        <v>1.4</v>
+      </c>
+      <c r="AF138">
+        <v>2.85</v>
+      </c>
+      <c r="AG138">
+        <v>2.18</v>
+      </c>
+      <c r="AH138">
+        <v>1.64</v>
+      </c>
+      <c r="AI138">
+        <v>1.91</v>
+      </c>
+      <c r="AJ138">
+        <v>1.8</v>
+      </c>
+      <c r="AK138">
+        <v>1.73</v>
+      </c>
+      <c r="AL138">
+        <v>1.34</v>
+      </c>
+      <c r="AM138">
+        <v>1.25</v>
+      </c>
+      <c r="AN138">
+        <v>1.54</v>
+      </c>
+      <c r="AO138">
+        <v>1.15</v>
+      </c>
+      <c r="AP138">
+        <v>1.43</v>
+      </c>
+      <c r="AQ138">
+        <v>1.29</v>
+      </c>
+      <c r="AR138">
+        <v>1.47</v>
+      </c>
+      <c r="AS138">
+        <v>1.45</v>
+      </c>
+      <c r="AT138">
+        <v>2.92</v>
+      </c>
+      <c r="AU138">
+        <v>0</v>
+      </c>
+      <c r="AV138">
+        <v>3</v>
+      </c>
+      <c r="AW138">
+        <v>9</v>
+      </c>
+      <c r="AX138">
+        <v>9</v>
+      </c>
+      <c r="AY138">
+        <v>9</v>
+      </c>
+      <c r="AZ138">
+        <v>12</v>
+      </c>
+      <c r="BA138">
+        <v>6</v>
+      </c>
+      <c r="BB138">
+        <v>3</v>
+      </c>
+      <c r="BC138">
+        <v>9</v>
+      </c>
+      <c r="BD138">
+        <v>2.38</v>
+      </c>
+      <c r="BE138">
+        <v>8.1</v>
+      </c>
+      <c r="BF138">
+        <v>1.78</v>
+      </c>
+      <c r="BG138">
+        <v>1.31</v>
+      </c>
+      <c r="BH138">
+        <v>2.92</v>
+      </c>
+      <c r="BI138">
+        <v>1.59</v>
+      </c>
+      <c r="BJ138">
+        <v>2.16</v>
+      </c>
+      <c r="BK138">
+        <v>2.03</v>
+      </c>
+      <c r="BL138">
+        <v>1.7</v>
+      </c>
+      <c r="BM138">
+        <v>2.67</v>
+      </c>
+      <c r="BN138">
+        <v>1.39</v>
+      </c>
+      <c r="BO138">
+        <v>3.58</v>
+      </c>
+      <c r="BP138">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7451102</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45752.57291666666</v>
+      </c>
+      <c r="F139">
+        <v>28</v>
+      </c>
+      <c r="G139" t="s">
+        <v>76</v>
+      </c>
+      <c r="H139" t="s">
+        <v>70</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>3</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>3</v>
+      </c>
+      <c r="O139" t="s">
+        <v>173</v>
+      </c>
+      <c r="P139" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q139">
+        <v>5.5</v>
+      </c>
+      <c r="R139">
+        <v>2.2</v>
+      </c>
+      <c r="S139">
+        <v>2.25</v>
+      </c>
+      <c r="T139">
+        <v>1.4</v>
+      </c>
+      <c r="U139">
+        <v>2.75</v>
+      </c>
+      <c r="V139">
+        <v>3</v>
+      </c>
+      <c r="W139">
+        <v>1.36</v>
+      </c>
+      <c r="X139">
+        <v>8</v>
+      </c>
+      <c r="Y139">
+        <v>1.08</v>
+      </c>
+      <c r="Z139">
+        <v>5.09</v>
+      </c>
+      <c r="AA139">
+        <v>3.85</v>
+      </c>
+      <c r="AB139">
+        <v>1.62</v>
+      </c>
+      <c r="AC139">
+        <v>1.01</v>
+      </c>
+      <c r="AD139">
+        <v>11.4</v>
+      </c>
+      <c r="AE139">
+        <v>1.3</v>
+      </c>
+      <c r="AF139">
+        <v>3.35</v>
+      </c>
+      <c r="AG139">
+        <v>1.96</v>
+      </c>
+      <c r="AH139">
+        <v>1.83</v>
+      </c>
+      <c r="AI139">
+        <v>1.91</v>
+      </c>
+      <c r="AJ139">
+        <v>1.8</v>
+      </c>
+      <c r="AK139">
+        <v>2.25</v>
+      </c>
+      <c r="AL139">
+        <v>1.26</v>
+      </c>
+      <c r="AM139">
+        <v>1.14</v>
+      </c>
+      <c r="AN139">
+        <v>1.38</v>
+      </c>
+      <c r="AO139">
+        <v>1.23</v>
+      </c>
+      <c r="AP139">
+        <v>1.5</v>
+      </c>
+      <c r="AQ139">
+        <v>1.14</v>
+      </c>
+      <c r="AR139">
+        <v>1.32</v>
+      </c>
+      <c r="AS139">
+        <v>1.8</v>
+      </c>
+      <c r="AT139">
+        <v>3.12</v>
+      </c>
+      <c r="AU139">
+        <v>8</v>
+      </c>
+      <c r="AV139">
+        <v>4</v>
+      </c>
+      <c r="AW139">
+        <v>8</v>
+      </c>
+      <c r="AX139">
+        <v>6</v>
+      </c>
+      <c r="AY139">
+        <v>16</v>
+      </c>
+      <c r="AZ139">
+        <v>10</v>
+      </c>
+      <c r="BA139">
+        <v>8</v>
+      </c>
+      <c r="BB139">
+        <v>6</v>
+      </c>
+      <c r="BC139">
+        <v>14</v>
+      </c>
+      <c r="BD139">
+        <v>3.12</v>
+      </c>
+      <c r="BE139">
+        <v>8.4</v>
+      </c>
+      <c r="BF139">
+        <v>1.5</v>
+      </c>
+      <c r="BG139">
+        <v>1.39</v>
+      </c>
+      <c r="BH139">
+        <v>2.67</v>
+      </c>
+      <c r="BI139">
+        <v>1.72</v>
+      </c>
+      <c r="BJ139">
+        <v>2</v>
+      </c>
+      <c r="BK139">
+        <v>2.19</v>
+      </c>
+      <c r="BL139">
+        <v>1.57</v>
+      </c>
+      <c r="BM139">
+        <v>2.92</v>
+      </c>
+      <c r="BN139">
+        <v>1.31</v>
+      </c>
+      <c r="BO139">
+        <v>3.95</v>
+      </c>
+      <c r="BP139">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Croatia Prva HNL_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="242">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,6 +538,9 @@
     <t>['21', '53', '67']</t>
   </si>
   <si>
+    <t>['21', '40', '61', '79']</t>
+  </si>
+  <si>
     <t>['8', '61']</t>
   </si>
   <si>
@@ -731,6 +734,12 @@
   </si>
   <si>
     <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['75']</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1966,7 +1975,7 @@
         <v>83</v>
       </c>
       <c r="P5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2172,7 +2181,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2456,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ7">
         <v>1.29</v>
@@ -2790,7 +2799,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q9">
         <v>4.33</v>
@@ -2868,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ9">
         <v>1.29</v>
@@ -2996,7 +3005,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -3283,7 +3292,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ11">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3614,7 +3623,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q13">
         <v>3.25</v>
@@ -3820,7 +3829,7 @@
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -4026,7 +4035,7 @@
         <v>92</v>
       </c>
       <c r="P15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -4107,7 +4116,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ15">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR15">
         <v>0.6899999999999999</v>
@@ -4516,7 +4525,7 @@
         <v>1.5</v>
       </c>
       <c r="AP17">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17">
         <v>0.71</v>
@@ -4850,7 +4859,7 @@
         <v>95</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -5056,7 +5065,7 @@
         <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -5262,7 +5271,7 @@
         <v>81</v>
       </c>
       <c r="P21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -5343,7 +5352,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ21">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR21">
         <v>2.05</v>
@@ -5468,7 +5477,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5674,7 +5683,7 @@
         <v>81</v>
       </c>
       <c r="P23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -5961,7 +5970,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ24">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR24">
         <v>1.41</v>
@@ -6164,7 +6173,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ25">
         <v>0.93</v>
@@ -6292,7 +6301,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>5.5</v>
@@ -6498,7 +6507,7 @@
         <v>81</v>
       </c>
       <c r="P27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
@@ -6704,7 +6713,7 @@
         <v>81</v>
       </c>
       <c r="P28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6910,7 +6919,7 @@
         <v>81</v>
       </c>
       <c r="P29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -6991,7 +7000,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR29">
         <v>1.12</v>
@@ -7400,7 +7409,7 @@
         <v>1.33</v>
       </c>
       <c r="AP31">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ31">
         <v>0.93</v>
@@ -7734,7 +7743,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -7940,7 +7949,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -8146,7 +8155,7 @@
         <v>81</v>
       </c>
       <c r="P35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q35">
         <v>3.5</v>
@@ -8224,10 +8233,10 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ35">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR35">
         <v>1.65</v>
@@ -8636,7 +8645,7 @@
         <v>0.75</v>
       </c>
       <c r="AP37">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -9382,7 +9391,7 @@
         <v>107</v>
       </c>
       <c r="P41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q41">
         <v>3.1</v>
@@ -9588,7 +9597,7 @@
         <v>108</v>
       </c>
       <c r="P42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q42">
         <v>4</v>
@@ -9669,7 +9678,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ42">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -9872,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ43">
         <v>0.21</v>
@@ -10081,7 +10090,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ44">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR44">
         <v>1.77</v>
@@ -10206,7 +10215,7 @@
         <v>81</v>
       </c>
       <c r="P45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q45">
         <v>6</v>
@@ -10618,7 +10627,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>4.5</v>
@@ -10696,10 +10705,10 @@
         <v>2</v>
       </c>
       <c r="AP47">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ47">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR47">
         <v>1.56</v>
@@ -10824,7 +10833,7 @@
         <v>112</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q48">
         <v>4.5</v>
@@ -10902,10 +10911,10 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ48">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR48">
         <v>1.2</v>
@@ -11030,7 +11039,7 @@
         <v>113</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>6.5</v>
@@ -11236,7 +11245,7 @@
         <v>81</v>
       </c>
       <c r="P50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q50">
         <v>5.5</v>
@@ -11648,7 +11657,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11854,7 +11863,7 @@
         <v>116</v>
       </c>
       <c r="P53" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q53">
         <v>1.8</v>
@@ -12266,7 +12275,7 @@
         <v>117</v>
       </c>
       <c r="P55" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q55">
         <v>1.8</v>
@@ -12347,7 +12356,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ55">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR55">
         <v>1.97</v>
@@ -12678,7 +12687,7 @@
         <v>81</v>
       </c>
       <c r="P57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q57">
         <v>8.5</v>
@@ -12756,7 +12765,7 @@
         <v>1.6</v>
       </c>
       <c r="AP57">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ57">
         <v>1.14</v>
@@ -12884,7 +12893,7 @@
         <v>81</v>
       </c>
       <c r="P58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12962,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ58">
         <v>1.29</v>
@@ -13377,7 +13386,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ60">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR60">
         <v>1.28</v>
@@ -13708,7 +13717,7 @@
         <v>81</v>
       </c>
       <c r="P62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q62">
         <v>4</v>
@@ -13786,7 +13795,7 @@
         <v>0.8</v>
       </c>
       <c r="AP62">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -13914,7 +13923,7 @@
         <v>121</v>
       </c>
       <c r="P63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63">
         <v>9.5</v>
@@ -14120,7 +14129,7 @@
         <v>118</v>
       </c>
       <c r="P64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>1.91</v>
@@ -14326,7 +14335,7 @@
         <v>122</v>
       </c>
       <c r="P65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q65">
         <v>3.1</v>
@@ -14532,7 +14541,7 @@
         <v>123</v>
       </c>
       <c r="P66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14613,7 +14622,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ66">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR66">
         <v>1.64</v>
@@ -14738,7 +14747,7 @@
         <v>124</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -14944,7 +14953,7 @@
         <v>125</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q68">
         <v>2.75</v>
@@ -15231,7 +15240,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ69">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR69">
         <v>1.96</v>
@@ -15356,7 +15365,7 @@
         <v>126</v>
       </c>
       <c r="P70" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15640,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ71">
         <v>0.21</v>
@@ -15768,7 +15777,7 @@
         <v>128</v>
       </c>
       <c r="P72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q72">
         <v>2.25</v>
@@ -15974,7 +15983,7 @@
         <v>129</v>
       </c>
       <c r="P73" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q73">
         <v>3.75</v>
@@ -16055,7 +16064,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ73">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR73">
         <v>1.53</v>
@@ -16386,7 +16395,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q75">
         <v>2.6</v>
@@ -16464,7 +16473,7 @@
         <v>0.71</v>
       </c>
       <c r="AP75">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -17416,7 +17425,7 @@
         <v>81</v>
       </c>
       <c r="P80" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q80">
         <v>7</v>
@@ -17494,10 +17503,10 @@
         <v>1.86</v>
       </c>
       <c r="AP80">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ80">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR80">
         <v>1.06</v>
@@ -17828,7 +17837,7 @@
         <v>135</v>
       </c>
       <c r="P82" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -18034,7 +18043,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q83">
         <v>6</v>
@@ -18112,7 +18121,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ83">
         <v>1.14</v>
@@ -18240,7 +18249,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q84">
         <v>2.2</v>
@@ -18527,7 +18536,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ85">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -18652,7 +18661,7 @@
         <v>138</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q86">
         <v>3.1</v>
@@ -18733,7 +18742,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ86">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR86">
         <v>1.59</v>
@@ -18858,7 +18867,7 @@
         <v>139</v>
       </c>
       <c r="P87" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q87">
         <v>2.25</v>
@@ -19064,7 +19073,7 @@
         <v>140</v>
       </c>
       <c r="P88" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19270,7 +19279,7 @@
         <v>141</v>
       </c>
       <c r="P89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q89">
         <v>1.91</v>
@@ -19682,7 +19691,7 @@
         <v>143</v>
       </c>
       <c r="P91" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q91">
         <v>7</v>
@@ -19760,7 +19769,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ91">
         <v>1.29</v>
@@ -19888,7 +19897,7 @@
         <v>144</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>1.95</v>
@@ -20094,7 +20103,7 @@
         <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20300,7 +20309,7 @@
         <v>145</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q94">
         <v>1.91</v>
@@ -20506,7 +20515,7 @@
         <v>146</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q95">
         <v>2.1</v>
@@ -21124,7 +21133,7 @@
         <v>83</v>
       </c>
       <c r="P98" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21202,7 +21211,7 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ98">
         <v>1.29</v>
@@ -21411,7 +21420,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ99">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR99">
         <v>1.4</v>
@@ -21536,7 +21545,7 @@
         <v>148</v>
       </c>
       <c r="P100" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q100">
         <v>4.75</v>
@@ -21614,7 +21623,7 @@
         <v>1.44</v>
       </c>
       <c r="AP100">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ100">
         <v>1.29</v>
@@ -22235,7 +22244,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ103">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR103">
         <v>1.14</v>
@@ -22566,7 +22575,7 @@
         <v>81</v>
       </c>
       <c r="P105" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q105">
         <v>1.93</v>
@@ -22772,7 +22781,7 @@
         <v>153</v>
       </c>
       <c r="P106" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22978,7 +22987,7 @@
         <v>154</v>
       </c>
       <c r="P107" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q107">
         <v>3.5</v>
@@ -23056,7 +23065,7 @@
         <v>1</v>
       </c>
       <c r="AP107">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23184,7 +23193,7 @@
         <v>155</v>
       </c>
       <c r="P108" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q108">
         <v>4.7</v>
@@ -23390,7 +23399,7 @@
         <v>156</v>
       </c>
       <c r="P109" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q109">
         <v>1.56</v>
@@ -23802,7 +23811,7 @@
         <v>81</v>
       </c>
       <c r="P111" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q111">
         <v>3.55</v>
@@ -23883,7 +23892,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ111">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24086,7 +24095,7 @@
         <v>0.82</v>
       </c>
       <c r="AP112">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ112">
         <v>0.93</v>
@@ -24295,7 +24304,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ113">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR113">
         <v>1.48</v>
@@ -25038,7 +25047,7 @@
         <v>160</v>
       </c>
       <c r="P117" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25325,7 +25334,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ118">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR118">
         <v>1.07</v>
@@ -25450,7 +25459,7 @@
         <v>161</v>
       </c>
       <c r="P119" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q119">
         <v>2.49</v>
@@ -25656,7 +25665,7 @@
         <v>162</v>
       </c>
       <c r="P120" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -25862,7 +25871,7 @@
         <v>81</v>
       </c>
       <c r="P121" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q121">
         <v>3.6</v>
@@ -25940,7 +25949,7 @@
         <v>0.75</v>
       </c>
       <c r="AP121">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ121">
         <v>0.93</v>
@@ -26068,7 +26077,7 @@
         <v>163</v>
       </c>
       <c r="P122" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q122">
         <v>1.77</v>
@@ -26558,10 +26567,10 @@
         <v>1.09</v>
       </c>
       <c r="AP124">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ124">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR124">
         <v>1.51</v>
@@ -26686,7 +26695,7 @@
         <v>165</v>
       </c>
       <c r="P125" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q125">
         <v>1.91</v>
@@ -26892,7 +26901,7 @@
         <v>81</v>
       </c>
       <c r="P126" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q126">
         <v>4.33</v>
@@ -27098,7 +27107,7 @@
         <v>81</v>
       </c>
       <c r="P127" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q127">
         <v>3.3</v>
@@ -27382,7 +27391,7 @@
         <v>1.08</v>
       </c>
       <c r="AP128">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -28128,7 +28137,7 @@
         <v>169</v>
       </c>
       <c r="P132" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q132">
         <v>2.5</v>
@@ -28206,7 +28215,7 @@
         <v>0.08</v>
       </c>
       <c r="AP132">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ132">
         <v>0.21</v>
@@ -28334,7 +28343,7 @@
         <v>170</v>
       </c>
       <c r="P133" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q133">
         <v>3.2</v>
@@ -28415,7 +28424,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ133">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR133">
         <v>1.26</v>
@@ -28621,7 +28630,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ134">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR134">
         <v>1.47</v>
@@ -28952,7 +28961,7 @@
         <v>172</v>
       </c>
       <c r="P136" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q136">
         <v>5.5</v>
@@ -29364,7 +29373,7 @@
         <v>81</v>
       </c>
       <c r="P138" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q138">
         <v>4.33</v>
@@ -29727,6 +29736,418 @@
       </c>
       <c r="BP139">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7451104</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45753.45833333334</v>
+      </c>
+      <c r="F140">
+        <v>28</v>
+      </c>
+      <c r="G140" t="s">
+        <v>77</v>
+      </c>
+      <c r="H140" t="s">
+        <v>72</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>1</v>
+      </c>
+      <c r="O140" t="s">
+        <v>81</v>
+      </c>
+      <c r="P140" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q140">
+        <v>4.4</v>
+      </c>
+      <c r="R140">
+        <v>1.98</v>
+      </c>
+      <c r="S140">
+        <v>2.69</v>
+      </c>
+      <c r="T140">
+        <v>1.47</v>
+      </c>
+      <c r="U140">
+        <v>2.5</v>
+      </c>
+      <c r="V140">
+        <v>3.15</v>
+      </c>
+      <c r="W140">
+        <v>1.31</v>
+      </c>
+      <c r="X140">
+        <v>7.6</v>
+      </c>
+      <c r="Y140">
+        <v>1.03</v>
+      </c>
+      <c r="Z140">
+        <v>3.64</v>
+      </c>
+      <c r="AA140">
+        <v>3.25</v>
+      </c>
+      <c r="AB140">
+        <v>2.07</v>
+      </c>
+      <c r="AC140">
+        <v>1.04</v>
+      </c>
+      <c r="AD140">
+        <v>7.1</v>
+      </c>
+      <c r="AE140">
+        <v>1.35</v>
+      </c>
+      <c r="AF140">
+        <v>2.75</v>
+      </c>
+      <c r="AG140">
+        <v>2.19</v>
+      </c>
+      <c r="AH140">
+        <v>1.65</v>
+      </c>
+      <c r="AI140">
+        <v>1.92</v>
+      </c>
+      <c r="AJ140">
+        <v>1.79</v>
+      </c>
+      <c r="AK140">
+        <v>1.73</v>
+      </c>
+      <c r="AL140">
+        <v>1.33</v>
+      </c>
+      <c r="AM140">
+        <v>1.27</v>
+      </c>
+      <c r="AN140">
+        <v>1.38</v>
+      </c>
+      <c r="AO140">
+        <v>1.62</v>
+      </c>
+      <c r="AP140">
+        <v>1.29</v>
+      </c>
+      <c r="AQ140">
+        <v>1.71</v>
+      </c>
+      <c r="AR140">
+        <v>1.57</v>
+      </c>
+      <c r="AS140">
+        <v>1.25</v>
+      </c>
+      <c r="AT140">
+        <v>2.82</v>
+      </c>
+      <c r="AU140">
+        <v>2</v>
+      </c>
+      <c r="AV140">
+        <v>4</v>
+      </c>
+      <c r="AW140">
+        <v>7</v>
+      </c>
+      <c r="AX140">
+        <v>9</v>
+      </c>
+      <c r="AY140">
+        <v>9</v>
+      </c>
+      <c r="AZ140">
+        <v>13</v>
+      </c>
+      <c r="BA140">
+        <v>8</v>
+      </c>
+      <c r="BB140">
+        <v>7</v>
+      </c>
+      <c r="BC140">
+        <v>15</v>
+      </c>
+      <c r="BD140">
+        <v>2.34</v>
+      </c>
+      <c r="BE140">
+        <v>7.5</v>
+      </c>
+      <c r="BF140">
+        <v>1.82</v>
+      </c>
+      <c r="BG140">
+        <v>1.39</v>
+      </c>
+      <c r="BH140">
+        <v>2.77</v>
+      </c>
+      <c r="BI140">
+        <v>1.68</v>
+      </c>
+      <c r="BJ140">
+        <v>2.11</v>
+      </c>
+      <c r="BK140">
+        <v>2.11</v>
+      </c>
+      <c r="BL140">
+        <v>1.68</v>
+      </c>
+      <c r="BM140">
+        <v>2.7</v>
+      </c>
+      <c r="BN140">
+        <v>1.41</v>
+      </c>
+      <c r="BO140">
+        <v>3.65</v>
+      </c>
+      <c r="BP140">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7451101</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45753.57291666666</v>
+      </c>
+      <c r="F141">
+        <v>28</v>
+      </c>
+      <c r="G141" t="s">
+        <v>75</v>
+      </c>
+      <c r="H141" t="s">
+        <v>73</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>2</v>
+      </c>
+      <c r="L141">
+        <v>4</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>5</v>
+      </c>
+      <c r="O141" t="s">
+        <v>174</v>
+      </c>
+      <c r="P141" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q141">
+        <v>4.2</v>
+      </c>
+      <c r="R141">
+        <v>1.95</v>
+      </c>
+      <c r="S141">
+        <v>2.83</v>
+      </c>
+      <c r="T141">
+        <v>1.49</v>
+      </c>
+      <c r="U141">
+        <v>2.44</v>
+      </c>
+      <c r="V141">
+        <v>3.34</v>
+      </c>
+      <c r="W141">
+        <v>1.28</v>
+      </c>
+      <c r="X141">
+        <v>8.9</v>
+      </c>
+      <c r="Y141">
+        <v>1.01</v>
+      </c>
+      <c r="Z141">
+        <v>3.4</v>
+      </c>
+      <c r="AA141">
+        <v>3.22</v>
+      </c>
+      <c r="AB141">
+        <v>2.17</v>
+      </c>
+      <c r="AC141">
+        <v>1.04</v>
+      </c>
+      <c r="AD141">
+        <v>7.1</v>
+      </c>
+      <c r="AE141">
+        <v>1.4</v>
+      </c>
+      <c r="AF141">
+        <v>2.57</v>
+      </c>
+      <c r="AG141">
+        <v>2.35</v>
+      </c>
+      <c r="AH141">
+        <v>1.57</v>
+      </c>
+      <c r="AI141">
+        <v>2</v>
+      </c>
+      <c r="AJ141">
+        <v>1.72</v>
+      </c>
+      <c r="AK141">
+        <v>1.66</v>
+      </c>
+      <c r="AL141">
+        <v>1.33</v>
+      </c>
+      <c r="AM141">
+        <v>1.3</v>
+      </c>
+      <c r="AN141">
+        <v>0.92</v>
+      </c>
+      <c r="AO141">
+        <v>0.92</v>
+      </c>
+      <c r="AP141">
+        <v>1.07</v>
+      </c>
+      <c r="AQ141">
+        <v>0.86</v>
+      </c>
+      <c r="AR141">
+        <v>1.17</v>
+      </c>
+      <c r="AS141">
+        <v>1.29</v>
+      </c>
+      <c r="AT141">
+        <v>2.46</v>
+      </c>
+      <c r="AU141">
+        <v>7</v>
+      </c>
+      <c r="AV141">
+        <v>2</v>
+      </c>
+      <c r="AW141">
+        <v>3</v>
+      </c>
+      <c r="AX141">
+        <v>6</v>
+      </c>
+      <c r="AY141">
+        <v>10</v>
+      </c>
+      <c r="AZ141">
+        <v>8</v>
+      </c>
+      <c r="BA141">
+        <v>3</v>
+      </c>
+      <c r="BB141">
+        <v>5</v>
+      </c>
+      <c r="BC141">
+        <v>8</v>
+      </c>
+      <c r="BD141">
+        <v>2.29</v>
+      </c>
+      <c r="BE141">
+        <v>7.5</v>
+      </c>
+      <c r="BF141">
+        <v>1.85</v>
+      </c>
+      <c r="BG141">
+        <v>1.39</v>
+      </c>
+      <c r="BH141">
+        <v>2.77</v>
+      </c>
+      <c r="BI141">
+        <v>1.68</v>
+      </c>
+      <c r="BJ141">
+        <v>2.11</v>
+      </c>
+      <c r="BK141">
+        <v>2.11</v>
+      </c>
+      <c r="BL141">
+        <v>1.68</v>
+      </c>
+      <c r="BM141">
+        <v>2.7</v>
+      </c>
+      <c r="BN141">
+        <v>1.41</v>
+      </c>
+      <c r="BO141">
+        <v>3.65</v>
+      </c>
+      <c r="BP141">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
